--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -22,7 +22,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$107</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$117</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$101</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -770,181 +770,181 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.6% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.9% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.8% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.6% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.9% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.8% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 15070억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 15070억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 19077억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 19511억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 23242억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 24098억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 27257억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 28662억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 31268억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 33280억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 35337억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 37958억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 39441억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 42672억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 43574억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 47420억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 46324억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 50536억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 47809억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 52184억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1365,6 +1365,126 @@
       <text>
         <t>모델값 역산(implied): 전분기 + 지배주주순이익 − v
 전분기 + 지배주주순이익 − 배당</t>
+      </text>
+    </comment>
+    <comment ref="AC33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AD33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AF33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AG33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AH33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AI33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AK33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AL33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AM33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AN33" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+마지막 실적 유지(가정)</t>
+      </text>
+    </comment>
+    <comment ref="AC34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AD34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AF34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AG34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AH34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AI34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AK34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AL34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AM34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
+      </text>
+    </comment>
+    <comment ref="AN34" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 전분기 − 1
+전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
@@ -2099,61 +2219,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.6% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.9% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.8% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
@@ -2249,121 +2369,121 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.6% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 14.8%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.3% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.9% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.8% + 회사 캘리브레이션 +4.4%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 -2.8%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 15070억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 15070억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 19077억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 19511억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 23242억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 24098억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 27257억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 28662억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 31268억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 33280억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 35337억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 37958억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 39441억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 42672억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 43574억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 47420억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 46324억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 50536억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 47809억 × 4.64% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 52184억 × 4.64% − 총차입금 5940억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -2965,6 +3085,126 @@
       <text>
         <t>추정: 전분기 + 지배주주순이익 − 배당
 [roll]</t>
+      </text>
+    </comment>
+    <comment ref="AC22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN22" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 마지막 실적 유지(가정)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AC23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AD23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AF23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AG23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AH23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AI23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AK23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AL23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AM23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
+      </text>
+    </comment>
+    <comment ref="AN23" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 전분기 − (순이익 − 배당): 순이익 = 순현금 증가 가정(CAPEX≈감가, 운전자본 불변)
+[qoq]</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
@@ -4441,7 +4681,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4562,14 +4802,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출은 2026Q2 기준 잔고 소진분만 — 이후 신규 수주 매출 미포함(2028 감소는 이 한계). forecast_panel 모듈 참고 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출은 2026Q2 기준 잔고 소진분만 — 신규수주 매출 미포함(forecast_panel 042660 status partial(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) — new_order_revenue 값 없음; 2028 감소는 이 한계). forecast_panel 모듈 참고 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.8, "op_wape_pct": 51.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 31776.86, "rev_act": 30233.58, "op_pred": 2132.75, "op_act": 2897.59}, {"q": "2025Q4", "rev_pred": 31776.86, "rev_act": 33229.51, "op_pred": 2132.75, "op_act": 2475.19}, {"q": "2026Q1", "rev_pred": 31609.47, "rev_act": 32099.4, "op_pred": 2096.51, "op_act": 4410.65}, {"q": "2026Q2", "rev_pred": 31245.58, "rev_act": 54431.71, "op_pred": 2039.44, "op_act": 7361.14}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 17.8, "op_wape_pct": 51.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "sls_marine_plus_uncovered_backlog_runoff", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 31776.86, "rev_act": 30233.58, "op_pred": 2132.75, "op_act": 2897.59}, {"q": "2025Q4", "rev_pred": 31776.86, "rev_act": 33229.51, "op_pred": 2132.75, "op_act": 2475.19}, {"q": "2026Q1", "rev_pred": 31609.47, "rev_act": 32099.4, "op_pred": 2105.18, "op_act": 4410.65}, {"q": "2026Q2", "rev_pred": 31245.58, "rev_act": 54431.71, "op_pred": 2012.41, "op_act": 7361.14}]}</t>
         </is>
       </c>
     </row>
@@ -8771,42 +9011,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.108688</v>
+        <v>0.119738</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109488</v>
+        <v>0.119938</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.107388</v>
+        <v>0.121238</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.106888</v>
+        <v>0.122138</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.106988</v>
+        <v>0.122138</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.107088</v>
+        <v>0.122138</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.107088</v>
+        <v>0.122138</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109088</v>
+        <v>0.122138</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.112688</v>
+        <v>0.122138</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.111988</v>
+        <v>0.122138</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8899,36 +9139,36 @@
         <v/>
       </c>
       <c r="AC24" s="24" t="n">
-        <v>0.134656</v>
+        <v>0.249478</v>
       </c>
       <c r="AD24" s="24" t="n">
-        <v>0.469799</v>
+        <v>0.609396</v>
       </c>
       <c r="AE24" s="25" t="n"/>
       <c r="AF24" s="24" t="n">
-        <v>-0.218341</v>
+        <v>-0.117904</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>-0.20932</v>
+        <v>-0.09689300000000001</v>
       </c>
       <c r="AH24" s="24" t="n">
-        <v>-0.015639</v>
+        <v>0.02005</v>
       </c>
       <c r="AI24" s="24" t="n">
-        <v>-0.021918</v>
+        <v>0.018349</v>
       </c>
       <c r="AJ24" s="25" t="n"/>
       <c r="AK24" s="24" t="n">
-        <v>-0.002793</v>
+        <v>0.007426</v>
       </c>
       <c r="AL24" s="24" t="n">
-        <v>0.02058</v>
+        <v>0</v>
       </c>
       <c r="AM24" s="24" t="n">
-        <v>0.053271</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="24" t="n">
-        <v>0.045752</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="25" t="n"/>
     </row>
@@ -9048,39 +9288,39 @@
         <v>174.84</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>221.33</v>
+        <v>226.37</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>269.65</v>
+        <v>279.59</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>316.23</v>
+        <v>332.54</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>362.77</v>
+        <v>386.11</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>409.98</v>
+        <v>440.39</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>457.59</v>
+        <v>495.08</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>505.54</v>
+        <v>550.17</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>537.45</v>
+        <v>586.3099999999999</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>554.6799999999999</v>
+        <v>605.4400000000001</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -9520,16 +9760,16 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.049999</v>
+        <v>0.05</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.05</v>
+        <v>0.050001</v>
       </c>
       <c r="AH28" s="24" t="n">
         <v>0.05</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.049999</v>
+        <v>0.05</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
@@ -9539,10 +9779,10 @@
         <v>0.05</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.050001</v>
+        <v>0.05</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.049998</v>
+        <v>0.049999</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>0.05</v>
@@ -9665,10 +9905,10 @@
         <v/>
       </c>
       <c r="AC29" s="24" t="n">
+        <v>0.999966</v>
+      </c>
+      <c r="AD29" s="24" t="n">
         <v>0.999965</v>
-      </c>
-      <c r="AD29" s="24" t="n">
-        <v>0.999964</v>
       </c>
       <c r="AE29" s="25">
         <f>IFERROR(subQ!AE17/subQ!AE16,"")</f>
@@ -9691,16 +9931,16 @@
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.999966</v>
+        <v>0.999964</v>
       </c>
       <c r="AL29" s="24" t="n">
-        <v>0.9999670000000001</v>
+        <v>0.999965</v>
       </c>
       <c r="AM29" s="24" t="n">
-        <v>0.999966</v>
+        <v>0.999964</v>
       </c>
       <c r="AN29" s="24" t="n">
-        <v>0.999966</v>
+        <v>0.999963</v>
       </c>
       <c r="AO29" s="25">
         <f>IFERROR(subQ!AO17/subQ!AO16,"")</f>
@@ -9933,20 +10173,20 @@
         <v>0.0029</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
@@ -9956,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -10061,7 +10301,7 @@
         <v>0.002</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
@@ -10078,16 +10318,16 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AL32" s="29" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AM32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -10185,18 +10425,38 @@
         <f>IFERROR(subQ!AB22/subQ!AA22-1,"")</f>
         <v/>
       </c>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
+      <c r="AC33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AE33" s="25" t="n"/>
-      <c r="AF33" s="31" t="n"/>
-      <c r="AG33" s="31" t="n"/>
-      <c r="AH33" s="31" t="n"/>
-      <c r="AI33" s="31" t="n"/>
+      <c r="AF33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ33" s="25" t="n"/>
-      <c r="AK33" s="31" t="n"/>
-      <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="31" t="n"/>
-      <c r="AN33" s="31" t="n"/>
+      <c r="AK33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="AO33" s="25" t="n"/>
     </row>
     <row r="34">
@@ -10293,18 +10553,38 @@
         <f>IFERROR(subQ!AB23/subQ!AA23-1,"")</f>
         <v/>
       </c>
-      <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="31" t="n"/>
+      <c r="AC34" s="24" t="n">
+        <v>0.486363</v>
+      </c>
+      <c r="AD34" s="24" t="n">
+        <v>0.338024</v>
+      </c>
       <c r="AE34" s="25" t="n"/>
-      <c r="AF34" s="31" t="n"/>
-      <c r="AG34" s="31" t="n"/>
-      <c r="AH34" s="31" t="n"/>
-      <c r="AI34" s="31" t="n"/>
+      <c r="AF34" s="24" t="n">
+        <v>0.251358</v>
+      </c>
+      <c r="AG34" s="24" t="n">
+        <v>0.203196</v>
+      </c>
+      <c r="AH34" s="24" t="n">
+        <v>0.171121</v>
+      </c>
+      <c r="AI34" s="24" t="n">
+        <v>0.147232</v>
+      </c>
       <c r="AJ34" s="25" t="n"/>
-      <c r="AK34" s="31" t="n"/>
-      <c r="AL34" s="31" t="n"/>
-      <c r="AM34" s="31" t="n"/>
-      <c r="AN34" s="31" t="n"/>
+      <c r="AK34" s="24" t="n">
+        <v>0.129267</v>
+      </c>
+      <c r="AL34" s="24" t="n">
+        <v>0.075101</v>
+      </c>
+      <c r="AM34" s="24" t="n">
+        <v>0.036965</v>
+      </c>
+      <c r="AN34" s="24" t="n">
+        <v>0.035535</v>
+      </c>
       <c r="AO34" s="25" t="n"/>
     </row>
     <row r="35">
@@ -10402,36 +10682,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.265883</v>
+        <v>0.294662</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.218299</v>
+        <v>0.235115</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.172755</v>
+        <v>0.1894</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.147174</v>
+        <v>0.161086</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.130121</v>
+        <v>0.140578</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.116124</v>
+        <v>0.124192</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.104793</v>
+        <v>0.111273</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.06312</v>
+        <v>0.065694</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.032051</v>
+        <v>0.03262</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.030768</v>
+        <v>0.03149</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11054,36 +11334,36 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.57254</v>
+        <v>-0.580708</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.5881150000000001</v>
+        <v>-0.60485</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.527042</v>
+        <v>-0.559493</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.170272</v>
+        <v>-0.261786</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>0.355778</v>
+        <v>0.218924</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>0.240464</v>
+        <v>0.127917</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>0.171136</v>
+        <v>0.093988</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>0.07620300000000001</v>
+        <v>0.054846</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>0.304027</v>
+        <v>0.296043</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>0.64639</v>
+        <v>0.664368</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -11173,36 +11453,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>-0.463158</v>
+        <v>-0.466667</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.507614</v>
+        <v>-0.51269</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.5391010000000001</v>
+        <v>-0.545757</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.466801</v>
+        <v>-0.478873</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>-0.169935</v>
+        <v>-0.1875</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>-0.164948</v>
+        <v>-0.180556</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.155235</v>
+        <v>-0.175824</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.139623</v>
+        <v>-0.15444</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.11811</v>
+        <v>-0.125506</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.090535</v>
+        <v>-0.097458</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -11474,42 +11754,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>0.108688</v>
+        <v>0.119738</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.109488</v>
+        <v>0.119938</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.107388</v>
+        <v>0.121238</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.106888</v>
+        <v>0.122138</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.106988</v>
+        <v>0.122138</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.107088</v>
+        <v>0.122138</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.107088</v>
+        <v>0.122138</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.109088</v>
+        <v>0.122138</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.112688</v>
+        <v>0.122138</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.111988</v>
+        <v>0.122139</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -11784,42 +12064,42 @@
         <v/>
       </c>
       <c r="AC46" s="24" t="n">
-        <v>0.108678</v>
+        <v>0.119744</v>
       </c>
       <c r="AD46" s="24" t="n">
-        <v>0.10948</v>
+        <v>0.119933</v>
       </c>
       <c r="AE46" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF46" s="24" t="n">
-        <v>0.10738</v>
+        <v>0.121231</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.106885</v>
+        <v>0.122151</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.106979</v>
+        <v>0.122151</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.107097</v>
+        <v>0.122151</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
-        <v>0.107097</v>
+        <v>0.122151</v>
       </c>
       <c r="AL46" s="24" t="n">
-        <v>0.109079</v>
+        <v>0.122151</v>
       </c>
       <c r="AM46" s="24" t="n">
-        <v>0.112689</v>
+        <v>0.122151</v>
       </c>
       <c r="AN46" s="24" t="n">
-        <v>0.111982</v>
+        <v>0.122151</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO36,"")</f>
@@ -12314,7 +12594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO107"/>
+  <dimension ref="A1:AO117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12562,7 +12842,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15561,7 +15841,9 @@
       <c r="P36" s="9" t="n"/>
       <c r="U36" s="9" t="n"/>
       <c r="Z36" s="9" t="n"/>
-      <c r="AB36" s="5" t="n"/>
+      <c r="AB36" s="19" t="n">
+        <v>594000</v>
+      </c>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
@@ -16864,7 +17146,9 @@
       </c>
       <c r="U51" s="9" t="n"/>
       <c r="Z51" s="9" t="n"/>
-      <c r="AB51" s="5" t="n"/>
+      <c r="AB51" s="19" t="n">
+        <v>594000</v>
+      </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
@@ -16932,7 +17216,9 @@
       </c>
       <c r="U52" s="9" t="n"/>
       <c r="Z52" s="9" t="n"/>
-      <c r="AB52" s="5" t="n"/>
+      <c r="AB52" s="19" t="n">
+        <v>-913031.1800000001</v>
+      </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
       <c r="AE52" s="11" t="n"/>
@@ -19462,78 +19748,47 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>28365.93</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>-725825.8100000001</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>-279038.48</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>-178055.47</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>117487.13</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>-1065432.63</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>-776346.72</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>18351.27</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>-726049.36</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>-455110.5</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>-1939155.31</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
       <c r="Q87" s="18" t="n">
-        <v>-1164444.89</v>
+        <v>22627</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>-502494.72</v>
+        <v>24380</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>-982928.98</v>
+        <v>19162</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>-254705.88</v>
+        <v>-1895</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>-2904574.47</v>
+        <v>64274</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>222413.2</v>
+        <v>17967</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>625473.29</v>
+        <v>17323</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>-340157.92</v>
+        <v>11726</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>806943.01</v>
+        <v>28820</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>1314671.58</v>
+        <v>75836</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>221996.29</v>
+        <v>9995</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>818214.29</v>
+        <v>17609</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -19555,70 +19810,47 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>0</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>570.89</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>585.74</v>
-      </c>
-      <c r="L88" s="18" t="n">
-        <v>950</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>73.25</v>
-      </c>
-      <c r="N88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="34" t="n">
-        <v>1023.25</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
       <c r="Q88" s="18" t="n">
-        <v>874</v>
+        <v>42</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>180.29</v>
+        <v>138</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>23.91</v>
+        <v>24</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-23.91</v>
+        <v>-24</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>1054.29</v>
+        <v>180</v>
+      </c>
+      <c r="V88" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="W88" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>3.19</v>
+        <v>2</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="Z88" s="34" t="n">
+        <v>29</v>
+      </c>
       <c r="AA88" s="18" t="n">
-        <v>121.28</v>
+        <v>172</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>51.64</v>
+        <v>1</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -19640,78 +19872,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>7088.08</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>8233.24</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>20154.3</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>8731.629999999999</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>10813.24</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>47932.41</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>11840.48</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>2092.89</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>15650.8</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>23849.44</v>
-      </c>
-      <c r="P89" s="34" t="n">
-        <v>53433.61</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
       <c r="Q89" s="18" t="n">
-        <v>17990.78</v>
+        <v>38982</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>16925.54</v>
+        <v>50689</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>14328.67</v>
+        <v>51808</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>9180.48</v>
+        <v>31036</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>58425.47</v>
+        <v>172515</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>7649.97</v>
+        <v>51493</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>8719.76</v>
+        <v>52609</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>4860.76</v>
+        <v>52080</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>8226.370000000001</v>
+        <v>39548</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>29456.86</v>
+        <v>195730</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>22274.1</v>
+        <v>56339</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>8554.870000000001</v>
+        <v>57194</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -19733,78 +19934,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>-17785.61</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>-12600.45</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>-17975.27</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>-22239.45</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>-24468.02</v>
-      </c>
-      <c r="K90" s="34" t="n">
-        <v>-77283.19</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>-38266.93</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>-42682.63</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>-28547.14</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>-32046.25</v>
-      </c>
-      <c r="P90" s="34" t="n">
-        <v>-141542.95</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
       <c r="Q90" s="18" t="n">
-        <v>-28799.85</v>
+        <v>196178</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>-40860.06</v>
+        <v>-22099</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>-43469.7</v>
+        <v>60422</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>-44717.18</v>
+        <v>142740</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>-157846.79</v>
+        <v>377241</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>-45826.16</v>
+        <v>86914</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>-48032.26</v>
+        <v>77318</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>-44122.04</v>
+        <v>50378</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>-32882.26</v>
+        <v>137811</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>-170862.72</v>
+        <v>352421</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>-49982.21</v>
+        <v>170749</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>-56717.4</v>
+        <v>123524</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -19826,78 +19996,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>-708.27</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>-909.66</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>7831.54</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>-1614.01</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>2673.88</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>7981.75</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>-1151.16</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>12275.54</v>
-      </c>
-      <c r="N91" s="18" t="n">
-        <v>-1121.81</v>
-      </c>
-      <c r="O91" s="18" t="n">
-        <v>-4803.11</v>
-      </c>
-      <c r="P91" s="34" t="n">
-        <v>5199.46</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
+      <c r="P91" s="9" t="n"/>
       <c r="Q91" s="18" t="n">
-        <v>-3507.54</v>
+        <v>147113</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>-2602.74</v>
+        <v>-79298</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>6211.84</v>
+        <v>76480</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-2582.08</v>
+        <v>87226</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>-2480.52</v>
+        <v>231521</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>-2878.11</v>
+        <v>100622</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>-4028.71</v>
+        <v>189793</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>11377.47</v>
+        <v>103540</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>-12005.01</v>
+        <v>84738</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>-7534.36</v>
+        <v>478693</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>-1365.14</v>
+        <v>89671</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>12043.24</v>
+        <v>75007</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -19919,78 +20058,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>44786.95</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>-13993.74</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>222684.82</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>-127443.01</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>6726.06</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>87974.13</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>59136.81</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>-34385.63</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>289746.99</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>-117791.82</v>
-      </c>
-      <c r="P92" s="34" t="n">
-        <v>196706.35</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
       <c r="Q92" s="18" t="n">
-        <v>-147211.19</v>
+        <v>84015</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>-101940.75</v>
+        <v>34744</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>-487427.7</v>
+        <v>-94289</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>-373558.26</v>
+        <v>219930</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>-1110137.9</v>
+        <v>244400</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>-75810.35000000001</v>
+        <v>29834</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>-172152.81</v>
+        <v>146180</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>-336567.53</v>
+        <v>-30542</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>-864341.5600000001</v>
+        <v>-8947</v>
       </c>
       <c r="Z92" s="34" t="n">
-        <v>-1448872.25</v>
+        <v>136525</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>-303222.3</v>
+        <v>248259</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>-271440.3</v>
+        <v>40822</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -20012,78 +20120,47 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>43708.47</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>134627.27</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>-13498.7</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>-133723.18</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>-117185.87</v>
-      </c>
-      <c r="K93" s="34" t="n">
-        <v>-129780.48</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>325443.03</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>1314513.81</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>-154120.54</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>1399356.47</v>
-      </c>
-      <c r="P93" s="34" t="n">
-        <v>2885192.77</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
       <c r="Q93" s="18" t="n">
-        <v>1160125.54</v>
+        <v>78497</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>779253.24</v>
+        <v>57386</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>672194.24</v>
+        <v>-30504</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>191428.06</v>
+        <v>150785</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>2803001.08</v>
+        <v>256164</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>237800.98</v>
+        <v>12719</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>-377324.57</v>
+        <v>303104</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>61631.06</v>
+        <v>-199276</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>407710.37</v>
+        <v>-34343</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>329817.84</v>
+        <v>82204</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>353480.5</v>
+        <v>146145</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>-160614.05</v>
+        <v>49400</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -20105,70 +20182,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>107250.23</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>201791.78</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>53934.47</v>
-      </c>
       <c r="K94" s="9" t="n"/>
-      <c r="L94" s="18" t="n">
-        <v>424426.52</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>495573.48</v>
-      </c>
-      <c r="N94" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="O94" s="18" t="n">
-        <v>40138.54</v>
-      </c>
-      <c r="P94" s="34" t="n">
-        <v>960148.54</v>
-      </c>
+      <c r="P94" s="9" t="n"/>
       <c r="Q94" s="18" t="n">
-        <v>1207199.91</v>
+        <v>-16355</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>802270.8100000001</v>
+        <v>-26309</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>500018.42</v>
+        <v>-32646</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>20986.31</v>
+        <v>-32931</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>2530475.45</v>
+        <v>-108241</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>146738.1</v>
+        <v>-33526</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>9862.73</v>
+        <v>-35286</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>425966.24</v>
+        <v>-40354</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>98005.37</v>
+        <v>-10728</v>
       </c>
       <c r="Z94" s="34" t="n">
-        <v>680572.4399999999</v>
+        <v>-119894</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>272085.21</v>
+        <v>-46344</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>226289.15</v>
+        <v>-39585</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -20190,73 +20244,28 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>0</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>8348.75</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>8348.74</v>
-      </c>
-      <c r="K95" s="34" t="n">
-        <v>16701.52</v>
-      </c>
-      <c r="L95" s="18" t="n">
-        <v>8418.639999999999</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>8414.610000000001</v>
-      </c>
-      <c r="N95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="18" t="n">
-        <v>19036.3</v>
-      </c>
-      <c r="P95" s="34" t="n">
-        <v>35869.55</v>
-      </c>
-      <c r="Q95" s="18" t="n">
-        <v>10643.51</v>
-      </c>
-      <c r="R95" s="18" t="n">
-        <v>10639.48</v>
-      </c>
-      <c r="S95" s="18" t="n">
-        <v>10639.48</v>
-      </c>
-      <c r="T95" s="18" t="n">
-        <v>10639.48</v>
-      </c>
-      <c r="U95" s="34" t="n">
-        <v>42561.95</v>
-      </c>
-      <c r="V95" s="18" t="n">
-        <v>10788.93</v>
-      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="P95" s="9" t="n"/>
+      <c r="U95" s="9" t="n"/>
       <c r="W95" s="18" t="n">
-        <v>11004.89</v>
+        <v>157782</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>10564.9</v>
+        <v>-71331</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>-9779</v>
       </c>
       <c r="Z95" s="9" t="n"/>
       <c r="AA95" s="18" t="n">
-        <v>10760.66</v>
+        <v>1318</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>10756.64</v>
+        <v>3864</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -20278,78 +20287,28 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>4788.95</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="G96" s="18" t="n">
-        <v>4815.98</v>
-      </c>
-      <c r="H96" s="18" t="n">
-        <v>5794.73</v>
-      </c>
-      <c r="I96" s="18" t="n">
-        <v>5954.99</v>
-      </c>
-      <c r="J96" s="18" t="n">
-        <v>6019.43</v>
-      </c>
-      <c r="K96" s="34" t="n">
-        <v>22585.13</v>
-      </c>
-      <c r="L96" s="18" t="n">
-        <v>5415.34</v>
-      </c>
-      <c r="M96" s="18" t="n">
-        <v>6394.35</v>
-      </c>
-      <c r="N96" s="18" t="n">
-        <v>8610.940000000001</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>8840.51</v>
-      </c>
-      <c r="P96" s="34" t="n">
-        <v>29261.14</v>
-      </c>
-      <c r="Q96" s="18" t="n">
-        <v>8851.950000000001</v>
-      </c>
-      <c r="R96" s="18" t="n">
-        <v>9613.83</v>
-      </c>
-      <c r="S96" s="18" t="n">
-        <v>10737.63</v>
-      </c>
-      <c r="T96" s="18" t="n">
-        <v>10596.94</v>
-      </c>
-      <c r="U96" s="34" t="n">
-        <v>39800.35</v>
-      </c>
-      <c r="V96" s="18" t="n">
-        <v>9871.09</v>
-      </c>
+      <c r="K96" s="9" t="n"/>
+      <c r="P96" s="9" t="n"/>
+      <c r="U96" s="9" t="n"/>
       <c r="W96" s="18" t="n">
-        <v>10540.34</v>
+        <v>-14573</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>9900.98</v>
+        <v>1014</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>11764.92</v>
-      </c>
-      <c r="Z96" s="34" t="n">
-        <v>42077.33</v>
-      </c>
+        <v>9075</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
       <c r="AA96" s="18" t="n">
-        <v>10527.75</v>
+        <v>166856</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>11370.94</v>
+        <v>87408</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -20371,78 +20330,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>116861.35</v>
+        <v>28365.93</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>-605192.28</v>
+        <v>-725825.8100000001</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>-69852.37</v>
+        <v>-279038.48</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>-439221.66</v>
+        <v>-178055.47</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>7027.33</v>
+        <v>117487.13</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>-1107238.98</v>
+        <v>-1065432.63</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>-391766.88</v>
+        <v>-776346.72</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1298479.44</v>
+        <v>18351.27</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>-590422.9</v>
+        <v>-726049.36</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>826454.14</v>
+        <v>-455110.5</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>1142743.8</v>
+        <v>-1939155.31</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>-151530.54</v>
+        <v>-1164444.89</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>174817.77</v>
+        <v>-502494.72</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>-798162.4399999999</v>
+        <v>-982928.98</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>-436836.08</v>
+        <v>-254705.88</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>-1211711.29</v>
+        <v>-2904574.47</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>384403.83</v>
+        <v>222413.2</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>75995.91</v>
+        <v>625473.29</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>-615094.4</v>
+        <v>-340157.92</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>350311.83</v>
+        <v>806943.01</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>195617.17</v>
+        <v>1314671.58</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>272254.48</v>
+        <v>221996.29</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>386159.94</v>
+        <v>818214.29</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -20464,78 +20423,70 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E98" s="18" t="n">
-        <v>116393.84</v>
+        <v>0</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="18" t="n">
-        <v>1174446.61</v>
+        <v>570.89</v>
       </c>
       <c r="H98" s="18" t="n">
-        <v>-68383.92999999999</v>
+        <v>14.85</v>
       </c>
       <c r="I98" s="18" t="n">
-        <v>-421876.96</v>
+        <v>0</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>-24464.37</v>
+        <v>0</v>
       </c>
       <c r="K98" s="34" t="n">
-        <v>659721.35</v>
+        <v>585.74</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>270117.31</v>
+        <v>950</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>1294373.07</v>
+        <v>73.25</v>
       </c>
       <c r="N98" s="18" t="n">
-        <v>-585872.04</v>
+        <v>0</v>
       </c>
       <c r="O98" s="18" t="n">
-        <v>820689.41</v>
+        <v>0</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>1799307.75</v>
+        <v>1023.25</v>
       </c>
       <c r="Q98" s="18" t="n">
-        <v>1648803.91</v>
+        <v>874</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>175952.84</v>
+        <v>180.29</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>-808143.4</v>
+        <v>23.91</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>-428353.61</v>
+        <v>-23.91</v>
       </c>
       <c r="U98" s="34" t="n">
-        <v>588259.74</v>
-      </c>
-      <c r="V98" s="18" t="n">
-        <v>973241.3100000001</v>
-      </c>
-      <c r="W98" s="18" t="n">
-        <v>64407.2</v>
+        <v>1054.29</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>-608147.95</v>
+        <v>3.19</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>348970.6</v>
-      </c>
-      <c r="Z98" s="34" t="n">
-        <v>778471.16</v>
-      </c>
+        <v>6.75</v>
+      </c>
+      <c r="Z98" s="9" t="n"/>
       <c r="AA98" s="18" t="n">
-        <v>1058396.68</v>
+        <v>121.28</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>387807.72</v>
+        <v>51.64</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -20557,53 +20508,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>7088.08</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>456.88</v>
-      </c>
-      <c r="K99" s="9" t="n"/>
+        <v>8233.24</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>20154.3</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>8731.629999999999</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>10813.24</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>47932.41</v>
+      </c>
       <c r="L99" s="18" t="n">
-        <v>77.48999999999999</v>
-      </c>
-      <c r="P99" s="9" t="n"/>
+        <v>11840.48</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>2092.89</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>15650.8</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>23849.44</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>53433.61</v>
+      </c>
       <c r="Q99" s="18" t="n">
-        <v>380.26</v>
+        <v>17990.78</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>375.79</v>
+        <v>16925.54</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>97.14</v>
+        <v>14328.67</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>517.42</v>
+        <v>9180.48</v>
       </c>
       <c r="U99" s="34" t="n">
-        <v>1370.61</v>
+        <v>58425.47</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>462.54</v>
+        <v>7649.97</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>1314.87</v>
+        <v>8719.76</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>685.1</v>
+        <v>4860.76</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>1021.33</v>
+        <v>8226.370000000001</v>
       </c>
       <c r="Z99" s="34" t="n">
-        <v>3483.84</v>
+        <v>29456.86</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>198.45</v>
+        <v>22274.1</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>638.91</v>
+        <v>8554.870000000001</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -20625,53 +20601,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
-        </is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>-17785.61</v>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>-12600.45</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>-17975.27</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>-22239.45</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>-24468.02</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>-77283.19</v>
+      </c>
       <c r="L100" s="18" t="n">
-        <v>23203.62</v>
+        <v>-38266.93</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>1163614.22</v>
+        <v>-42682.63</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>139687.01</v>
+        <v>-28547.14</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>87565.17999999999</v>
+        <v>-32046.25</v>
       </c>
       <c r="P100" s="34" t="n">
-        <v>1414070.03</v>
+        <v>-141542.95</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>22145.89</v>
+        <v>-28799.85</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>-40860.06</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>7010.35</v>
-      </c>
-      <c r="U100" s="9" t="n"/>
+        <v>-43469.7</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>-44717.18</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>-157846.79</v>
+      </c>
       <c r="V100" s="18" t="n">
-        <v>150000</v>
+        <v>-45826.16</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>500000</v>
+        <v>-48032.26</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>520000</v>
+        <v>-44122.04</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>100000</v>
+        <v>-32882.26</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>1270000</v>
+        <v>-170862.72</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>250000</v>
+        <v>-49982.21</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>310000</v>
+        <v>-56717.4</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -20693,47 +20694,78 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
+          <t>법인세납부(CF)</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>-708.27</v>
       </c>
       <c r="F101" s="9" t="n"/>
-      <c r="K101" s="9" t="n"/>
-      <c r="P101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>-909.66</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>7831.54</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>-1614.01</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>2673.88</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>7981.75</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>-1151.16</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>12275.54</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>-1121.81</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>-4803.11</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>5199.46</v>
+      </c>
       <c r="Q101" s="18" t="n">
-        <v>135373.66</v>
+        <v>-3507.54</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>51546.11</v>
+        <v>-2602.74</v>
       </c>
       <c r="S101" s="18" t="n">
-        <v>64147.03</v>
+        <v>6211.84</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>122573.42</v>
+        <v>-2582.08</v>
       </c>
       <c r="U101" s="34" t="n">
-        <v>373640.22</v>
+        <v>-2480.52</v>
       </c>
       <c r="V101" s="18" t="n">
-        <v>92830.66</v>
+        <v>-2878.11</v>
       </c>
       <c r="W101" s="18" t="n">
-        <v>65595.34</v>
+        <v>-4028.71</v>
       </c>
       <c r="X101" s="18" t="n">
-        <v>233233.46</v>
+        <v>11377.47</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>317960.24</v>
+        <v>-12005.01</v>
       </c>
       <c r="Z101" s="34" t="n">
-        <v>709619.7</v>
+        <v>-7534.36</v>
       </c>
       <c r="AA101" s="18" t="n">
-        <v>106566.99</v>
+        <v>-1365.14</v>
       </c>
       <c r="AB101" s="19" t="n">
-        <v>197933.37</v>
+        <v>12043.24</v>
       </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -20755,47 +20787,78 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
+          <t>투자활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>44786.95</v>
       </c>
       <c r="F102" s="9" t="n"/>
-      <c r="K102" s="9" t="n"/>
-      <c r="P102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>-13993.74</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>222684.82</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>-127443.01</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>6726.06</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>87974.13</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>59136.81</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>-34385.63</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>289746.99</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>-117791.82</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>196706.35</v>
+      </c>
       <c r="Q102" s="18" t="n">
-        <v>136070.21</v>
+        <v>-147211.19</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>52537.99</v>
+        <v>-101940.75</v>
       </c>
       <c r="S102" s="18" t="n">
-        <v>66193.41</v>
+        <v>-487427.7</v>
       </c>
       <c r="T102" s="18" t="n">
-        <v>124582.48</v>
+        <v>-373558.26</v>
       </c>
       <c r="U102" s="34" t="n">
-        <v>379384.09</v>
+        <v>-1110137.9</v>
       </c>
       <c r="V102" s="18" t="n">
-        <v>95435.87</v>
+        <v>-75810.35000000001</v>
       </c>
       <c r="W102" s="18" t="n">
-        <v>66589.32000000001</v>
+        <v>-172152.81</v>
       </c>
       <c r="X102" s="18" t="n">
-        <v>235140.73</v>
+        <v>-336567.53</v>
       </c>
       <c r="Y102" s="18" t="n">
-        <v>319456.33</v>
+        <v>-864341.5600000001</v>
       </c>
       <c r="Z102" s="34" t="n">
-        <v>716622.25</v>
+        <v>-1448872.25</v>
       </c>
       <c r="AA102" s="18" t="n">
-        <v>107432.08</v>
+        <v>-303222.3</v>
       </c>
       <c r="AB102" s="19" t="n">
-        <v>198433.94</v>
+        <v>-271440.3</v>
       </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -20817,47 +20880,78 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>43708.47</v>
       </c>
       <c r="F103" s="9" t="n"/>
-      <c r="K103" s="9" t="n"/>
-      <c r="P103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>134627.27</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>-13498.7</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>-133723.18</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>-117185.87</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>-129780.48</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>325443.03</v>
+      </c>
+      <c r="M103" s="18" t="n">
+        <v>1314513.81</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>-154120.54</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>1399356.47</v>
+      </c>
+      <c r="P103" s="34" t="n">
+        <v>2885192.77</v>
+      </c>
       <c r="Q103" s="18" t="n">
-        <v>696.55</v>
+        <v>1160125.54</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>991.88</v>
+        <v>779253.24</v>
       </c>
       <c r="S103" s="18" t="n">
-        <v>2046.38</v>
+        <v>672194.24</v>
       </c>
       <c r="T103" s="18" t="n">
-        <v>2009.06</v>
+        <v>191428.06</v>
       </c>
       <c r="U103" s="34" t="n">
-        <v>5743.87</v>
+        <v>2803001.08</v>
       </c>
       <c r="V103" s="18" t="n">
-        <v>2605.21</v>
+        <v>237800.98</v>
       </c>
       <c r="W103" s="18" t="n">
-        <v>993.98</v>
+        <v>-377324.57</v>
       </c>
       <c r="X103" s="18" t="n">
-        <v>1907.27</v>
+        <v>61631.06</v>
       </c>
       <c r="Y103" s="18" t="n">
-        <v>1496.09</v>
+        <v>407710.37</v>
       </c>
       <c r="Z103" s="34" t="n">
-        <v>7002.55</v>
+        <v>329817.84</v>
       </c>
       <c r="AA103" s="18" t="n">
-        <v>865.09</v>
+        <v>353480.5</v>
       </c>
       <c r="AB103" s="19" t="n">
-        <v>500.57</v>
+        <v>-160614.05</v>
       </c>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
@@ -20879,35 +20973,71 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>107250.23</v>
       </c>
       <c r="F104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>201791.78</v>
+      </c>
+      <c r="H104" s="18" t="n">
+        <v>53934.47</v>
+      </c>
       <c r="K104" s="9" t="n"/>
-      <c r="P104" s="9" t="n"/>
+      <c r="L104" s="18" t="n">
+        <v>424426.52</v>
+      </c>
+      <c r="M104" s="18" t="n">
+        <v>495573.48</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O104" s="18" t="n">
+        <v>40138.54</v>
+      </c>
+      <c r="P104" s="34" t="n">
+        <v>960148.54</v>
+      </c>
+      <c r="Q104" s="18" t="n">
+        <v>1207199.91</v>
+      </c>
+      <c r="R104" s="18" t="n">
+        <v>802270.8100000001</v>
+      </c>
       <c r="S104" s="18" t="n">
-        <v>30.8</v>
+        <v>500018.42</v>
       </c>
       <c r="T104" s="18" t="n">
-        <v>654.55</v>
-      </c>
-      <c r="U104" s="9" t="n"/>
+        <v>20986.31</v>
+      </c>
+      <c r="U104" s="34" t="n">
+        <v>2530475.45</v>
+      </c>
       <c r="V104" s="18" t="n">
-        <v>13.09</v>
+        <v>146738.1</v>
       </c>
       <c r="W104" s="18" t="n">
-        <v>0</v>
+        <v>9862.73</v>
       </c>
       <c r="X104" s="18" t="n">
-        <v>0</v>
+        <v>425966.24</v>
       </c>
       <c r="Y104" s="18" t="n">
-        <v>19810.38</v>
+        <v>98005.37</v>
       </c>
       <c r="Z104" s="34" t="n">
-        <v>19823.47</v>
-      </c>
-      <c r="AB104" s="5" t="n"/>
+        <v>680572.4399999999</v>
+      </c>
+      <c r="AA104" s="18" t="n">
+        <v>272085.21</v>
+      </c>
+      <c r="AB104" s="19" t="n">
+        <v>226289.15</v>
+      </c>
       <c r="AC104" s="10" t="n"/>
       <c r="AD104" s="10" t="n"/>
       <c r="AE104" s="11" t="n"/>
@@ -20928,25 +21058,73 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
-        </is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="9" t="n"/>
-      <c r="K105" s="9" t="n"/>
-      <c r="P105" s="9" t="n"/>
+      <c r="G105" s="18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>8348.75</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>8348.74</v>
+      </c>
+      <c r="K105" s="34" t="n">
+        <v>16701.52</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>8418.639999999999</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>8414.610000000001</v>
+      </c>
+      <c r="N105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="18" t="n">
+        <v>19036.3</v>
+      </c>
+      <c r="P105" s="34" t="n">
+        <v>35869.55</v>
+      </c>
+      <c r="Q105" s="18" t="n">
+        <v>10643.51</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>10639.48</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>10639.48</v>
+      </c>
       <c r="T105" s="18" t="n">
-        <v>68020</v>
-      </c>
-      <c r="U105" s="9" t="n"/>
-      <c r="Y105" s="18" t="n">
-        <v>435953.69</v>
+        <v>10639.48</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>42561.95</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>10788.93</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>11004.89</v>
+      </c>
+      <c r="X105" s="18" t="n">
+        <v>10564.9</v>
       </c>
       <c r="Z105" s="9" t="n"/>
       <c r="AA105" s="18" t="n">
-        <v>500</v>
+        <v>10760.66</v>
       </c>
       <c r="AB105" s="19" t="n">
-        <v>20869.55</v>
+        <v>10756.64</v>
       </c>
       <c r="AC105" s="10" t="n"/>
       <c r="AD105" s="10" t="n"/>
@@ -20968,32 +21146,79 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>사채의증가</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>4788.95</v>
       </c>
       <c r="F106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
-      <c r="P106" s="9" t="n"/>
-      <c r="U106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>4815.98</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>5794.73</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>5954.99</v>
+      </c>
+      <c r="J106" s="18" t="n">
+        <v>6019.43</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>22585.13</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>5415.34</v>
+      </c>
+      <c r="M106" s="18" t="n">
+        <v>6394.35</v>
+      </c>
+      <c r="N106" s="18" t="n">
+        <v>8610.940000000001</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>8840.51</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>29261.14</v>
+      </c>
+      <c r="Q106" s="18" t="n">
+        <v>8851.950000000001</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>9613.83</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>10737.63</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>10596.94</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>39800.35</v>
+      </c>
       <c r="V106" s="18" t="n">
-        <v>161343.38</v>
+        <v>9871.09</v>
       </c>
       <c r="W106" s="18" t="n">
-        <v>0</v>
+        <v>10540.34</v>
       </c>
       <c r="X106" s="18" t="n">
-        <v>119552.54</v>
+        <v>9900.98</v>
       </c>
       <c r="Y106" s="18" t="n">
-        <v>0</v>
+        <v>11764.92</v>
       </c>
       <c r="Z106" s="34" t="n">
-        <v>280895.92</v>
+        <v>42077.33</v>
       </c>
       <c r="AA106" s="18" t="n">
-        <v>338241.83</v>
-      </c>
-      <c r="AB106" s="5" t="n"/>
+        <v>10527.75</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>11370.94</v>
+      </c>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
       <c r="AE106" s="11" t="n"/>
@@ -21014,19 +21239,78 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>116861.35</v>
       </c>
       <c r="F107" s="9" t="n"/>
-      <c r="K107" s="9" t="n"/>
-      <c r="P107" s="9" t="n"/>
-      <c r="U107" s="9" t="n"/>
-      <c r="Z107" s="9" t="n"/>
+      <c r="G107" s="18" t="n">
+        <v>-605192.28</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>-69852.37</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>-439221.66</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>7027.33</v>
+      </c>
+      <c r="K107" s="34" t="n">
+        <v>-1107238.98</v>
+      </c>
+      <c r="L107" s="18" t="n">
+        <v>-391766.88</v>
+      </c>
+      <c r="M107" s="18" t="n">
+        <v>1298479.44</v>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>-590422.9</v>
+      </c>
+      <c r="O107" s="18" t="n">
+        <v>826454.14</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>1142743.8</v>
+      </c>
+      <c r="Q107" s="18" t="n">
+        <v>-151530.54</v>
+      </c>
+      <c r="R107" s="18" t="n">
+        <v>174817.77</v>
+      </c>
+      <c r="S107" s="18" t="n">
+        <v>-798162.4399999999</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>-436836.08</v>
+      </c>
+      <c r="U107" s="34" t="n">
+        <v>-1211711.29</v>
+      </c>
+      <c r="V107" s="18" t="n">
+        <v>384403.83</v>
+      </c>
+      <c r="W107" s="18" t="n">
+        <v>75995.91</v>
+      </c>
+      <c r="X107" s="18" t="n">
+        <v>-615094.4</v>
+      </c>
+      <c r="Y107" s="18" t="n">
+        <v>350311.83</v>
+      </c>
+      <c r="Z107" s="34" t="n">
+        <v>195617.17</v>
+      </c>
       <c r="AA107" s="18" t="n">
-        <v>4908.63</v>
+        <v>272254.48</v>
       </c>
       <c r="AB107" s="19" t="n">
-        <v>203.86</v>
+        <v>386159.94</v>
       </c>
       <c r="AC107" s="10" t="n"/>
       <c r="AD107" s="10" t="n"/>
@@ -21041,6 +21325,590 @@
       <c r="AM107" s="10" t="n"/>
       <c r="AN107" s="10" t="n"/>
       <c r="AO107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>116393.84</v>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="18" t="n">
+        <v>1174446.61</v>
+      </c>
+      <c r="H108" s="18" t="n">
+        <v>-68383.92999999999</v>
+      </c>
+      <c r="I108" s="18" t="n">
+        <v>-421876.96</v>
+      </c>
+      <c r="J108" s="18" t="n">
+        <v>-24464.37</v>
+      </c>
+      <c r="K108" s="34" t="n">
+        <v>659721.35</v>
+      </c>
+      <c r="L108" s="18" t="n">
+        <v>270117.31</v>
+      </c>
+      <c r="M108" s="18" t="n">
+        <v>1294373.07</v>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>-585872.04</v>
+      </c>
+      <c r="O108" s="18" t="n">
+        <v>820689.41</v>
+      </c>
+      <c r="P108" s="34" t="n">
+        <v>1799307.75</v>
+      </c>
+      <c r="Q108" s="18" t="n">
+        <v>1648803.91</v>
+      </c>
+      <c r="R108" s="18" t="n">
+        <v>175952.84</v>
+      </c>
+      <c r="S108" s="18" t="n">
+        <v>-808143.4</v>
+      </c>
+      <c r="T108" s="18" t="n">
+        <v>-428353.61</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>588259.74</v>
+      </c>
+      <c r="V108" s="18" t="n">
+        <v>973241.3100000001</v>
+      </c>
+      <c r="W108" s="18" t="n">
+        <v>64407.2</v>
+      </c>
+      <c r="X108" s="18" t="n">
+        <v>-608147.95</v>
+      </c>
+      <c r="Y108" s="18" t="n">
+        <v>348970.6</v>
+      </c>
+      <c r="Z108" s="34" t="n">
+        <v>778471.16</v>
+      </c>
+      <c r="AA108" s="18" t="n">
+        <v>1058396.68</v>
+      </c>
+      <c r="AB108" s="19" t="n">
+        <v>387807.72</v>
+      </c>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="10" t="n"/>
+      <c r="AL108" s="10" t="n"/>
+      <c r="AM108" s="10" t="n"/>
+      <c r="AN108" s="10" t="n"/>
+      <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="18" t="n">
+        <v>456.88</v>
+      </c>
+      <c r="K109" s="9" t="n"/>
+      <c r="L109" s="18" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="P109" s="9" t="n"/>
+      <c r="Q109" s="18" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="R109" s="18" t="n">
+        <v>375.79</v>
+      </c>
+      <c r="S109" s="18" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="T109" s="18" t="n">
+        <v>517.42</v>
+      </c>
+      <c r="U109" s="34" t="n">
+        <v>1370.61</v>
+      </c>
+      <c r="V109" s="18" t="n">
+        <v>462.54</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>1314.87</v>
+      </c>
+      <c r="X109" s="18" t="n">
+        <v>685.1</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>1021.33</v>
+      </c>
+      <c r="Z109" s="34" t="n">
+        <v>3483.84</v>
+      </c>
+      <c r="AA109" s="18" t="n">
+        <v>198.45</v>
+      </c>
+      <c r="AB109" s="19" t="n">
+        <v>638.91</v>
+      </c>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="n"/>
+      <c r="K110" s="9" t="n"/>
+      <c r="L110" s="18" t="n">
+        <v>23203.62</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>1163614.22</v>
+      </c>
+      <c r="N110" s="18" t="n">
+        <v>139687.01</v>
+      </c>
+      <c r="O110" s="18" t="n">
+        <v>87565.17999999999</v>
+      </c>
+      <c r="P110" s="34" t="n">
+        <v>1414070.03</v>
+      </c>
+      <c r="Q110" s="18" t="n">
+        <v>22145.89</v>
+      </c>
+      <c r="S110" s="18" t="n">
+        <v>7010.35</v>
+      </c>
+      <c r="U110" s="9" t="n"/>
+      <c r="V110" s="18" t="n">
+        <v>150000</v>
+      </c>
+      <c r="W110" s="18" t="n">
+        <v>500000</v>
+      </c>
+      <c r="X110" s="18" t="n">
+        <v>520000</v>
+      </c>
+      <c r="Y110" s="18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z110" s="34" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="AA110" s="18" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>310000</v>
+      </c>
+      <c r="AC110" s="10" t="n"/>
+      <c r="AD110" s="10" t="n"/>
+      <c r="AE110" s="11" t="n"/>
+      <c r="AF110" s="10" t="n"/>
+      <c r="AG110" s="10" t="n"/>
+      <c r="AH110" s="10" t="n"/>
+      <c r="AI110" s="10" t="n"/>
+      <c r="AJ110" s="11" t="n"/>
+      <c r="AK110" s="10" t="n"/>
+      <c r="AL110" s="10" t="n"/>
+      <c r="AM110" s="10" t="n"/>
+      <c r="AN110" s="10" t="n"/>
+      <c r="AO110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+      <c r="P111" s="9" t="n"/>
+      <c r="Q111" s="18" t="n">
+        <v>135373.66</v>
+      </c>
+      <c r="R111" s="18" t="n">
+        <v>51546.11</v>
+      </c>
+      <c r="S111" s="18" t="n">
+        <v>64147.03</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>122573.42</v>
+      </c>
+      <c r="U111" s="34" t="n">
+        <v>373640.22</v>
+      </c>
+      <c r="V111" s="18" t="n">
+        <v>92830.66</v>
+      </c>
+      <c r="W111" s="18" t="n">
+        <v>65595.34</v>
+      </c>
+      <c r="X111" s="18" t="n">
+        <v>233233.46</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>317960.24</v>
+      </c>
+      <c r="Z111" s="34" t="n">
+        <v>709619.7</v>
+      </c>
+      <c r="AA111" s="18" t="n">
+        <v>106566.99</v>
+      </c>
+      <c r="AB111" s="19" t="n">
+        <v>197933.37</v>
+      </c>
+      <c r="AC111" s="10" t="n"/>
+      <c r="AD111" s="10" t="n"/>
+      <c r="AE111" s="11" t="n"/>
+      <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="11" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+      <c r="P112" s="9" t="n"/>
+      <c r="Q112" s="18" t="n">
+        <v>136070.21</v>
+      </c>
+      <c r="R112" s="18" t="n">
+        <v>52537.99</v>
+      </c>
+      <c r="S112" s="18" t="n">
+        <v>66193.41</v>
+      </c>
+      <c r="T112" s="18" t="n">
+        <v>124582.48</v>
+      </c>
+      <c r="U112" s="34" t="n">
+        <v>379384.09</v>
+      </c>
+      <c r="V112" s="18" t="n">
+        <v>95435.87</v>
+      </c>
+      <c r="W112" s="18" t="n">
+        <v>66589.32000000001</v>
+      </c>
+      <c r="X112" s="18" t="n">
+        <v>235140.73</v>
+      </c>
+      <c r="Y112" s="18" t="n">
+        <v>319456.33</v>
+      </c>
+      <c r="Z112" s="34" t="n">
+        <v>716622.25</v>
+      </c>
+      <c r="AA112" s="18" t="n">
+        <v>107432.08</v>
+      </c>
+      <c r="AB112" s="19" t="n">
+        <v>198433.94</v>
+      </c>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="11" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="11" t="n"/>
+      <c r="AK112" s="10" t="n"/>
+      <c r="AL112" s="10" t="n"/>
+      <c r="AM112" s="10" t="n"/>
+      <c r="AN112" s="10" t="n"/>
+      <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
+      <c r="P113" s="9" t="n"/>
+      <c r="Q113" s="18" t="n">
+        <v>696.55</v>
+      </c>
+      <c r="R113" s="18" t="n">
+        <v>991.88</v>
+      </c>
+      <c r="S113" s="18" t="n">
+        <v>2046.38</v>
+      </c>
+      <c r="T113" s="18" t="n">
+        <v>2009.06</v>
+      </c>
+      <c r="U113" s="34" t="n">
+        <v>5743.87</v>
+      </c>
+      <c r="V113" s="18" t="n">
+        <v>2605.21</v>
+      </c>
+      <c r="W113" s="18" t="n">
+        <v>993.98</v>
+      </c>
+      <c r="X113" s="18" t="n">
+        <v>1907.27</v>
+      </c>
+      <c r="Y113" s="18" t="n">
+        <v>1496.09</v>
+      </c>
+      <c r="Z113" s="34" t="n">
+        <v>7002.55</v>
+      </c>
+      <c r="AA113" s="18" t="n">
+        <v>865.09</v>
+      </c>
+      <c r="AB113" s="19" t="n">
+        <v>500.57</v>
+      </c>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>무형자산의감소</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
+      <c r="P114" s="9" t="n"/>
+      <c r="S114" s="18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T114" s="18" t="n">
+        <v>654.55</v>
+      </c>
+      <c r="U114" s="9" t="n"/>
+      <c r="V114" s="18" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="W114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="18" t="n">
+        <v>19810.38</v>
+      </c>
+      <c r="Z114" s="34" t="n">
+        <v>19823.47</v>
+      </c>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="n"/>
+      <c r="K115" s="9" t="n"/>
+      <c r="P115" s="9" t="n"/>
+      <c r="T115" s="18" t="n">
+        <v>68020</v>
+      </c>
+      <c r="U115" s="9" t="n"/>
+      <c r="Y115" s="18" t="n">
+        <v>435953.69</v>
+      </c>
+      <c r="Z115" s="9" t="n"/>
+      <c r="AA115" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB115" s="19" t="n">
+        <v>20869.55</v>
+      </c>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
+      <c r="P116" s="9" t="n"/>
+      <c r="U116" s="9" t="n"/>
+      <c r="V116" s="18" t="n">
+        <v>161343.38</v>
+      </c>
+      <c r="W116" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="18" t="n">
+        <v>119552.54</v>
+      </c>
+      <c r="Y116" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="34" t="n">
+        <v>280895.92</v>
+      </c>
+      <c r="AA116" s="18" t="n">
+        <v>338241.83</v>
+      </c>
+      <c r="AB116" s="5" t="n"/>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="10" t="n"/>
+      <c r="AL116" s="10" t="n"/>
+      <c r="AM116" s="10" t="n"/>
+      <c r="AN116" s="10" t="n"/>
+      <c r="AO116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+      <c r="P117" s="9" t="n"/>
+      <c r="U117" s="9" t="n"/>
+      <c r="Z117" s="9" t="n"/>
+      <c r="AA117" s="18" t="n">
+        <v>4908.63</v>
+      </c>
+      <c r="AB117" s="19" t="n">
+        <v>203.86</v>
+      </c>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21301,7 +22169,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32643,25 +33511,58 @@
         <v/>
       </c>
       <c r="AA22" s="18" t="n"/>
-      <c r="AB22" s="19" t="n"/>
-      <c r="AC22" s="20" t="n"/>
-      <c r="AD22" s="20" t="n"/>
+      <c r="AB22" s="19">
+        <f>IFERROR(VLOOKUP($D22,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC22" s="20">
+        <f>IFERROR(AB22*(1+변수!AC33),"")</f>
+        <v/>
+      </c>
+      <c r="AD22" s="20">
+        <f>IFERROR(AC22*(1+변수!AD33),"")</f>
+        <v/>
+      </c>
       <c r="AE22" s="35">
         <f>AD22</f>
         <v/>
       </c>
-      <c r="AF22" s="20" t="n"/>
-      <c r="AG22" s="20" t="n"/>
-      <c r="AH22" s="20" t="n"/>
-      <c r="AI22" s="20" t="n"/>
+      <c r="AF22" s="20">
+        <f>IFERROR(AD22*(1+변수!AF33),"")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="20">
+        <f>IFERROR(AF22*(1+변수!AG33),"")</f>
+        <v/>
+      </c>
+      <c r="AH22" s="20">
+        <f>IFERROR(AG22*(1+변수!AH33),"")</f>
+        <v/>
+      </c>
+      <c r="AI22" s="20">
+        <f>IFERROR(AH22*(1+변수!AI33),"")</f>
+        <v/>
+      </c>
       <c r="AJ22" s="35">
         <f>AI22</f>
         <v/>
       </c>
-      <c r="AK22" s="20" t="n"/>
-      <c r="AL22" s="20" t="n"/>
-      <c r="AM22" s="20" t="n"/>
-      <c r="AN22" s="20" t="n"/>
+      <c r="AK22" s="20">
+        <f>IFERROR(AI22*(1+변수!AK33),"")</f>
+        <v/>
+      </c>
+      <c r="AL22" s="20">
+        <f>IFERROR(AK22*(1+변수!AL33),"")</f>
+        <v/>
+      </c>
+      <c r="AM22" s="20">
+        <f>IFERROR(AL22*(1+변수!AM33),"")</f>
+        <v/>
+      </c>
+      <c r="AN22" s="20">
+        <f>IFERROR(AM22*(1+변수!AN33),"")</f>
+        <v/>
+      </c>
       <c r="AO22" s="35">
         <f>AN22</f>
         <v/>
@@ -32759,25 +33660,58 @@
         <v/>
       </c>
       <c r="AA23" s="18" t="n"/>
-      <c r="AB23" s="19" t="n"/>
-      <c r="AC23" s="20" t="n"/>
-      <c r="AD23" s="20" t="n"/>
+      <c r="AB23" s="19">
+        <f>IFERROR(VLOOKUP($D23,BS연결,MATCH(AB$1,BS연결H,0),0)/100,"")</f>
+        <v/>
+      </c>
+      <c r="AC23" s="20">
+        <f>IFERROR(AB23*(1+변수!AC34),"")</f>
+        <v/>
+      </c>
+      <c r="AD23" s="20">
+        <f>IFERROR(AC23*(1+변수!AD34),"")</f>
+        <v/>
+      </c>
       <c r="AE23" s="35">
         <f>AD23</f>
         <v/>
       </c>
-      <c r="AF23" s="20" t="n"/>
-      <c r="AG23" s="20" t="n"/>
-      <c r="AH23" s="20" t="n"/>
-      <c r="AI23" s="20" t="n"/>
+      <c r="AF23" s="20">
+        <f>IFERROR(AD23*(1+변수!AF34),"")</f>
+        <v/>
+      </c>
+      <c r="AG23" s="20">
+        <f>IFERROR(AF23*(1+변수!AG34),"")</f>
+        <v/>
+      </c>
+      <c r="AH23" s="20">
+        <f>IFERROR(AG23*(1+변수!AH34),"")</f>
+        <v/>
+      </c>
+      <c r="AI23" s="20">
+        <f>IFERROR(AH23*(1+변수!AI34),"")</f>
+        <v/>
+      </c>
       <c r="AJ23" s="35">
         <f>AI23</f>
         <v/>
       </c>
-      <c r="AK23" s="20" t="n"/>
-      <c r="AL23" s="20" t="n"/>
-      <c r="AM23" s="20" t="n"/>
-      <c r="AN23" s="20" t="n"/>
+      <c r="AK23" s="20">
+        <f>IFERROR(AI23*(1+변수!AK34),"")</f>
+        <v/>
+      </c>
+      <c r="AL23" s="20">
+        <f>IFERROR(AK23*(1+변수!AL34),"")</f>
+        <v/>
+      </c>
+      <c r="AM23" s="20">
+        <f>IFERROR(AL23*(1+변수!AM34),"")</f>
+        <v/>
+      </c>
+      <c r="AN23" s="20">
+        <f>IFERROR(AM23*(1+변수!AN34),"")</f>
+        <v/>
+      </c>
       <c r="AO23" s="35">
         <f>AN23</f>
         <v/>
@@ -37456,12 +38390,12 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>cohort:④호황</t>
+          <t>cohort:③중마진</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>코호트 ④호황</t>
+          <t>코호트 ③중마진</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
@@ -37489,112 +38423,31 @@
         <v>61.512</v>
       </c>
       <c r="M14" s="26" t="n">
-        <v>71.649</v>
+        <v>62.195</v>
       </c>
       <c r="N14" s="26" t="n">
-        <v>106.364</v>
+        <v>62.879</v>
       </c>
       <c r="O14" s="26" t="n">
-        <v>106.364</v>
+        <v>62.879</v>
       </c>
       <c r="P14" s="26" t="n">
-        <v>104.051</v>
+        <v>61.512</v>
       </c>
       <c r="Q14" s="26" t="n">
-        <v>105.207</v>
+        <v>62.195</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>106.364</v>
+        <v>62.879</v>
       </c>
       <c r="S14" s="26" t="n">
-        <v>106.364</v>
+        <v>62.879</v>
       </c>
       <c r="T14" s="26" t="n">
-        <v>104.051</v>
+        <v>61.512</v>
       </c>
       <c r="U14" s="26" t="n">
-        <v>47.113</v>
-      </c>
-      <c r="V14" s="26" t="n">
-        <v>43.485</v>
-      </c>
-      <c r="W14" s="26" t="n">
-        <v>43.485</v>
-      </c>
-      <c r="X14" s="26" t="n">
-        <v>56.49</v>
-      </c>
-      <c r="Y14" s="26" t="n">
-        <v>76.26000000000001</v>
-      </c>
-      <c r="Z14" s="26" t="n">
-        <v>130.454</v>
-      </c>
-      <c r="AA14" s="26" t="n">
-        <v>130.454</v>
-      </c>
-      <c r="AB14" s="26" t="n">
-        <v>127.618</v>
-      </c>
-      <c r="AC14" s="26" t="n">
-        <v>129.036</v>
-      </c>
-      <c r="AD14" s="26" t="n">
-        <v>130.454</v>
-      </c>
-      <c r="AE14" s="26" t="n">
-        <v>156.959</v>
-      </c>
-      <c r="AF14" s="26" t="n">
-        <v>209.876</v>
-      </c>
-      <c r="AG14" s="26" t="n">
-        <v>242.477</v>
-      </c>
-      <c r="AH14" s="26" t="n">
-        <v>322.495</v>
-      </c>
-      <c r="AI14" s="26" t="n">
-        <v>361.212</v>
-      </c>
-      <c r="AJ14" s="26" t="n">
-        <v>298.501</v>
-      </c>
-      <c r="AK14" s="26" t="n">
-        <v>284.613</v>
-      </c>
-      <c r="AL14" s="26" t="n">
-        <v>287.741</v>
-      </c>
-      <c r="AM14" s="26" t="n">
-        <v>287.741</v>
-      </c>
-      <c r="AN14" s="26" t="n">
-        <v>284.613</v>
-      </c>
-      <c r="AO14" s="26" t="n">
-        <v>284.613</v>
-      </c>
-      <c r="AP14" s="26" t="n">
-        <v>287.741</v>
-      </c>
-      <c r="AQ14" s="26" t="n">
-        <v>273.086</v>
-      </c>
-      <c r="AR14" s="26" t="n">
-        <v>218.258</v>
-      </c>
-      <c r="AS14" s="26" t="n">
-        <v>200.557</v>
-      </c>
-      <c r="AT14" s="26" t="n">
-        <v>162.322</v>
-      </c>
-      <c r="AU14" s="26" t="n">
-        <v>72.88500000000001</v>
-      </c>
-      <c r="AV14" s="26" t="n">
-        <v>40.18</v>
+        <v>4.101</v>
       </c>
       <c r="BF14" s="26" t="n">
         <v>180.435</v>
@@ -37603,388 +38456,421 @@
         <v>250.148</v>
       </c>
       <c r="BH14" s="26" t="n">
-        <v>345.889</v>
+        <v>249.465</v>
       </c>
       <c r="BI14" s="26" t="n">
-        <v>421.986</v>
+        <v>249.465</v>
       </c>
       <c r="BJ14" s="26" t="n">
-        <v>238.134</v>
-      </c>
-      <c r="BK14" s="26" t="n">
-        <v>393.658</v>
-      </c>
-      <c r="BL14" s="26" t="n">
-        <v>544.067</v>
-      </c>
-      <c r="BM14" s="26" t="n">
-        <v>1136.06</v>
-      </c>
-      <c r="BN14" s="26" t="n">
-        <v>1158.596</v>
-      </c>
-      <c r="BO14" s="26" t="n">
-        <v>1130.053</v>
-      </c>
-      <c r="BP14" s="26" t="n">
-        <v>654.022</v>
-      </c>
-      <c r="BQ14" s="26" t="n">
-        <v>40.18</v>
+        <v>65.613</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>cohort:등급없음</t>
+          <t>cohort:④호황</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>코호트 등급없음</t>
-        </is>
+          <t>코호트 ④호황</t>
+        </is>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>9.452999999999999</v>
+      </c>
+      <c r="N15" s="26" t="n">
+        <v>43.485</v>
+      </c>
+      <c r="O15" s="26" t="n">
+        <v>43.485</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>23.4</v>
+        <v>42.539</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>36.092</v>
+        <v>43.012</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="S15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="T15" s="26" t="n">
-        <v>35.695</v>
+        <v>42.539</v>
       </c>
       <c r="U15" s="26" t="n">
-        <v>36.092</v>
+        <v>43.012</v>
       </c>
       <c r="V15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="W15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="X15" s="26" t="n">
-        <v>36.092</v>
+        <v>43.012</v>
       </c>
       <c r="Y15" s="26" t="n">
-        <v>36.092</v>
+        <v>43.012</v>
       </c>
       <c r="Z15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="AA15" s="26" t="n">
-        <v>36.489</v>
+        <v>43.485</v>
       </c>
       <c r="AB15" s="26" t="n">
-        <v>45.248</v>
+        <v>42.539</v>
       </c>
       <c r="AC15" s="26" t="n">
-        <v>60.928</v>
+        <v>43.012</v>
       </c>
       <c r="AD15" s="26" t="n">
-        <v>61.597</v>
+        <v>43.485</v>
       </c>
       <c r="AE15" s="26" t="n">
-        <v>72.26000000000001</v>
+        <v>43.485</v>
       </c>
       <c r="AF15" s="26" t="n">
-        <v>156.217</v>
+        <v>42.539</v>
       </c>
       <c r="AG15" s="26" t="n">
-        <v>157.953</v>
+        <v>43.012</v>
       </c>
       <c r="AH15" s="26" t="n">
-        <v>196.116</v>
+        <v>43.485</v>
       </c>
       <c r="AI15" s="26" t="n">
-        <v>215.214</v>
+        <v>43.485</v>
       </c>
       <c r="AJ15" s="26" t="n">
-        <v>210.535</v>
-      </c>
-      <c r="AK15" s="26" t="n">
-        <v>177.972</v>
-      </c>
-      <c r="AL15" s="26" t="n">
-        <v>178.725</v>
-      </c>
-      <c r="AM15" s="26" t="n">
-        <v>178.725</v>
-      </c>
-      <c r="AN15" s="26" t="n">
-        <v>160.407</v>
-      </c>
-      <c r="AO15" s="26" t="n">
-        <v>151.947</v>
-      </c>
-      <c r="AP15" s="26" t="n">
-        <v>153.616</v>
-      </c>
-      <c r="AQ15" s="26" t="n">
-        <v>153.616</v>
-      </c>
-      <c r="AR15" s="26" t="n">
-        <v>150.277</v>
-      </c>
-      <c r="AS15" s="26" t="n">
-        <v>140.218</v>
-      </c>
-      <c r="AT15" s="26" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="AU15" s="26" t="n">
-        <v>25.117</v>
-      </c>
-      <c r="AV15" s="26" t="n">
-        <v>24.571</v>
-      </c>
-      <c r="AW15" s="26" t="n">
-        <v>24.844</v>
-      </c>
-      <c r="AX15" s="26" t="n">
-        <v>25.117</v>
-      </c>
-      <c r="AY15" s="26" t="n">
-        <v>25.117</v>
-      </c>
-      <c r="AZ15" s="26" t="n">
-        <v>24.571</v>
-      </c>
-      <c r="BA15" s="26" t="n">
-        <v>24.844</v>
-      </c>
-      <c r="BB15" s="26" t="n">
-        <v>25.117</v>
-      </c>
-      <c r="BC15" s="26" t="n">
-        <v>25.117</v>
-      </c>
-      <c r="BD15" s="26" t="n">
-        <v>24.844</v>
-      </c>
-      <c r="BE15" s="26" t="n">
-        <v>24.844</v>
+        <v>17.016</v>
+      </c>
+      <c r="BH15" s="26" t="n">
+        <v>96.423</v>
       </c>
       <c r="BI15" s="26" t="n">
-        <v>132.47</v>
+        <v>172.521</v>
       </c>
       <c r="BJ15" s="26" t="n">
-        <v>144.765</v>
+        <v>172.521</v>
       </c>
       <c r="BK15" s="26" t="n">
-        <v>145.162</v>
+        <v>172.994</v>
       </c>
       <c r="BL15" s="26" t="n">
-        <v>240.033</v>
+        <v>172.521</v>
       </c>
       <c r="BM15" s="26" t="n">
-        <v>725.5</v>
+        <v>172.521</v>
       </c>
       <c r="BN15" s="26" t="n">
-        <v>745.957</v>
-      </c>
-      <c r="BO15" s="26" t="n">
-        <v>619.586</v>
-      </c>
-      <c r="BP15" s="26" t="n">
-        <v>361.222</v>
-      </c>
-      <c r="BQ15" s="26" t="n">
-        <v>99.649</v>
-      </c>
-      <c r="BR15" s="26" t="n">
-        <v>99.649</v>
-      </c>
-      <c r="BS15" s="26" t="n">
-        <v>49.688</v>
+        <v>17.016</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>cohort:③중마진</t>
+          <t>cohort:등급없음</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>코호트 ③중마진</t>
-        </is>
+          <t>코호트 등급없음</t>
+        </is>
+      </c>
+      <c r="P16" s="26" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="Q16" s="26" t="n">
+        <v>36.092</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>36.489</v>
+      </c>
+      <c r="S16" s="26" t="n">
+        <v>36.489</v>
       </c>
       <c r="T16" s="26" t="n">
-        <v>8.15</v>
+        <v>35.695</v>
       </c>
       <c r="U16" s="26" t="n">
-        <v>28.477</v>
+        <v>36.092</v>
       </c>
       <c r="V16" s="26" t="n">
-        <v>29.764</v>
+        <v>36.489</v>
       </c>
       <c r="W16" s="26" t="n">
-        <v>34.958</v>
+        <v>36.489</v>
       </c>
       <c r="X16" s="26" t="n">
-        <v>41.879</v>
+        <v>36.092</v>
       </c>
       <c r="Y16" s="26" t="n">
-        <v>50.352</v>
+        <v>36.092</v>
       </c>
       <c r="Z16" s="26" t="n">
-        <v>56.513</v>
+        <v>36.489</v>
       </c>
       <c r="AA16" s="26" t="n">
-        <v>56.513</v>
+        <v>36.489</v>
       </c>
       <c r="AB16" s="26" t="n">
-        <v>55.284</v>
+        <v>45.248</v>
       </c>
       <c r="AC16" s="26" t="n">
-        <v>55.899</v>
+        <v>60.928</v>
       </c>
       <c r="AD16" s="26" t="n">
-        <v>79.492</v>
+        <v>61.597</v>
       </c>
       <c r="AE16" s="26" t="n">
-        <v>241.17</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="AF16" s="26" t="n">
-        <v>404.587</v>
+        <v>156.217</v>
       </c>
       <c r="AG16" s="26" t="n">
-        <v>466.238</v>
+        <v>157.953</v>
       </c>
       <c r="AH16" s="26" t="n">
-        <v>517.022</v>
+        <v>196.116</v>
       </c>
       <c r="AI16" s="26" t="n">
-        <v>557.873</v>
+        <v>215.214</v>
       </c>
       <c r="AJ16" s="26" t="n">
-        <v>545.746</v>
+        <v>210.535</v>
       </c>
       <c r="AK16" s="26" t="n">
-        <v>536.977</v>
+        <v>177.972</v>
       </c>
       <c r="AL16" s="26" t="n">
-        <v>538.062</v>
+        <v>178.725</v>
       </c>
       <c r="AM16" s="26" t="n">
-        <v>528.11</v>
+        <v>178.725</v>
       </c>
       <c r="AN16" s="26" t="n">
-        <v>522.369</v>
+        <v>160.407</v>
       </c>
       <c r="AO16" s="26" t="n">
-        <v>490.016</v>
+        <v>151.947</v>
       </c>
       <c r="AP16" s="26" t="n">
-        <v>479.284</v>
+        <v>153.616</v>
       </c>
       <c r="AQ16" s="26" t="n">
-        <v>479.284</v>
+        <v>153.616</v>
       </c>
       <c r="AR16" s="26" t="n">
-        <v>449.618</v>
+        <v>150.277</v>
       </c>
       <c r="AS16" s="26" t="n">
-        <v>361.458</v>
+        <v>140.218</v>
       </c>
       <c r="AT16" s="26" t="n">
-        <v>99.988</v>
+        <v>45.61</v>
       </c>
       <c r="AU16" s="26" t="n">
-        <v>56.668</v>
+        <v>25.117</v>
       </c>
       <c r="AV16" s="26" t="n">
-        <v>23.163</v>
+        <v>24.571</v>
       </c>
       <c r="AW16" s="26" t="n">
-        <v>19.644</v>
+        <v>24.844</v>
       </c>
       <c r="AX16" s="26" t="n">
-        <v>19.86</v>
+        <v>25.117</v>
       </c>
       <c r="AY16" s="26" t="n">
-        <v>14.463</v>
+        <v>25.117</v>
+      </c>
+      <c r="AZ16" s="26" t="n">
+        <v>24.571</v>
+      </c>
+      <c r="BA16" s="26" t="n">
+        <v>24.844</v>
+      </c>
+      <c r="BB16" s="26" t="n">
+        <v>25.117</v>
+      </c>
+      <c r="BC16" s="26" t="n">
+        <v>25.117</v>
+      </c>
+      <c r="BD16" s="26" t="n">
+        <v>24.844</v>
+      </c>
+      <c r="BE16" s="26" t="n">
+        <v>24.844</v>
+      </c>
+      <c r="BI16" s="26" t="n">
+        <v>132.47</v>
       </c>
       <c r="BJ16" s="26" t="n">
-        <v>101.349</v>
+        <v>144.765</v>
       </c>
       <c r="BK16" s="26" t="n">
-        <v>205.257</v>
+        <v>145.162</v>
       </c>
       <c r="BL16" s="26" t="n">
-        <v>431.845</v>
+        <v>240.033</v>
       </c>
       <c r="BM16" s="26" t="n">
-        <v>1945.72</v>
+        <v>725.5</v>
       </c>
       <c r="BN16" s="26" t="n">
-        <v>2148.895</v>
+        <v>745.957</v>
       </c>
       <c r="BO16" s="26" t="n">
-        <v>1970.953</v>
+        <v>619.586</v>
       </c>
       <c r="BP16" s="26" t="n">
-        <v>967.732</v>
+        <v>361.222</v>
       </c>
       <c r="BQ16" s="26" t="n">
-        <v>77.13</v>
+        <v>99.649</v>
+      </c>
+      <c r="BR16" s="26" t="n">
+        <v>99.649</v>
+      </c>
+      <c r="BS16" s="26" t="n">
+        <v>49.688</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>cohort:②BEP</t>
+          <t>cohort:⑤초호황</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>코호트 ②BEP</t>
-        </is>
+          <t>코호트 ⑤초호황</t>
+        </is>
+      </c>
+      <c r="T17" s="26" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="U17" s="26" t="n">
+        <v>28.477</v>
+      </c>
+      <c r="V17" s="26" t="n">
+        <v>29.764</v>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>34.958</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>55.357</v>
+      </c>
+      <c r="Y17" s="26" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Z17" s="26" t="n">
+        <v>143.482</v>
+      </c>
+      <c r="AA17" s="26" t="n">
+        <v>143.482</v>
+      </c>
+      <c r="AB17" s="26" t="n">
+        <v>140.363</v>
+      </c>
+      <c r="AC17" s="26" t="n">
+        <v>141.922</v>
+      </c>
+      <c r="AD17" s="26" t="n">
+        <v>166.461</v>
+      </c>
+      <c r="AE17" s="26" t="n">
+        <v>354.645</v>
       </c>
       <c r="AF17" s="26" t="n">
-        <v>33.467</v>
+        <v>605.391</v>
       </c>
       <c r="AG17" s="26" t="n">
-        <v>56.397</v>
+        <v>722.1</v>
       </c>
       <c r="AH17" s="26" t="n">
-        <v>57.017</v>
+        <v>853.049</v>
       </c>
       <c r="AI17" s="26" t="n">
-        <v>57.017</v>
+        <v>932.617</v>
       </c>
       <c r="AJ17" s="26" t="n">
-        <v>55.778</v>
+        <v>883.009</v>
       </c>
       <c r="AK17" s="26" t="n">
-        <v>56.397</v>
+        <v>877.987</v>
       </c>
       <c r="AL17" s="26" t="n">
-        <v>57.017</v>
+        <v>882.8200000000001</v>
       </c>
       <c r="AM17" s="26" t="n">
-        <v>57.017</v>
+        <v>872.867</v>
       </c>
       <c r="AN17" s="26" t="n">
-        <v>56.397</v>
+        <v>863.38</v>
       </c>
       <c r="AO17" s="26" t="n">
-        <v>37.805</v>
+        <v>812.433</v>
+      </c>
+      <c r="AP17" s="26" t="n">
+        <v>767.024</v>
+      </c>
+      <c r="AQ17" s="26" t="n">
+        <v>752.369</v>
+      </c>
+      <c r="AR17" s="26" t="n">
+        <v>667.876</v>
+      </c>
+      <c r="AS17" s="26" t="n">
+        <v>562.016</v>
+      </c>
+      <c r="AT17" s="26" t="n">
+        <v>262.31</v>
+      </c>
+      <c r="AU17" s="26" t="n">
+        <v>129.553</v>
+      </c>
+      <c r="AV17" s="26" t="n">
+        <v>63.343</v>
+      </c>
+      <c r="AW17" s="26" t="n">
+        <v>19.644</v>
+      </c>
+      <c r="AX17" s="26" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AY17" s="26" t="n">
+        <v>14.463</v>
+      </c>
+      <c r="BJ17" s="26" t="n">
+        <v>101.349</v>
+      </c>
+      <c r="BK17" s="26" t="n">
+        <v>425.921</v>
+      </c>
+      <c r="BL17" s="26" t="n">
+        <v>803.391</v>
       </c>
       <c r="BM17" s="26" t="n">
-        <v>203.898</v>
+        <v>3113.157</v>
       </c>
       <c r="BN17" s="26" t="n">
-        <v>226.209</v>
+        <v>3516.683</v>
       </c>
       <c r="BO17" s="26" t="n">
-        <v>94.202</v>
+        <v>3195.206</v>
+      </c>
+      <c r="BP17" s="26" t="n">
+        <v>1621.755</v>
+      </c>
+      <c r="BQ17" s="26" t="n">
+        <v>117.31</v>
       </c>
     </row>
     <row r="18">
@@ -38896,145 +39782,145 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="M23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0566</v>
       </c>
       <c r="N23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="O23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="Q23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="R23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.1</v>
+        <v>0.0704</v>
       </c>
       <c r="T23" s="21" t="n">
-        <v>0.0964</v>
+        <v>0.0762</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.1161</v>
       </c>
       <c r="V23" s="21" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1203</v>
       </c>
       <c r="W23" s="21" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1223</v>
       </c>
       <c r="X23" s="21" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1281</v>
       </c>
       <c r="Y23" s="21" t="n">
-        <v>0.0801</v>
+        <v>0.133</v>
       </c>
       <c r="Z23" s="21" t="n">
-        <v>0.0849</v>
+        <v>0.1384</v>
       </c>
       <c r="AA23" s="21" t="n">
-        <v>0.0849</v>
+        <v>0.1384</v>
       </c>
       <c r="AB23" s="21" t="n">
-        <v>0.0849</v>
+        <v>0.1384</v>
       </c>
       <c r="AC23" s="21" t="n">
-        <v>0.0849</v>
+        <v>0.1384</v>
       </c>
       <c r="AD23" s="21" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1396</v>
       </c>
       <c r="AE23" s="21" t="n">
-        <v>0.0697</v>
+        <v>0.1445</v>
       </c>
       <c r="AF23" s="21" t="n">
-        <v>0.0636</v>
+        <v>0.1467</v>
       </c>
       <c r="AG23" s="21" t="n">
-        <v>0.0622</v>
+        <v>0.1472</v>
       </c>
       <c r="AH23" s="21" t="n">
-        <v>0.0648</v>
+        <v>0.1476</v>
       </c>
       <c r="AI23" s="21" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.1478</v>
       </c>
       <c r="AJ23" s="21" t="n">
-        <v>0.0635</v>
+        <v>0.1491</v>
       </c>
       <c r="AK23" s="21" t="n">
-        <v>0.063</v>
+        <v>0.15</v>
       </c>
       <c r="AL23" s="21" t="n">
-        <v>0.0631</v>
+        <v>0.15</v>
       </c>
       <c r="AM23" s="21" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AN23" s="21" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AO23" s="21" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="AP23" s="21" t="n">
-        <v>0.0688</v>
+        <v>0.15</v>
       </c>
       <c r="AQ23" s="21" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="AR23" s="21" t="n">
-        <v>0.0663</v>
+        <v>0.15</v>
       </c>
       <c r="AS23" s="21" t="n">
-        <v>0.0678</v>
+        <v>0.15</v>
       </c>
       <c r="AT23" s="21" t="n">
-        <v>0.0809</v>
+        <v>0.15</v>
       </c>
       <c r="AU23" s="21" t="n">
-        <v>0.0781</v>
+        <v>0.15</v>
       </c>
       <c r="AV23" s="21" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="AW23" s="21" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AX23" s="21" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="AY23" s="21" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="25">
@@ -39146,7 +40032,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -39250,7 +40136,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -39302,7 +40188,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -39354,7 +40240,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -39406,7 +40292,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -39458,7 +40344,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -39510,7 +40396,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -39562,7 +40448,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -39614,7 +40500,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -39710,7 +40596,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -39762,7 +40648,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -39814,7 +40700,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -39866,7 +40752,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -39918,7 +40804,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -39970,7 +40856,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -40022,7 +40908,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -40074,7 +40960,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -40126,7 +41012,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -40178,7 +41064,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -40230,7 +41116,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -40282,7 +41168,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -40378,7 +41264,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -40430,7 +41316,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -40482,7 +41368,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -40669,7 +41555,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -40721,7 +41607,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -40773,7 +41659,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -40825,7 +41711,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -40847,7 +41733,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 5%, ③중마진 62%, ④호황 33% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 5%, ③중마진 62%, ④호황 33%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
@@ -48339,7 +49225,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5287.2</v>
+        <v>5943.5</v>
       </c>
     </row>
     <row r="30">
@@ -48359,7 +49245,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.96</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="32">
@@ -48379,7 +49265,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2153</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="34">
@@ -48389,7 +49275,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="35">
@@ -48399,7 +49285,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>58700</v>
+        <v>66100</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="분기" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="연간예상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="외화" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1645,55 +1645,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15535억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)</t>
+SLS 해양 원화 15501억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14386억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)</t>
+SLS 해양 원화 14349억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14107억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)</t>
+SLS 해양 원화 14071억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14196억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)</t>
+SLS 해양 원화 14159억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14060억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)</t>
+SLS 해양 원화 14024억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13907억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)</t>
+SLS 해양 원화 13871억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13210억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 13175억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12611억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 12578억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12410억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 12378억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2260,49 +2260,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21781억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21778억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 25165억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 25159억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28617억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28606억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32125억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32111억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35668억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35651억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39261억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39240억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41520억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41495억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 42574억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 42546억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2320,49 +2320,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 21781억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 21778억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 25165억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 25159억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 28617억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 28606억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 32125억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 32111억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 35668억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 35651억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39261억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39240억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41520억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41495억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 42574억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 42546억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4042,55 +4042,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15535억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)
+        <t>추정: SLS 해양 원화 15501억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14386억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)
+        <t>추정: SLS 해양 원화 14349억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14107억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)
+        <t>추정: SLS 해양 원화 14071억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14196억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)
+        <t>추정: SLS 해양 원화 14159억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14060억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)
+        <t>추정: SLS 해양 원화 14024억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13907억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)
+        <t>추정: SLS 해양 원화 13871억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13210억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 13175억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12611억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 12578억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12410억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 12378억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
@@ -4853,7 +4853,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -7591,35 +7591,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -7710,35 +7710,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -7829,35 +7829,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -7948,35 +7948,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8067,35 +8067,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8186,35 +8186,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8305,35 +8305,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8424,35 +8424,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8559,7 +8559,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>78700</v>
+        <v>77500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -8650,7 +8650,7 @@
         <v>123000</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>79100</v>
+        <v>79200</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -8832,7 +8832,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78650</v>
+        <v>78266.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10391,36 +10391,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.008021065000000001</v>
+        <v>-0.00777945</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.00530737</v>
+        <v>0.002214942</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.007736176</v>
+        <v>-0.001442085</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.00557208</v>
+        <v>-0.004672694</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.012587656</v>
+        <v>0.001502197</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.000969832</v>
+        <v>0.004951887</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.001704363</v>
+        <v>-0.00567505</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.003793842</v>
+        <v>-0.000955404</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.003435922</v>
+        <v>-0.004941933</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.000452044</v>
+        <v>-0.003727192</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -10519,36 +10519,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.003078752</v>
+        <v>-0.002964344</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.00321709</v>
+        <v>-0.006332485</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.00506089</v>
+        <v>0.001225825</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.005907951</v>
+        <v>-0.004345886</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.004232992</v>
+        <v>-0.00015213</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.001874576</v>
+        <v>0.00209785</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.006272557</v>
+        <v>-0.000253824</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.005483096</v>
+        <v>0.0007706739999999999</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-5.813e-06</v>
+        <v>-0.001432421</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.006842091</v>
+        <v>-3.7575e-05</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -10778,33 +10778,33 @@
         <v>-0.072675543</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.08136873999999999</v>
+        <v>-0.08129399900000001</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.0876798</v>
+        <v>-0.087580431</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.098022336</v>
+        <v>-0.097902314</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.110474744</v>
+        <v>-0.110323822</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.125418895</v>
+        <v>-0.125227234</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.145416933</v>
+        <v>-0.145164174</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.106972946</v>
+        <v>-0.106696279</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.055938882</v>
+        <v>-0.055681966</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.058961892</v>
+        <v>-0.058674169</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -10906,33 +10906,33 @@
         <v>0.218477776</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.186162925</v>
+        <v>0.185991927</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.155356976</v>
+        <v>0.155215909</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.13714733</v>
+        <v>0.137041954</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.122603921</v>
+        <v>0.122519993</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.110289668</v>
+        <v>0.110223533</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.100728662</v>
+        <v>0.100674577</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.057528737</v>
+        <v>0.057468971</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.025403708</v>
+        <v>0.025335543</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.024652443</v>
+        <v>0.024587293</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -11632,33 +11632,33 @@
         <v>26161.004344</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>26161.025617</v>
+        <v>26161.027134</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>26161.141182</v>
+        <v>26161.144812</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>26161.043712</v>
+        <v>26161.052217</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>26161.049507</v>
+        <v>26161.049665</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>26161.045092</v>
+        <v>26161.040791</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>26161.054594</v>
+        <v>26161.062808</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>12335.861445</v>
+        <v>12335.855156</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>-0.043702</v>
+        <v>-0.047803</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>0.043032</v>
+        <v>0.036751</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -11778,39 +11778,39 @@
         <v>0.119420424</v>
       </c>
       <c r="AD41" s="31" t="n">
-        <v>0.119545768</v>
+        <v>0.119545707</v>
       </c>
       <c r="AE41" s="25">
         <f>IFERROR(subQ!AE39/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF41" s="31" t="n">
-        <v>0.12031205</v>
+        <v>0.120312072</v>
       </c>
       <c r="AG41" s="31" t="n">
-        <v>0.121765236</v>
+        <v>0.121765145</v>
       </c>
       <c r="AH41" s="31" t="n">
-        <v>0.121772004</v>
+        <v>0.121772148</v>
       </c>
       <c r="AI41" s="31" t="n">
-        <v>0.121716996</v>
+        <v>0.121717026</v>
       </c>
       <c r="AJ41" s="25">
         <f>IFERROR(subQ!AJ39/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK41" s="31" t="n">
-        <v>0.122175264</v>
+        <v>0.12217521</v>
       </c>
       <c r="AL41" s="31" t="n">
-        <v>0.122144304</v>
+        <v>0.122144182</v>
       </c>
       <c r="AM41" s="31" t="n">
-        <v>0.121823587</v>
+        <v>0.121824049</v>
       </c>
       <c r="AN41" s="31" t="n">
-        <v>0.121730918</v>
+        <v>0.121730876</v>
       </c>
       <c r="AO41" s="25">
         <f>IFERROR(subQ!AO39/subQ!AO38,"")</f>
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>78700</v>
+        <v>77500</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2199999453657897</v>
+        <v>0.2199996554207108</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.05559123538196922</v>
+        <v>0.05559119000592207</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.9999653282677582</v>
+        <v>0.9999652896352045</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.0720169882373661</v>
+        <v>0.07201706670552778</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03568161716461894</v>
+        <v>0.03568172018691858</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41055,73 +41055,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="22">
@@ -41226,73 +41226,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1374.91</v>
+        <v>1371.93</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1369.53</v>
+        <v>1365.97</v>
       </c>
     </row>
     <row r="23">
@@ -41397,73 +41397,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1638165.5</v>
+        <v>1634612.7</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1521147.8</v>
+        <v>1517191.8</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1446373.4</v>
+        <v>1442611.9</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1454025.1</v>
+        <v>1450243.7</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1440395.2</v>
+        <v>1436649.2</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1402312.3</v>
+        <v>1398665.3</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1320953</v>
+        <v>1317517.6</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1261052.8</v>
+        <v>1257773.2</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1240982.7</v>
+        <v>1237755.3</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1120688.3</v>
+        <v>1117773.7</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>961936.1</v>
+        <v>959434.4</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>421903.9</v>
+        <v>420806.7</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>211898.4</v>
+        <v>211347.4</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>120459.9</v>
+        <v>120146.6</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60970.3</v>
+        <v>60811.7</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61640.3</v>
+        <v>61479.9</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>54244.1</v>
+        <v>54103</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33674.1</v>
+        <v>33586.6</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -41487,25 +41487,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5759748.1</v>
+        <v>5756195.3</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5861941.5</v>
+        <v>5846696.6</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5225300.8</v>
+        <v>5211711.4</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2716426.7</v>
+        <v>2709362.2</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>297314.6</v>
+        <v>296541.2</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>136567.4</v>
+        <v>136212.2</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>68096.60000000001</v>
+        <v>67919.60000000001</v>
       </c>
     </row>
     <row r="24">
@@ -41610,73 +41610,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1553474.4</v>
+        <v>1550105.3</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1438622.2</v>
+        <v>1434880.9</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1410730.4</v>
+        <v>1407061.6</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1419637.9</v>
+        <v>1415945.9</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1406008</v>
+        <v>1402351.4</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1390725.3</v>
+        <v>1387108.5</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1320953</v>
+        <v>1317517.6</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1261052.8</v>
+        <v>1257773.2</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1240982.7</v>
+        <v>1237755.3</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1120688.3</v>
+        <v>1117773.7</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>961936.1</v>
+        <v>959434.4</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>421903.9</v>
+        <v>420806.7</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>211898.4</v>
+        <v>211347.4</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>120459.9</v>
+        <v>120146.6</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60970.3</v>
+        <v>60811.7</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61640.3</v>
+        <v>61479.9</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>54244.1</v>
+        <v>54103</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33674.1</v>
+        <v>33586.6</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -41700,25 +41700,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5407507.3</v>
+        <v>5404138.2</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5674998.5</v>
+        <v>5660239.8</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5213713.8</v>
+        <v>5200154.6</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2716426.7</v>
+        <v>2709362.2</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>297314.6</v>
+        <v>296541.2</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>136567.4</v>
+        <v>136212.2</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>68096.60000000001</v>
+        <v>67919.60000000001</v>
       </c>
     </row>
     <row r="25">
@@ -41823,46 +41823,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1247474.1</v>
+        <v>1244768.6</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1140446.2</v>
+        <v>1137480.3</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1109241.4</v>
+        <v>1106356.6</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1114835.7</v>
+        <v>1111936.4</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1101205.9</v>
+        <v>1098342</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1089236.2</v>
+        <v>1086403.5</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1019463.9</v>
+        <v>1016812.6</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>956250.7</v>
+        <v>953763.8</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>936180.6</v>
+        <v>933745.9</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>822512.3</v>
+        <v>820373.2</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>660447</v>
+        <v>658729.4</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>130690.8</v>
+        <v>130350.9</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>105401.9</v>
+        <v>105127.8</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34915.8</v>
+        <v>34825</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -41994,73 +41994,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>306000.4</v>
+        <v>305336.7</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>298176</v>
+        <v>297400.5</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>301489.1</v>
+        <v>300705</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>304802.1</v>
+        <v>304009.4</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>304802.1</v>
+        <v>304009.4</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>301489.1</v>
+        <v>300705</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>301489.1</v>
+        <v>300705</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>304802.1</v>
+        <v>304009.4</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>304802.1</v>
+        <v>304009.4</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>298176</v>
+        <v>297400.5</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>301489.1</v>
+        <v>300705</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>291213.2</v>
+        <v>290455.8</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>106496.5</v>
+        <v>106219.5</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85544.10000000001</v>
+        <v>85321.60000000001</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60970.3</v>
+        <v>60811.7</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61640.3</v>
+        <v>61479.9</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>54244.1</v>
+        <v>54103</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33674.1</v>
+        <v>33586.6</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34422.5</v>
+        <v>34332.9</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>34048.3</v>
+        <v>33959.8</v>
       </c>
     </row>
     <row r="27">
@@ -42388,95 +42388,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -51421,7 +51421,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -56938,7 +56938,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -59190,7 +59190,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4421.5</v>
+        <v>4418.3</v>
       </c>
     </row>
     <row r="30">
@@ -59210,7 +59210,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.8</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="32">
@@ -59220,7 +59220,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="33">
@@ -59230,7 +59230,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.18</v>
+        <v>0.1799</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1645,55 +1645,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15501억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)</t>
+SLS 해양 원화 15472억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14349억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)</t>
+SLS 해양 원화 14304억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14071억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)</t>
+SLS 해양 원화 14026억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14159억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)</t>
+SLS 해양 원화 14115억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14024억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)</t>
+SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13871억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)</t>
+SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13175억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 13134억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12578억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 12538억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12378억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
+SLS 해양 원화 12339억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2260,49 +2260,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21778억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21775억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 25159억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 25152억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28606억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28595억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32111억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32095억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35651억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35630억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39240억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39215억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41495억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41466억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 42546억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 42513억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2320,49 +2320,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 21778억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 21775억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 25159억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 25152억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 28606억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 28595억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 32111억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 32095억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 35651억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 35630억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39240억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39215억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41495억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41466억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 42546억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 42513억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4042,55 +4042,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15501억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)
+        <t>추정: SLS 해양 원화 15472억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14349억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)
+        <t>추정: SLS 해양 원화 14304억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14071억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)
+        <t>추정: SLS 해양 원화 14026억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14159억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)
+        <t>추정: SLS 해양 원화 14115억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14024억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)
+        <t>추정: SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13871억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)
+        <t>추정: SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13175억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 13134억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12578억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 12538억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12378억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 12339억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억)
 [sls_link]</t>
       </text>
     </comment>
@@ -4853,7 +4853,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -7591,35 +7591,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -7710,35 +7710,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -7829,35 +7829,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -7948,35 +7948,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8067,35 +8067,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -8186,35 +8186,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -8305,35 +8305,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -8424,35 +8424,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8559,7 +8559,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>77500</v>
+        <v>74400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -8741,7 +8741,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>77000</v>
+        <v>74100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -8832,7 +8832,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78266.7</v>
+        <v>77325</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10391,36 +10391,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.00777945</v>
+        <v>-0.009630975</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.002214942</v>
+        <v>0.003669057</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.001442085</v>
+        <v>-0.004706386</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.004672694</v>
+        <v>-0.006927217</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.001502197</v>
+        <v>-0.002565651</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.004951887</v>
+        <v>0.005814751</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.00567505</v>
+        <v>-0.005768793</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.000955404</v>
+        <v>-0.002466643</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.004941933</v>
+        <v>0.00081555</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.003727192</v>
+        <v>-0.004294812</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -10519,36 +10519,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.002964344</v>
+        <v>-0.004965137</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.006332485</v>
+        <v>-0.004939136</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.001225825</v>
+        <v>-0.002042923</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.004345886</v>
+        <v>-0.006606908</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.00015213</v>
+        <v>-0.004225874</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.00209785</v>
+        <v>0.002953773</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.000253824</v>
+        <v>-0.000355684</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.0007706739999999999</v>
+        <v>-0.000693341</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.001432421</v>
+        <v>0.00442246</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-3.7575e-05</v>
+        <v>-0.01050769</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -10778,33 +10778,33 @@
         <v>-0.072675543</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.08129399900000001</v>
+        <v>-0.081229494</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.087580431</v>
+        <v>-0.0874634</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.097902314</v>
+        <v>-0.097760524</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.110323822</v>
+        <v>-0.110146142</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.125227234</v>
+        <v>-0.125001414</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.145164174</v>
+        <v>-0.144866302</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.106696279</v>
+        <v>-0.106369173</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.055681966</v>
+        <v>-0.055375895</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.058674169</v>
+        <v>-0.058332148</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -10906,33 +10906,33 @@
         <v>0.218477776</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.185991927</v>
+        <v>0.185844347</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.155215909</v>
+        <v>0.155038674</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.137041954</v>
+        <v>0.136908679</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.122519993</v>
+        <v>0.122414537</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.110223533</v>
+        <v>0.110139736</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.100674577</v>
+        <v>0.100606533</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.057468971</v>
+        <v>0.057395326</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.025335543</v>
+        <v>0.025252377</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.024587293</v>
+        <v>0.024508555</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -11632,33 +11632,33 @@
         <v>26161.004344</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>26161.027134</v>
+        <v>26161.029273</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>26161.144812</v>
+        <v>26161.139202</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>26161.052217</v>
+        <v>26161.049713</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>26161.049665</v>
+        <v>26161.047298</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>26161.040791</v>
+        <v>26161.049775</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>26161.062808</v>
+        <v>26161.061114</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>12335.855156</v>
+        <v>12335.859179</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>-0.047803</v>
+        <v>-0.047646</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>0.036751</v>
+        <v>0.035435</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -11778,39 +11778,39 @@
         <v>0.119420424</v>
       </c>
       <c r="AD41" s="31" t="n">
-        <v>0.119545707</v>
+        <v>0.11954566</v>
       </c>
       <c r="AE41" s="25">
         <f>IFERROR(subQ!AE39/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF41" s="31" t="n">
-        <v>0.120312072</v>
+        <v>0.120312174</v>
       </c>
       <c r="AG41" s="31" t="n">
-        <v>0.121765145</v>
+        <v>0.121765213</v>
       </c>
       <c r="AH41" s="31" t="n">
-        <v>0.121772148</v>
+        <v>0.121772077</v>
       </c>
       <c r="AI41" s="31" t="n">
-        <v>0.121717026</v>
+        <v>0.121717054</v>
       </c>
       <c r="AJ41" s="25">
         <f>IFERROR(subQ!AJ39/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK41" s="31" t="n">
-        <v>0.12217521</v>
+        <v>0.122175309</v>
       </c>
       <c r="AL41" s="31" t="n">
-        <v>0.122144182</v>
+        <v>0.122144334</v>
       </c>
       <c r="AM41" s="31" t="n">
-        <v>0.121824049</v>
+        <v>0.121824172</v>
       </c>
       <c r="AN41" s="31" t="n">
-        <v>0.121730876</v>
+        <v>0.121730969</v>
       </c>
       <c r="AO41" s="25">
         <f>IFERROR(subQ!AO39/subQ!AO38,"")</f>
@@ -12155,11 +12155,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>77500</v>
+        <v>74400</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,800원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2199996554207108</v>
+        <v>0.2199999780933792</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.05559119000592207</v>
+        <v>0.05559124886421644</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.9999652896352045</v>
+        <v>0.9999652442800508</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.07201706670552778</v>
+        <v>0.07201697195873438</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03568172018691858</v>
+        <v>0.03568173811159159</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41055,73 +41055,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="22">
@@ -41226,73 +41226,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1371.93</v>
+        <v>1369.36</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1365.97</v>
+        <v>1361.66</v>
       </c>
     </row>
     <row r="23">
@@ -41397,73 +41397,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1634612.7</v>
+        <v>1631553.4</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1517191.8</v>
+        <v>1512407.8</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1442611.9</v>
+        <v>1438063</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1450243.7</v>
+        <v>1445670.8</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1436649.2</v>
+        <v>1432119.2</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1398665.3</v>
+        <v>1394255.1</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1317517.6</v>
+        <v>1313363.2</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1257773.2</v>
+        <v>1253807.2</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1237755.3</v>
+        <v>1233852.4</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1117773.7</v>
+        <v>1114249.2</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>959434.4</v>
+        <v>956409.1</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>420806.7</v>
+        <v>419479.8</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>211347.4</v>
+        <v>210680.9</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>120146.6</v>
+        <v>119767.8</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60811.7</v>
+        <v>60619.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61479.9</v>
+        <v>61286.1</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>54103</v>
+        <v>53932.4</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33586.6</v>
+        <v>33480.7</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -41487,25 +41487,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5756195.3</v>
+        <v>5753136</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5846696.6</v>
+        <v>5828260.8</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5211711.4</v>
+        <v>5195277.9</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2709362.2</v>
+        <v>2700819</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>296541.2</v>
+        <v>295606.2</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>136212.2</v>
+        <v>135782.8</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67919.60000000001</v>
+        <v>67705.39999999999</v>
       </c>
     </row>
     <row r="24">
@@ -41610,73 +41610,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1550105.3</v>
+        <v>1547204.1</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1434880.9</v>
+        <v>1430356.4</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1407061.6</v>
+        <v>1402624.9</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1415945.9</v>
+        <v>1411481.1</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1402351.4</v>
+        <v>1397929.5</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1387108.5</v>
+        <v>1382734.7</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1317517.6</v>
+        <v>1313363.2</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1257773.2</v>
+        <v>1253807.2</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1237755.3</v>
+        <v>1233852.4</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1117773.7</v>
+        <v>1114249.2</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>959434.4</v>
+        <v>956409.1</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>420806.7</v>
+        <v>419479.8</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>211347.4</v>
+        <v>210680.9</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>120146.6</v>
+        <v>119767.8</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60811.7</v>
+        <v>60619.9</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61479.9</v>
+        <v>61286.1</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>54103</v>
+        <v>53932.4</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33586.6</v>
+        <v>33480.7</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -41700,25 +41700,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5404138.2</v>
+        <v>5401237</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5660239.8</v>
+        <v>5642391.9</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5200154.6</v>
+        <v>5183757.5</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2709362.2</v>
+        <v>2700819</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>296541.2</v>
+        <v>295606.2</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>136212.2</v>
+        <v>135782.8</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67919.60000000001</v>
+        <v>67705.39999999999</v>
       </c>
     </row>
     <row r="25">
@@ -41823,46 +41823,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1244768.6</v>
+        <v>1242438.8</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1137480.3</v>
+        <v>1133893.6</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1106356.6</v>
+        <v>1102868.1</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1111936.4</v>
+        <v>1108430.3</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1098342</v>
+        <v>1094878.7</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1086403.5</v>
+        <v>1082977.9</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1016812.6</v>
+        <v>1013606.4</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>953763.8</v>
+        <v>950756.4</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>933745.9</v>
+        <v>930801.6</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>820373.2</v>
+        <v>817786.4</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>658729.4</v>
+        <v>656652.3</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>130350.9</v>
+        <v>129939.9</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>105127.8</v>
+        <v>104796.3</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34825</v>
+        <v>34715.2</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -41994,73 +41994,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>305336.7</v>
+        <v>304765.3</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>297400.5</v>
+        <v>296462.8</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>300705</v>
+        <v>299756.8</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>304009.4</v>
+        <v>303050.8</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>304009.4</v>
+        <v>303050.8</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>300705</v>
+        <v>299756.8</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>300705</v>
+        <v>299756.8</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>304009.4</v>
+        <v>303050.8</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>304009.4</v>
+        <v>303050.8</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>297400.5</v>
+        <v>296462.8</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>300705</v>
+        <v>299756.8</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>290455.8</v>
+        <v>289540</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>106219.5</v>
+        <v>105884.6</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85321.60000000001</v>
+        <v>85052.60000000001</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60811.7</v>
+        <v>60619.9</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61479.9</v>
+        <v>61286.1</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>54103</v>
+        <v>53932.4</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33586.6</v>
+        <v>33480.7</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34332.9</v>
+        <v>34224.7</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33959.8</v>
+        <v>33852.7</v>
       </c>
     </row>
     <row r="27">
@@ -42388,95 +42388,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -51421,7 +51421,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -56938,7 +56938,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -59190,7 +59190,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4418.3</v>
+        <v>4414.6</v>
       </c>
     </row>
     <row r="30">
@@ -59210,7 +59210,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.54</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="32">
@@ -59220,7 +59220,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.16</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="33">
@@ -59230,7 +59230,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1799</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13293억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3048억 중 2179억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 13278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3044억 중 2177억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12184억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2965억 중 2120억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 12183억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2964억 중 2120억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11883억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 11882억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11948억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 11947억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11684억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 11683억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10172억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 10171억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21498억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21496억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 24855억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 24854억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28463억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28461억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32394억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32393억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 36678억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 36676억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41338억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41336억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45039억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45037억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47909억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47907억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 21498억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 21496억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 24855억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 24854억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 28463억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 28461억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 32394억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 32393억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 36678억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 36676억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41338억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41336억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 45039억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 45037억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47909억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47907억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13293억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3048억 중 2179억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 13278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3044억 중 2177억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12184억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2965억 중 2120억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 12183억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2964억 중 2120억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11883억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 11882억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11948억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 11947억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11684억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 11683억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2998억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10172억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3031억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 10171억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
 [sls_link]</t>
       </text>
     </comment>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(covered_scope_new_revenue, 미보정 book-value proxy, status partial; FY합 100,974억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억 중 패널 신규수주 규모(체결 분기별 한도)만큼 72% 만 기존 SLS 에서 제외 — 나머지 28% 는 선표에 유지(패널이 공시 체결 속도보다 작음: 2026Q3 패널 31,967억 vs 공시 44,707억) — 추정 창 SLS −20,325억(2026 3,107억 · 2027 8,597억 · 2028 8,621억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 44,707억 vs 패널 base 신규수주 31,967억(140%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 3,107억 vs 525억 · 2027 8,597억 vs 23,608억 · 2028 8,621억 vs 76,841억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -264억(차 -138억, -110%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(covered_scope_new_revenue, 미보정 book-value proxy, status partial; FY합 100,974억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억 중 패널 신규수주 규모(체결 분기별 한도)만큼 72% 만 기존 SLS 에서 제외 — 나머지 28% 는 선표에 유지(패널이 공시 체결 속도보다 작음: 2026Q3 패널 31,967억 vs 공시 44,707억) — 추정 창 SLS −20,322억(2026 3,105억 · 2027 8,597억 · 2028 8,620억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 44,707억 vs 패널 base 신규수주 31,967억(140%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 3,105억 vs 525억 · 2027 8,597억 vs 23,608억 · 2028 8,620억 vs 76,841억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -264억(차 -138억, -110%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4371.2</v>
+        <v>4370.8</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.02</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="33">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>74400</v>
+        <v>71900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9576,7 +9576,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>74100</v>
+        <v>71500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>77325</v>
+        <v>76180</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11226,36 +11226,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.009638028</v>
+        <v>-0.010258093</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.000865359</v>
+        <v>0.002290663</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.005424932</v>
+        <v>0.001835503</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.00276055</v>
+        <v>-0.006723585</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.004077799</v>
+        <v>-0.009416603000000001</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.002354706</v>
+        <v>0.001059672</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.007347704</v>
+        <v>-0.015296469</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.000993573</v>
+        <v>2.892e-06</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.005191882</v>
+        <v>-0.007072188</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.007223241</v>
+        <v>-0.000322071</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11354,36 +11354,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.009311989</v>
+        <v>-0.010822672</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.001429573</v>
+        <v>0.010869208</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.010006443</v>
+        <v>-0.003668361</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.005867677</v>
+        <v>-0.000835822</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.008249563</v>
+        <v>-0.004684027</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.011484001</v>
+        <v>-0.006295407</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.006391687</v>
+        <v>-0.005639676</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.005297883</v>
+        <v>-0.00731985</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.003123224</v>
+        <v>-0.005802572</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.003391438</v>
+        <v>-0.000600178</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11613,33 +11613,33 @@
         <v>-0.07035767800000001</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.076927917</v>
+        <v>-0.076894676</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.086357499</v>
+        <v>-0.086352075</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.101564255</v>
+        <v>-0.101557743</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.123206018</v>
+        <v>-0.12319745</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.153075396</v>
+        <v>-0.153063154</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.196673551</v>
+        <v>-0.196655735</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.194406068</v>
+        <v>-0.194383282</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.187129504</v>
+        <v>-0.187101107</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.257133369</v>
+        <v>-0.257085316</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11741,33 +11741,33 @@
         <v>0.211510435</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.177456917</v>
+        <v>0.177380238</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.156170254</v>
+        <v>0.156176703</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.145143017</v>
+        <v>0.145148039</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.138138033</v>
+        <v>0.138142842</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.132217629</v>
+        <v>0.132221585</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.127070508</v>
+        <v>0.127074355</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.089526088</v>
+        <v>0.089528094</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.063717776</v>
+        <v>0.063718688</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06690702599999999</v>
+        <v>0.066907912</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12467,33 +12467,33 @@
         <v>26530.920974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>27029.499334</v>
+        <v>27028.508064</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>27005.920586</v>
+        <v>27005.871358</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>27015.21967</v>
+        <v>27015.173461</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>27024.623062</v>
+        <v>27024.579897</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>27024.615539</v>
+        <v>27024.574955</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>27015.221071</v>
+        <v>27015.173973</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13190.029136</v>
+        <v>13189.98406</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>863.5281179999999</v>
+        <v>863.478631</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>863.621199</v>
+        <v>863.570783</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12768,39 +12768,39 @@
         <v>0.118831519</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007438</v>
+        <v>0.119007673</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230652</v>
+        <v>0.120230666</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882753</v>
+        <v>0.120882719</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881145</v>
+        <v>0.120881113</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893271</v>
+        <v>0.120893216</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120793023</v>
+        <v>0.120792971</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799662</v>
+        <v>0.120799723</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869768</v>
+        <v>0.120869733</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890285</v>
+        <v>0.120890219</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13145,11 +13145,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>74400</v>
+        <v>71900</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,800원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 77,200원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13420,7 +13420,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200000605926043</v>
+        <v>0.22000029432375</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559124946616326</v>
+        <v>0.05559126709828072</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999658750226808</v>
+        <v>0.9999655956080019</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.07201636151799078</v>
+        <v>0.07201634856510408</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568143875893812</v>
+        <v>0.03568140706331503</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42273,73 +42273,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="22">
@@ -42444,73 +42444,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1369.36</v>
+        <v>1367.81</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1361.66</v>
+        <v>1361.59</v>
       </c>
     </row>
     <row r="23">
@@ -42615,73 +42615,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1631553.4</v>
+        <v>1629698</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1512407.8</v>
+        <v>1512325</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1438063</v>
+        <v>1437984.3</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1445670.8</v>
+        <v>1445591.6</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1432119.2</v>
+        <v>1432040.8</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1394255.1</v>
+        <v>1394178.8</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1313363.2</v>
+        <v>1313291.3</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1253807.2</v>
+        <v>1253738.6</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1233852.4</v>
+        <v>1233784.9</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1114249.2</v>
+        <v>1114188.2</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>956409.1</v>
+        <v>956356.8</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>419479.8</v>
+        <v>419456.9</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>210680.9</v>
+        <v>210669.4</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119767.8</v>
+        <v>119761.2</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60619.9</v>
+        <v>60616.6</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61286.1</v>
+        <v>61282.7</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>53932.4</v>
+        <v>53929.5</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33480.7</v>
+        <v>33478.8</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -42705,25 +42705,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5753136</v>
+        <v>5751280.6</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5828260.8</v>
+        <v>5827941.7</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5195277.9</v>
+        <v>5194993.6</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2700819</v>
+        <v>2700671.3</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>295606.2</v>
+        <v>295590</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>135782.8</v>
+        <v>135775.2</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67705.39999999999</v>
+        <v>67701.60000000001</v>
       </c>
     </row>
     <row r="24">
@@ -42828,73 +42828,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1547204.1</v>
+        <v>1545444.6</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1430356.4</v>
+        <v>1430278.1</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1402624.9</v>
+        <v>1402548.1</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1411481.1</v>
+        <v>1411403.8</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1397929.5</v>
+        <v>1397853</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1382734.7</v>
+        <v>1382659</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1313363.2</v>
+        <v>1313291.3</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1253807.2</v>
+        <v>1253738.6</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1233852.4</v>
+        <v>1233784.9</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1114249.2</v>
+        <v>1114188.2</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>956409.1</v>
+        <v>956356.8</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>419479.8</v>
+        <v>419456.9</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>210680.9</v>
+        <v>210669.4</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119767.8</v>
+        <v>119761.2</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60619.9</v>
+        <v>60616.6</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61286.1</v>
+        <v>61282.7</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>53932.4</v>
+        <v>53929.5</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33480.7</v>
+        <v>33478.8</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -42918,25 +42918,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5401237</v>
+        <v>5399477.5</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5642391.9</v>
+        <v>5642083</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5183757.5</v>
+        <v>5183473.8</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2700819</v>
+        <v>2700671.3</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>295606.2</v>
+        <v>295590</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>135782.8</v>
+        <v>135775.2</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67705.39999999999</v>
+        <v>67701.60000000001</v>
       </c>
     </row>
     <row r="25">
@@ -43041,46 +43041,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1242438.8</v>
+        <v>1241026</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1133893.6</v>
+        <v>1133831.5</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1102868.1</v>
+        <v>1102807.7</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1108430.3</v>
+        <v>1108369.6</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1094878.7</v>
+        <v>1094818.8</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1082977.9</v>
+        <v>1082918.6</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1013606.4</v>
+        <v>1013550.9</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>950756.4</v>
+        <v>950704.3</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>930801.6</v>
+        <v>930750.6</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>817786.4</v>
+        <v>817741.6</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>656652.3</v>
+        <v>656616.4</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>129939.9</v>
+        <v>129932.7</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104796.3</v>
+        <v>104790.6</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34715.2</v>
+        <v>34713.3</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43212,73 +43212,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>304765.3</v>
+        <v>304418.7</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>296462.8</v>
+        <v>296446.5</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>299756.8</v>
+        <v>299740.4</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>303050.8</v>
+        <v>303034.2</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>303050.8</v>
+        <v>303034.2</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>299756.8</v>
+        <v>299740.4</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>299756.8</v>
+        <v>299740.4</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>303050.8</v>
+        <v>303034.2</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>303050.8</v>
+        <v>303034.2</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>296462.8</v>
+        <v>296446.5</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>299756.8</v>
+        <v>299740.4</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>289540</v>
+        <v>289524.1</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>105884.6</v>
+        <v>105878.8</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85052.60000000001</v>
+        <v>85047.89999999999</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60619.9</v>
+        <v>60616.6</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61286.1</v>
+        <v>61282.7</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>53932.4</v>
+        <v>53929.5</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33480.7</v>
+        <v>33478.8</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34224.7</v>
+        <v>34222.8</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33852.7</v>
+        <v>33850.8</v>
       </c>
     </row>
     <row r="27">
@@ -43606,95 +43606,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -54093,7 +54093,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -59866,7 +59866,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1023,62 +1023,62 @@
     </comment>
     <comment ref="AC27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0068(r4)
+max(세전, 0) × 세율 0.7%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AD27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0068(r4)
+max(세전, 0) × 세율 0.7%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AF27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0334(r4)
+max(세전, 0) × 세율 3.3%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AG27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0601(r4)
+max(세전, 0) × 세율 6.0%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AH27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.0867(r4)
+max(세전, 0) × 세율 8.7%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AI27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1134(r4)
+max(세전, 0) × 세율 11.3%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AK27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.14(r4)
+max(세전, 0) × 세율 14.0%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AL27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1667(r4)
+max(세전, 0) × 세율 16.7%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AM27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.1933(r4)
+max(세전, 0) × 세율 19.3%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AN27" authorId="0" shapeId="0">
       <text>
-        <t>3절 스칼라 '세율' 참조 — 숫자로 덮어쓰면 이 분기만 바뀐다
-max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)</t>
+        <t>모델값 역산(implied): v / 세전이익 · 모델 가정 tax_schedule 0.22(r4)
+max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)</t>
       </text>
     </comment>
     <comment ref="AC28" authorId="0" shapeId="0">
@@ -1642,121 +1642,121 @@
     <comment ref="AC40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13795억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 169302억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 1298억 중 928억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 14723억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 169302억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 1298억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3044억 중 2177억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 15454억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3044억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12183억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2964억 중 2120억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 14303억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2964억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11882억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 14025억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11947억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 14114억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 11683억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 13133억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 12537억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 10171억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)</t>
+SLS 해양 원화 12338억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AC42" authorId="0" shapeId="0">
@@ -2311,121 +2311,121 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 15070억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 17658억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 18258억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21810억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 21496억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26116억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 24854억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 28461억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34671억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 32393억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39190억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 36676억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43925억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41336억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48896억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45037억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52668억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47907억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55459억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 15070억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 17658억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 18258억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 21810억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 21496억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 26116억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 24854억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 28461억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34671억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 32393억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39190억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 36676억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43925억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41336억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48896억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 45037억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52668억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47907억 × 7.20%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55459억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2906,61 +2906,61 @@
     </comment>
     <comment ref="AC19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.7%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AD19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 0.7%(이월결손 경로 유지 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AF19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 3.3%(이월결손 경로 램프 1/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AG19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 6.0%(이월결손 경로 램프 2/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AH19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 8.7%(이월결손 경로 램프 3/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AI19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 11.3%(이월결손 경로 램프 4/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AK19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 14.0%(이월결손 경로 램프 5/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AL19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 16.7%(이월결손 경로 램프 6/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AM19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 19.3%(이월결손 경로 램프 7/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
     <comment ref="AN19" authorId="0" shapeId="0">
       <text>
-        <t>추정: max(세전, 0) × 세율 22.0%(최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정)
+        <t>추정: max(세전, 0) × 세율 22.0%(이월결손 경로 램프 8/8 — 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴)
 [tax]</t>
       </text>
     </comment>
@@ -4099,61 +4099,61 @@
     </comment>
     <comment ref="AC38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13795억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 169302억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 1298억 중 928억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 14723억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 169302억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 1298억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3044억 중 2177억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 15454억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3044억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12183억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2964억 중 2120억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 14303억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2964억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11882억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 14025억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11947억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 14114억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11812억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 11683억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10990억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 2997억 중 2143억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 13133억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10371억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 12537억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 10171억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 17% 적용; origin 2026Q2 이후 체결 6건 중 패널 신규수주 규모만큼(72%) 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 24396억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰) · origin 이후 공시 수주 SLS 3030억 중 2167억 제외(패널 신규수주 규모만큼, 72%)
+        <t>추정: SLS 해양 원화 12338억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4169,61 +4169,61 @@
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰 — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
@@ -4759,152 +4759,152 @@
   <commentList>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic covered_scope_new_revenue(억원) · 폴백·저신뢰 — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
   </commentList>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>· 세율 22.00% — 법인세 = MAX(세전,0) × 세율, 추정 전 분기 연결(Σ법인세/Σmax(세전,0) 역산, 재현 오차 ≤ 0.05억). 모델 가정 22.00% · 근거: 최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>· 세율 0.68% → 22%(terminal, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프) — 이월결손 램프(assumptions.tax_schedule): 변수 drv:법인세비용 추정 분기 셀이 분기별 세율(3절 '세율' 스칼라 연결 안 됨 — 그 값은 시작 세율) · 근거: 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 7.20% / 부채 3.57% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.072, 0.0357] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
+          <t>· 이자율 자산 5.78% / 부채 3.57% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0578, 0.0357] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)"}</t>
         </is>
       </c>
     </row>
@@ -5386,14 +5386,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 통계 흐름, 공시 계약 개별 반영 아님). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
+          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 공시 계약은 체결 분기별로 패널 신규수주와 상계(SLS 일정 유지)). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율, 선표 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율, 선표 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(이월결손 램프(assumptions.tax_schedule, 0.68%→22%) — 분기별 세율 드라이버 행 사용)</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(covered_scope_new_revenue, 미보정 book-value proxy, status partial; FY합 100,974억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억 중 패널 신규수주 규모(체결 분기별 한도)만큼 72% 만 기존 SLS 에서 제외 — 나머지 28% 는 선표에 유지(패널이 공시 체결 속도보다 작음: 2026Q3 패널 31,967억 vs 공시 44,707억) — 추정 창 SLS −20,322억(2026 3,105억 · 2027 8,597억 · 2028 8,620억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 44,707억 vs 패널 base 신규수주 31,967억(140%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 3,105억 vs 525억 · 2027 8,597억 vs 23,608억 · 2028 8,620억 vs 76,841억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -264억(차 -138억, -110%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,342억 vs 0억 · 2027 12,023억 vs 13,801억 · 2028 12,055억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4370.8</v>
+        <v>5553.2</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.45</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="32">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.178</v>
+        <v>0.2261</v>
       </c>
     </row>
     <row r="34">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1.98</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="35">
@@ -5892,7 +5892,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>48600</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="36">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 세율</t>
+          <t>법인세율(/세전) — 법인세 = MAX(세전,0) × 분기별 세율(이월결손 램프, assumptions.tax_schedule)</t>
         </is>
       </c>
       <c r="E27" s="21">
@@ -10785,53 +10785,43 @@
         <f>IFERROR(subQ!AB19/subQ!AB18,"")</f>
         <v/>
       </c>
-      <c r="AC27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AD27" s="24">
-        <f>$D$54</f>
-        <v/>
+      <c r="AC27" s="31" t="n">
+        <v>0.006752619</v>
+      </c>
+      <c r="AD27" s="31" t="n">
+        <v>0.006752221</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
-      <c r="AF27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AG27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AH27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AI27" s="24">
-        <f>$D$54</f>
-        <v/>
+      <c r="AF27" s="31" t="n">
+        <v>0.033408184</v>
+      </c>
+      <c r="AG27" s="31" t="n">
+        <v>0.060064586</v>
+      </c>
+      <c r="AH27" s="31" t="n">
+        <v>0.086719712</v>
+      </c>
+      <c r="AI27" s="31" t="n">
+        <v>0.113376851</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
-      <c r="AK27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AL27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AM27" s="24">
-        <f>$D$54</f>
-        <v/>
-      </c>
-      <c r="AN27" s="24">
-        <f>$D$54</f>
-        <v/>
+      <c r="AK27" s="31" t="n">
+        <v>0.140031553</v>
+      </c>
+      <c r="AL27" s="31" t="n">
+        <v>0.166688023</v>
+      </c>
+      <c r="AM27" s="31" t="n">
+        <v>0.193344027</v>
+      </c>
+      <c r="AN27" s="31" t="n">
+        <v>0.219999898</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11226,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.010258093</v>
+        <v>-0.016425706</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.002290663</v>
+        <v>-0.000236324</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.001835503</v>
+        <v>0.001785977</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.006723585</v>
+        <v>-2.8442e-05</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.009416603000000001</v>
+        <v>-0.011250797</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.001059672</v>
+        <v>0.001146071</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.015296469</v>
+        <v>-0.00272848</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>2.892e-06</v>
+        <v>-0.005292611</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.007072188</v>
+        <v>-0.002267233</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.000322071</v>
+        <v>-0.0055904</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11354,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010822672</v>
+        <v>-0.010652692</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.010869208</v>
+        <v>-0.008852317</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.003668361</v>
+        <v>0.005879843</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.000835822</v>
+        <v>0.000577546</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.004684027</v>
+        <v>-0.00722992</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.006295407</v>
+        <v>-0.002289838</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.005639676</v>
+        <v>-0.004323726</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.00731985</v>
+        <v>-0.005487749</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.005802572</v>
+        <v>0.001393514</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.000600178</v>
+        <v>-0.000801439</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11610,36 +11600,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>-0.07035767800000001</v>
+        <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.076894676</v>
+        <v>-0.104625896</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.086352075</v>
+        <v>-0.114720877</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.101557743</v>
+        <v>-0.132685072</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.12319745</v>
+        <v>-0.159727465</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.153063154</v>
+        <v>-0.199177033</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.196655735</v>
+        <v>-0.261132455</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.194383282</v>
+        <v>-0.268153915</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.187101107</v>
+        <v>-0.271126921</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.257085316</v>
+        <v>-0.406236756</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11738,36 +11728,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.211510435</v>
+        <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.177380238</v>
+        <v>0.197410223</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.156176703</v>
+        <v>0.161858113</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.145148039</v>
+        <v>0.14263996</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.138142842</v>
+        <v>0.13033653</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.132221585</v>
+        <v>0.12081983</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.127074355</v>
+        <v>0.113177612</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.089528094</v>
+        <v>0.07714112100000001</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.063718688</v>
+        <v>0.052993377</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.066907912</v>
+        <v>0.054960976</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12464,36 +12454,36 @@
         <v/>
       </c>
       <c r="AC40" s="29" t="n">
-        <v>26530.920974</v>
+        <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>27028.508064</v>
+        <v>29205.238064</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>27005.871358</v>
+        <v>29125.601358</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>27015.173461</v>
+        <v>29158.443461</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>27024.579897</v>
+        <v>29191.409897</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>27024.574955</v>
+        <v>29191.404955</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>27015.173973</v>
+        <v>29158.453973</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13189.98406</v>
+        <v>15333.25406</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>863.478631</v>
+        <v>3030.318631</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>863.570783</v>
+        <v>3030.400783</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12510,7 +12500,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>매출조선신규 (forecast_panel base 신규수주 매출, 억원 — 가정)</t>
+          <t>매출조선신규 (forecast_panel base · 공시 상계 신규수주 매출, 억원 — 가정)</t>
         </is>
       </c>
       <c r="E41" s="26">
@@ -12613,39 +12603,39 @@
         <v>0</v>
       </c>
       <c r="AD41" s="29" t="n">
-        <v>525.42</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="30">
         <f>subQ!AE39</f>
         <v/>
       </c>
       <c r="AF41" s="29" t="n">
+        <v>525.42</v>
+      </c>
+      <c r="AG41" s="29" t="n">
         <v>1989.58</v>
       </c>
-      <c r="AG41" s="29" t="n">
+      <c r="AH41" s="29" t="n">
         <v>4224.28</v>
       </c>
-      <c r="AH41" s="29" t="n">
+      <c r="AI41" s="29" t="n">
         <v>7061.37</v>
-      </c>
-      <c r="AI41" s="29" t="n">
-        <v>10332.65</v>
       </c>
       <c r="AJ41" s="30">
         <f>subQ!AJ39</f>
         <v/>
       </c>
       <c r="AK41" s="29" t="n">
+        <v>10332.65</v>
+      </c>
+      <c r="AL41" s="29" t="n">
         <v>13869.95</v>
       </c>
-      <c r="AL41" s="29" t="n">
+      <c r="AM41" s="29" t="n">
         <v>17505.09</v>
       </c>
-      <c r="AM41" s="29" t="n">
+      <c r="AN41" s="29" t="n">
         <v>21069.91</v>
-      </c>
-      <c r="AN41" s="29" t="n">
-        <v>24396.21</v>
       </c>
       <c r="AO41" s="30">
         <f>subQ!AO39</f>
@@ -12765,42 +12755,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.118831519</v>
+        <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007673</v>
+        <v>0.119007467</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230666</v>
+        <v>0.120230675</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882719</v>
+        <v>0.120882774</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881113</v>
+        <v>0.120881153</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893216</v>
+        <v>0.120893227</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120792971</v>
+        <v>0.120792928</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799723</v>
+        <v>0.120799659</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869733</v>
+        <v>0.120869848</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890219</v>
+        <v>0.120890176</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13420,11 +13410,11 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.22000029432375</v>
+        <v>0.0068</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.22) · 최근 12분기 유효세율 -42.9% 가 5~27% 밖; 세전 &gt; 0 분기 중위 0.7% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>참고(연결 안 됨: 이월결손 램프(assumptions.tax_schedule, 0.68%→22%) — 분기별 세율 드라이버 행 사용) — 모델 assumptions 값(시작 0.68% → terminal 22%, 2026Q4 까지 유지 → 2027Q1~2028Q4 선형 램프 — 분기별 값은 2절 drv:법인세비용 행) · 최근 8분기 중 세전 &gt; 0 인 7분기(2024Q4~2026Q2) 법인세/세전 중위 0.7%·최근 4분기 중위 -1.2% 가 모두 5% 미만 → 이월결손 공제 중으로 보고 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -13459,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559126709828072</v>
+        <v>0.05559124419752796</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13498,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999655956080019</v>
+        <v>0.9999654830113993</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13537,11 +13527,11 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.07201634856510408</v>
+        <v>0.05777805522130511</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.072)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0578)</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -13576,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568140706331503</v>
+        <v>0.03568173077088636</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14017,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15268,10 +15258,54 @@
       <c r="K16" s="37" t="n">
         <v>40246.06</v>
       </c>
-      <c r="P16" s="9" t="n"/>
-      <c r="U16" s="9" t="n"/>
-      <c r="Z16" s="9" t="n"/>
-      <c r="AB16" s="5" t="n"/>
+      <c r="M16" s="18" t="n">
+        <v>39272.25</v>
+      </c>
+      <c r="N16" s="18" t="n">
+        <v>40704.47</v>
+      </c>
+      <c r="O16" s="18" t="n">
+        <v>39489.68</v>
+      </c>
+      <c r="P16" s="37" t="n">
+        <v>39489.68</v>
+      </c>
+      <c r="Q16" s="18" t="n">
+        <v>41142.97</v>
+      </c>
+      <c r="R16" s="18" t="n">
+        <v>80916.17999999999</v>
+      </c>
+      <c r="S16" s="18" t="n">
+        <v>189040.92</v>
+      </c>
+      <c r="T16" s="18" t="n">
+        <v>254635.47</v>
+      </c>
+      <c r="U16" s="37" t="n">
+        <v>254635.47</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>254224.05</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <v>268713.11</v>
+      </c>
+      <c r="X16" s="18" t="n">
+        <v>224837.95</v>
+      </c>
+      <c r="Y16" s="18" t="n">
+        <v>190795.74</v>
+      </c>
+      <c r="Z16" s="37" t="n">
+        <v>190795.74</v>
+      </c>
+      <c r="AA16" s="18" t="n">
+        <v>258426.71</v>
+      </c>
+      <c r="AB16" s="19" t="n">
+        <v>258768.03</v>
+      </c>
       <c r="AC16" s="10" t="n"/>
       <c r="AD16" s="10" t="n"/>
       <c r="AE16" s="11" t="n"/>
@@ -15320,52 +15354,52 @@
         <v>312265.32</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>241247.48</v>
+        <v>280519.73</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>207003.76</v>
+        <v>247708.23</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>91452.45</v>
+        <v>130942.13</v>
       </c>
       <c r="P17" s="37" t="n">
-        <v>91452.45</v>
+        <v>130942.13</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>147059.43</v>
+        <v>188202.4</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>263137.22</v>
+        <v>344053.4</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>165753.26</v>
+        <v>354794.18</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>361937.82</v>
+        <v>616573.29</v>
       </c>
       <c r="U17" s="37" t="n">
-        <v>361937.82</v>
+        <v>616573.29</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>340494.45</v>
+        <v>594718.5</v>
       </c>
       <c r="W17" s="18" t="n">
-        <v>396522.9</v>
+        <v>665236.01</v>
       </c>
       <c r="X17" s="18" t="n">
-        <v>488038.93</v>
+        <v>712876.88</v>
       </c>
       <c r="Y17" s="18" t="n">
-        <v>1005262.48</v>
+        <v>1196058.22</v>
       </c>
       <c r="Z17" s="37" t="n">
-        <v>1005262.48</v>
+        <v>1196058.22</v>
       </c>
       <c r="AA17" s="18" t="n">
-        <v>1278986.72</v>
+        <v>1537413.43</v>
       </c>
       <c r="AB17" s="19" t="n">
-        <v>1344249.3</v>
+        <v>1603017.33</v>
       </c>
       <c r="AC17" s="10" t="n"/>
       <c r="AD17" s="10" t="n"/>
@@ -17355,46 +17389,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>장기파생상품부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>393.23</v>
+        <v>61499.05</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>284.35</v>
+        <v>56743.12</v>
+      </c>
+      <c r="I40" s="18" t="n">
+        <v>53365.03</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>151.85</v>
-      </c>
-      <c r="P40" s="9" t="n"/>
+        <v>44450.98</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>55958.79</v>
+      </c>
+      <c r="N40" s="18" t="n">
+        <v>55011.27</v>
+      </c>
+      <c r="O40" s="18" t="n">
+        <v>51346.2</v>
+      </c>
+      <c r="P40" s="37" t="n">
+        <v>51346.2</v>
+      </c>
+      <c r="Q40" s="18" t="n">
+        <v>50602.76</v>
+      </c>
+      <c r="R40" s="18" t="n">
+        <v>42414.97</v>
+      </c>
       <c r="S40" s="18" t="n">
-        <v>2285.84</v>
-      </c>
-      <c r="U40" s="9" t="n"/>
+        <v>37540.68</v>
+      </c>
+      <c r="T40" s="18" t="n">
+        <v>98270.13</v>
+      </c>
+      <c r="U40" s="37" t="n">
+        <v>98270.13</v>
+      </c>
+      <c r="V40" s="18" t="n">
+        <v>100806.86</v>
+      </c>
+      <c r="W40" s="18" t="n">
+        <v>97641.45</v>
+      </c>
+      <c r="X40" s="18" t="n">
+        <v>94814.23</v>
+      </c>
       <c r="Y40" s="18" t="n">
-        <v>4878.03</v>
+        <v>93427.17</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>4878.03</v>
+        <v>93427.17</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>73775.64999999999</v>
+        <v>89058.33</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>112763.85</v>
+        <v>109164.2</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -17416,46 +17484,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>393.23</v>
+        <v>61499.05</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>284.35</v>
+        <v>56743.12</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>53365.03</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>151.85</v>
-      </c>
-      <c r="P41" s="9" t="n"/>
+        <v>44450.98</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <v>55958.79</v>
+      </c>
+      <c r="N41" s="18" t="n">
+        <v>55011.27</v>
+      </c>
+      <c r="O41" s="18" t="n">
+        <v>51346.2</v>
+      </c>
+      <c r="P41" s="37" t="n">
+        <v>51346.2</v>
+      </c>
+      <c r="Q41" s="18" t="n">
+        <v>50602.76</v>
+      </c>
+      <c r="R41" s="18" t="n">
+        <v>42414.97</v>
+      </c>
       <c r="S41" s="18" t="n">
-        <v>2285.84</v>
-      </c>
-      <c r="U41" s="9" t="n"/>
+        <v>37540.68</v>
+      </c>
+      <c r="T41" s="18" t="n">
+        <v>98270.13</v>
+      </c>
+      <c r="U41" s="37" t="n">
+        <v>98270.13</v>
+      </c>
+      <c r="V41" s="18" t="n">
+        <v>100806.86</v>
+      </c>
+      <c r="W41" s="18" t="n">
+        <v>97641.45</v>
+      </c>
+      <c r="X41" s="18" t="n">
+        <v>94814.23</v>
+      </c>
       <c r="Y41" s="18" t="n">
-        <v>4878.03</v>
+        <v>93427.17</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>4878.03</v>
+        <v>93427.17</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>73775.64999999999</v>
+        <v>89058.33</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>221928.05</v>
+        <v>149966.01</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -17477,80 +17579,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>63891.94</v>
+        <v>62229.92</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>63891.94</v>
+        <v>62229.92</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>63929.46</v>
+        <v>61892.28</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>77221.08</v>
+        <v>57027.47</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>41342.46</v>
+        <v>53365.03</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>118975.5</v>
+        <v>48674.54</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>118975.5</v>
+        <v>48674.54</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>119325.08</v>
+        <v>44602.83</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>128397.52</v>
+        <v>55958.79</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>141772.34</v>
+        <v>55011.27</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>19851.73</v>
+        <v>51346.2</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>19851.73</v>
+        <v>51346.2</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>20093.29</v>
+        <v>50602.76</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>20263.09</v>
+        <v>42414.97</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>19285.18</v>
+        <v>39826.52</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>22814.53</v>
+        <v>98270.13</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>22814.53</v>
+        <v>98270.13</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>23560.75</v>
+        <v>100806.86</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>23391.38</v>
+        <v>97641.45</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>22733.81</v>
+        <v>94814.23</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>34406.02</v>
+        <v>98305.2</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>34406.02</v>
+        <v>98305.2</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>40774.95</v>
+        <v>162833.98</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>37842.67</v>
+        <v>221928.05</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -17572,80 +17674,46 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>장기파생상품부채</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>8405626.1</v>
+        <v>1062.99</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>8405626.1</v>
+        <v>1062.99</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>9032707.380000001</v>
+        <v>393.23</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>10474077.89</v>
-      </c>
-      <c r="I43" s="18" t="n">
-        <v>11600483.55</v>
+        <v>284.35</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>11490693.37</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>11490693.37</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>11690042.34</v>
-      </c>
-      <c r="M43" s="18" t="n">
-        <v>11308538.51</v>
-      </c>
-      <c r="N43" s="18" t="n">
-        <v>10595985.33</v>
-      </c>
-      <c r="O43" s="18" t="n">
-        <v>9632615.57</v>
-      </c>
-      <c r="P43" s="37" t="n">
-        <v>9632615.57</v>
-      </c>
-      <c r="Q43" s="18" t="n">
-        <v>10531119.15</v>
-      </c>
-      <c r="R43" s="18" t="n">
-        <v>11890725.15</v>
-      </c>
+        <v>151.85</v>
+      </c>
+      <c r="P43" s="9" t="n"/>
       <c r="S43" s="18" t="n">
-        <v>12186230.97</v>
-      </c>
-      <c r="T43" s="18" t="n">
-        <v>12980459.27</v>
-      </c>
-      <c r="U43" s="37" t="n">
-        <v>12980459.27</v>
-      </c>
-      <c r="V43" s="18" t="n">
-        <v>13089100.94</v>
-      </c>
-      <c r="W43" s="18" t="n">
-        <v>13077936.43</v>
-      </c>
-      <c r="X43" s="18" t="n">
-        <v>13057869.04</v>
-      </c>
+        <v>2285.84</v>
+      </c>
+      <c r="U43" s="9" t="n"/>
       <c r="Y43" s="18" t="n">
-        <v>13965907.02</v>
+        <v>4878.03</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>13965907.02</v>
+        <v>4878.03</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>13970574.68</v>
+        <v>73775.64999999999</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>12617974.51</v>
+        <v>112763.85</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -17667,80 +17735,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>2217583.45</v>
+        <v>63891.94</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>2217583.45</v>
+        <v>63891.94</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>1726558.87</v>
+        <v>63929.46</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>1548380.96</v>
+        <v>77221.08</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>898685.87</v>
+        <v>41342.46</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>744971.9300000001</v>
+        <v>118975.5</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>744971.9300000001</v>
+        <v>118975.5</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>629060.1</v>
+        <v>119325.08</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>2332207.05</v>
+        <v>128397.52</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>2669774.89</v>
+        <v>141772.34</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>4307452.65</v>
+        <v>19851.73</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>4307452.65</v>
+        <v>19851.73</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>4358727.71</v>
+        <v>20093.29</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>4332926.74</v>
+        <v>20263.09</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>4176003.15</v>
+        <v>19285.18</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>4858676.07</v>
+        <v>22814.53</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>4858676.07</v>
+        <v>22814.53</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>5083866.41</v>
+        <v>23560.75</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>5221010.51</v>
+        <v>23391.38</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>5471256.51</v>
+        <v>22733.81</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>6170251.54</v>
+        <v>34406.02</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>6170251.54</v>
+        <v>34406.02</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>6821190.27</v>
+        <v>40774.95</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>7523412.2</v>
+        <v>37842.67</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -17762,80 +17830,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>541453.34</v>
+        <v>8405626.1</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>541453.34</v>
+        <v>8405626.1</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>541453.34</v>
+        <v>9032707.380000001</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>541453.34</v>
+        <v>10474077.89</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>541453.34</v>
+        <v>11600483.55</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>541453.34</v>
+        <v>11490693.37</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>541453.34</v>
+        <v>11490693.37</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>541453.34</v>
+        <v>11690042.34</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>1089366.99</v>
+        <v>11308538.51</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>1089366.99</v>
+        <v>10595985.33</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>1536794.49</v>
+        <v>9632615.57</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>1536794.49</v>
+        <v>9632615.57</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>1536794.49</v>
+        <v>10531119.15</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1536794.49</v>
+        <v>11890725.15</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>12186230.97</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>12980459.27</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>1537066.97</v>
+        <v>12980459.27</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>13089100.94</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>13077936.43</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>13057869.04</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>13965907.02</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>1537066.97</v>
+        <v>13965907.02</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>1537066.97</v>
+        <v>13970574.68</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>1537066.97</v>
+        <v>12617974.51</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -17857,80 +17925,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>16929.21</v>
+        <v>2217583.45</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>16929.21</v>
+        <v>2217583.45</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>16929.21</v>
+        <v>1726558.87</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>16929.21</v>
+        <v>1548380.96</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>16929.21</v>
+        <v>898685.87</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>16929.21</v>
+        <v>744971.9300000001</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>16929.21</v>
+        <v>744971.9300000001</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>16929.21</v>
+        <v>629060.1</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>1600761.65</v>
+        <v>2332207.05</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>1707154.89</v>
+        <v>2669774.89</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>2740229.78</v>
+        <v>4307452.65</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>2740229.78</v>
+        <v>4307452.65</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>111751.88</v>
+        <v>4358727.71</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>111751.88</v>
+        <v>4332926.74</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>117591.48</v>
+        <v>4176003.15</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>118688.52</v>
+        <v>4858676.07</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>118688.52</v>
+        <v>4858676.07</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>131643.11</v>
+        <v>5083866.41</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>149889.9</v>
+        <v>5221010.51</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>153434.15</v>
+        <v>5471256.51</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>181868.13</v>
+        <v>6170251.54</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>181868.13</v>
+        <v>6170251.54</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>207048.01</v>
+        <v>6821190.27</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>209082.59</v>
+        <v>7523412.2</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -17952,80 +18020,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2660477.05</v>
+        <v>541453.34</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>2660477.05</v>
+        <v>541453.34</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>2662471.19</v>
+        <v>541453.34</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>2661141.31</v>
+        <v>541453.34</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>2613833.78</v>
+        <v>541453.34</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>2887300.37</v>
+        <v>541453.34</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>2887300.37</v>
+        <v>541453.34</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2892892.83</v>
+        <v>541453.34</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>2339632.56</v>
+        <v>1089366.99</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>2339632.56</v>
+        <v>1089366.99</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>2339632.56</v>
+        <v>1536794.49</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>2339632.56</v>
+        <v>1536794.49</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>2341308.4</v>
+        <v>1536794.49</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>2344138.92</v>
+        <v>1536794.49</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>2339288.79</v>
+        <v>1537066.97</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>2334380.16</v>
+        <v>1537066.97</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>2334176.3</v>
+        <v>1537066.97</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -18047,80 +18115,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-1001276.15</v>
+        <v>16929.21</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>-1001276.15</v>
+        <v>16929.21</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-1494294.87</v>
+        <v>16929.21</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-1671142.89</v>
+        <v>16929.21</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-2273530.45</v>
+        <v>16929.21</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-2700710.99</v>
+        <v>16929.21</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>-2700710.99</v>
+        <v>16929.21</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-2822215.29</v>
+        <v>16929.21</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-3256684.53</v>
+        <v>1600761.65</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-3030709.54</v>
+        <v>1707154.89</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-2868157.13</v>
+        <v>2740229.78</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>-2868157.13</v>
+        <v>2740229.78</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>-196345.48</v>
+        <v>111751.88</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>-230551.14</v>
+        <v>111751.88</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>-311959.83</v>
+        <v>117591.48</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>236448.28</v>
+        <v>118688.52</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>236448.28</v>
+        <v>118688.52</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>444624.8</v>
+        <v>131643.11</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>585536.5699999999</v>
+        <v>149889.9</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>846227.71</v>
+        <v>153434.15</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>1551926.23</v>
+        <v>181868.13</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>1551926.23</v>
+        <v>181868.13</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>2031007.62</v>
+        <v>207048.01</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>2703669.86</v>
+        <v>209082.59</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -18142,80 +18210,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>2217583.45</v>
+        <v>2660477.05</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>2217583.45</v>
+        <v>2660477.05</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>1726558.87</v>
+        <v>2662471.19</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>1548380.96</v>
+        <v>2661141.31</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>898685.87</v>
+        <v>2613833.78</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>744971.9300000001</v>
+        <v>2887300.37</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>744971.9300000001</v>
+        <v>2887300.37</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>629060.1</v>
+        <v>2892892.83</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>2332207.05</v>
+        <v>2339632.56</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>2673777.83</v>
+        <v>2339632.56</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>4312157.12</v>
+        <v>2339632.56</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>4312157.12</v>
+        <v>2339632.56</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>4363320.98</v>
+        <v>2341308.4</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>4337656.77</v>
+        <v>2344138.92</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>4180771.58</v>
+        <v>2339288.79</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>4863349.89</v>
+        <v>2339288.79</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>4863349.89</v>
+        <v>2339288.79</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>5088572.51</v>
+        <v>2339288.79</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>5225776.43</v>
+        <v>2339288.79</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>5476057.45</v>
+        <v>2339288.79</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>6175007</v>
+        <v>2339288.79</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>6175007</v>
+        <v>2339288.79</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>6825972.78</v>
+        <v>2334380.16</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>7528212.29</v>
+        <v>2334176.3</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -18237,80 +18305,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>10623209.56</v>
+        <v>-1001276.15</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>10623209.56</v>
+        <v>-1001276.15</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>10759266.24</v>
+        <v>-1494294.87</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>12022458.85</v>
+        <v>-1671142.89</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>12499169.42</v>
+        <v>-2273530.45</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>12235665.3</v>
+        <v>-2700710.99</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>12235665.3</v>
+        <v>-2700710.99</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>12319102.44</v>
+        <v>-2822215.29</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>13640745.56</v>
+        <v>-3256684.53</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>13269763.16</v>
+        <v>-3030709.54</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>13944772.69</v>
+        <v>-2868157.13</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>13944772.69</v>
+        <v>-2868157.13</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>14894440.13</v>
+        <v>-196345.48</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>16228381.92</v>
+        <v>-230551.14</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>16367002.54</v>
+        <v>-311959.83</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>17843809.16</v>
+        <v>236448.28</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>17843809.16</v>
+        <v>236448.28</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>18177673.45</v>
+        <v>444624.8</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>18303712.87</v>
+        <v>585536.5699999999</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>18533926.49</v>
+        <v>846227.71</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>20140914.01</v>
+        <v>1551926.23</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>20140914.01</v>
+        <v>1551926.23</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>20796547.46</v>
+        <v>2031007.62</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>20146186.8</v>
+        <v>2703669.86</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -18332,80 +18400,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>2701697.29</v>
+        <v>2217583.45</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>2701697.29</v>
+        <v>2217583.45</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>2881148.63</v>
+        <v>1726558.87</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>2979867.71</v>
+        <v>1548380.96</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>3034732.14</v>
+        <v>898685.87</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>2687244.57</v>
+        <v>744971.9300000001</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>2687244.57</v>
+        <v>744971.9300000001</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>3077978.85</v>
+        <v>629060.1</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>2340008.94</v>
+        <v>2332207.05</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2314969.15</v>
+        <v>2673777.83</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>2191192.37</v>
+        <v>4312157.12</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>2191192.37</v>
+        <v>4312157.12</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>3428135.91</v>
+        <v>4363320.98</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>4269419.09</v>
+        <v>4337656.77</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>4888456.28</v>
+        <v>4180771.58</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>5265870.07</v>
+        <v>4863349.89</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>5265870.07</v>
+        <v>4863349.89</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>5520669.77</v>
+        <v>5088572.51</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>5028215.91</v>
+        <v>5225776.43</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>5172282.03</v>
+        <v>5476057.45</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>5646344.95</v>
+        <v>6175007</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>5646344.95</v>
+        <v>6175007</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>6142955.88</v>
+        <v>6825972.78</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>6037492.95</v>
+        <v>7528212.29</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -18427,80 +18495,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>612064.89</v>
+        <v>10623209.56</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>612064.89</v>
+        <v>10623209.56</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>1439819.38</v>
+        <v>10759266.24</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>1704193.45</v>
+        <v>12022458.85</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>1884151</v>
+        <v>12499169.42</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1535268.77</v>
+        <v>12235665.3</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>1535268.77</v>
+        <v>12235665.3</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>2807861.54</v>
+        <v>12319102.44</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>775518.5600000001</v>
+        <v>13640745.56</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>1336350.81</v>
+        <v>13269763.16</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>391884.62</v>
+        <v>13944772.69</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>391884.62</v>
+        <v>13944772.69</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>1779332</v>
+        <v>14894440.13</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>2444662.34</v>
+        <v>16228381.92</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>3871842.93</v>
+        <v>16367002.54</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>4677610.33</v>
+        <v>17843809.16</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>4677610.33</v>
+        <v>17843809.16</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>4547428.46</v>
+        <v>18177673.45</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>3990567.4</v>
+        <v>18303712.87</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>4742781.47</v>
+        <v>18533926.49</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>4867873.79</v>
+        <v>20140914.01</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>4867873.79</v>
+        <v>20140914.01</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>5072723.61</v>
+        <v>20796547.46</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>4530461.77</v>
+        <v>20146186.8</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -18522,80 +18590,80 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>2322797.1</v>
+        <v>2701697.29</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>2322797.1</v>
+        <v>2701697.29</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>1669671.45</v>
+        <v>2881148.63</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>1353697.67</v>
+        <v>2979867.71</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>1190804.13</v>
+        <v>3034732.14</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>1192221.86</v>
+        <v>2687244.57</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>1192221.86</v>
+        <v>2687244.57</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>270117.31</v>
+        <v>3077978.85</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>1564490.38</v>
+        <v>2340008.94</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>978618.34</v>
+        <v>2314969.15</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>1799307.75</v>
+        <v>2191192.37</v>
       </c>
       <c r="P53" s="37" t="n">
-        <v>1799307.75</v>
+        <v>2191192.37</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>1648803.91</v>
+        <v>3428135.91</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1824756.75</v>
+        <v>4269419.09</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>1016613.35</v>
+        <v>4888456.28</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>588259.74</v>
+        <v>5265870.07</v>
       </c>
       <c r="U53" s="37" t="n">
-        <v>588259.74</v>
+        <v>5265870.07</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>973241.3100000001</v>
+        <v>5520669.77</v>
       </c>
       <c r="W53" s="18" t="n">
-        <v>1037648.51</v>
+        <v>5028215.91</v>
       </c>
       <c r="X53" s="18" t="n">
-        <v>429500.56</v>
+        <v>5172282.03</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>778471.16</v>
+        <v>5646344.95</v>
       </c>
       <c r="Z53" s="37" t="n">
-        <v>778471.16</v>
+        <v>5646344.95</v>
       </c>
       <c r="AA53" s="18" t="n">
-        <v>1070232.27</v>
+        <v>6142955.88</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>1507031.18</v>
+        <v>6037492.95</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -18617,32 +18685,81 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>기타유동금융부채</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="n"/>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>612064.89</v>
+      </c>
+      <c r="F54" s="37" t="n">
+        <v>612064.89</v>
+      </c>
+      <c r="G54" s="18" t="n">
+        <v>1439819.38</v>
+      </c>
       <c r="H54" s="18" t="n">
-        <v>25751.28</v>
+        <v>1704193.45</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>50921.84</v>
+        <v>1884151</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>31440.48</v>
+        <v>1535268.77</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>31440.48</v>
+        <v>1535268.77</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>28739.37</v>
+        <v>2807861.54</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>16702.79</v>
-      </c>
-      <c r="P54" s="9" t="n"/>
-      <c r="U54" s="9" t="n"/>
-      <c r="Z54" s="9" t="n"/>
-      <c r="AB54" s="5" t="n"/>
+        <v>775518.5600000001</v>
+      </c>
+      <c r="N54" s="18" t="n">
+        <v>1336350.81</v>
+      </c>
+      <c r="O54" s="18" t="n">
+        <v>391884.62</v>
+      </c>
+      <c r="P54" s="37" t="n">
+        <v>391884.62</v>
+      </c>
+      <c r="Q54" s="18" t="n">
+        <v>1779332</v>
+      </c>
+      <c r="R54" s="18" t="n">
+        <v>2444662.34</v>
+      </c>
+      <c r="S54" s="18" t="n">
+        <v>3871842.93</v>
+      </c>
+      <c r="T54" s="18" t="n">
+        <v>4677610.33</v>
+      </c>
+      <c r="U54" s="37" t="n">
+        <v>4677610.33</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>4547428.46</v>
+      </c>
+      <c r="W54" s="18" t="n">
+        <v>3990567.4</v>
+      </c>
+      <c r="X54" s="18" t="n">
+        <v>4742781.47</v>
+      </c>
+      <c r="Y54" s="18" t="n">
+        <v>4867873.79</v>
+      </c>
+      <c r="Z54" s="37" t="n">
+        <v>4867873.79</v>
+      </c>
+      <c r="AA54" s="18" t="n">
+        <v>5072723.61</v>
+      </c>
+      <c r="AB54" s="19" t="n">
+        <v>4530461.77</v>
+      </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
       <c r="AE54" s="11" t="n"/>
@@ -18663,47 +18780,80 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>2322797.1</v>
+      </c>
+      <c r="F55" s="37" t="n">
+        <v>2322797.1</v>
+      </c>
+      <c r="G55" s="18" t="n">
+        <v>1669671.45</v>
+      </c>
       <c r="H55" s="18" t="n">
-        <v>25751.28</v>
+        <v>1353697.67</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>50921.84</v>
+        <v>1190804.13</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>31440.48</v>
+        <v>1192221.86</v>
       </c>
       <c r="K55" s="37" t="n">
-        <v>31440.48</v>
+        <v>1192221.86</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>28739.37</v>
+        <v>270117.31</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>16702.79</v>
-      </c>
-      <c r="P55" s="9" t="n"/>
-      <c r="U55" s="9" t="n"/>
+        <v>1603762.63</v>
+      </c>
+      <c r="N55" s="18" t="n">
+        <v>1019322.81</v>
+      </c>
+      <c r="O55" s="18" t="n">
+        <v>1838797.43</v>
+      </c>
+      <c r="P55" s="37" t="n">
+        <v>1838797.43</v>
+      </c>
+      <c r="Q55" s="18" t="n">
+        <v>1689946.88</v>
+      </c>
+      <c r="R55" s="18" t="n">
+        <v>1905672.93</v>
+      </c>
+      <c r="S55" s="18" t="n">
+        <v>1205654.27</v>
+      </c>
+      <c r="T55" s="18" t="n">
+        <v>842895.21</v>
+      </c>
+      <c r="U55" s="37" t="n">
+        <v>842895.21</v>
+      </c>
+      <c r="V55" s="18" t="n">
+        <v>1227465.36</v>
+      </c>
       <c r="W55" s="18" t="n">
-        <v>155113.83</v>
+        <v>1306361.62</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>142423.97</v>
+        <v>654338.51</v>
       </c>
       <c r="Y55" s="18" t="n">
-        <v>68957.10000000001</v>
+        <v>969266.9</v>
       </c>
       <c r="Z55" s="37" t="n">
-        <v>68957.10000000001</v>
+        <v>969266.9</v>
       </c>
       <c r="AA55" s="18" t="n">
-        <v>74104.37</v>
+        <v>1328658.98</v>
       </c>
       <c r="AB55" s="19" t="n">
-        <v>144534.63</v>
+        <v>1765799.21</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -18725,62 +18875,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>기타유동금융자산</t>
+          <t>기타유동금융부채</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
+      <c r="H56" s="18" t="n">
+        <v>25751.28</v>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>50921.84</v>
+      </c>
+      <c r="J56" s="18" t="n">
+        <v>31440.48</v>
+      </c>
+      <c r="K56" s="37" t="n">
+        <v>31440.48</v>
+      </c>
       <c r="L56" s="18" t="n">
-        <v>427146.69</v>
+        <v>28739.37</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>442305.34</v>
-      </c>
-      <c r="N56" s="18" t="n">
-        <v>112800.78</v>
-      </c>
-      <c r="O56" s="18" t="n">
-        <v>124947.86</v>
-      </c>
-      <c r="P56" s="37" t="n">
-        <v>124947.86</v>
-      </c>
-      <c r="Q56" s="18" t="n">
-        <v>135970.66</v>
-      </c>
-      <c r="R56" s="18" t="n">
-        <v>48489.08</v>
-      </c>
-      <c r="S56" s="18" t="n">
-        <v>20699.87</v>
-      </c>
-      <c r="T56" s="18" t="n">
-        <v>46003.53</v>
-      </c>
-      <c r="U56" s="37" t="n">
-        <v>46003.53</v>
-      </c>
-      <c r="V56" s="18" t="n">
-        <v>15219.09</v>
-      </c>
-      <c r="W56" s="18" t="n">
-        <v>9163.17</v>
-      </c>
-      <c r="X56" s="18" t="n">
-        <v>11472.76</v>
-      </c>
-      <c r="Y56" s="18" t="n">
-        <v>10204.24</v>
-      </c>
-      <c r="Z56" s="37" t="n">
-        <v>10204.24</v>
-      </c>
-      <c r="AA56" s="18" t="n">
-        <v>14360.34</v>
-      </c>
-      <c r="AB56" s="19" t="n">
-        <v>25464.24</v>
-      </c>
+        <v>16702.79</v>
+      </c>
+      <c r="P56" s="9" t="n"/>
+      <c r="U56" s="9" t="n"/>
+      <c r="Z56" s="9" t="n"/>
+      <c r="AB56" s="5" t="n"/>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
       <c r="AE56" s="11" t="n"/>
@@ -18801,58 +18921,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>단기금융부채</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
+      <c r="H57" s="18" t="n">
+        <v>25751.28</v>
+      </c>
+      <c r="I57" s="18" t="n">
+        <v>50921.84</v>
+      </c>
+      <c r="J57" s="18" t="n">
+        <v>31440.48</v>
+      </c>
+      <c r="K57" s="37" t="n">
+        <v>31440.48</v>
+      </c>
+      <c r="L57" s="18" t="n">
+        <v>28739.37</v>
+      </c>
       <c r="M57" s="18" t="n">
-        <v>713220.26</v>
-      </c>
-      <c r="N57" s="18" t="n">
-        <v>576236.23</v>
-      </c>
-      <c r="O57" s="18" t="n">
-        <v>526449.92</v>
-      </c>
-      <c r="P57" s="37" t="n">
-        <v>526449.92</v>
-      </c>
-      <c r="Q57" s="18" t="n">
-        <v>1713714.68</v>
-      </c>
-      <c r="R57" s="18" t="n">
-        <v>2519938.37</v>
-      </c>
-      <c r="S57" s="18" t="n">
-        <v>3179562.51</v>
-      </c>
-      <c r="T57" s="18" t="n">
-        <v>3237744.03</v>
-      </c>
-      <c r="U57" s="37" t="n">
-        <v>3237744.03</v>
-      </c>
-      <c r="V57" s="18" t="n">
-        <v>3371868.65</v>
-      </c>
+        <v>16702.79</v>
+      </c>
+      <c r="P57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
       <c r="W57" s="18" t="n">
-        <v>3030820.19</v>
+        <v>155113.83</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>3051187.29</v>
+        <v>142423.97</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>3300054.55</v>
+        <v>68957.10000000001</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>3300054.55</v>
+        <v>68957.10000000001</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>3529081.73</v>
+        <v>74104.37</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>3387397.65</v>
+        <v>144534.63</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -18874,41 +18983,61 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>기타유동금융자산</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
+      <c r="L58" s="18" t="n">
+        <v>427146.69</v>
+      </c>
       <c r="M58" s="18" t="n">
-        <v>1626788.68</v>
-      </c>
-      <c r="P58" s="9" t="n"/>
+        <v>442305.34</v>
+      </c>
+      <c r="N58" s="18" t="n">
+        <v>112800.78</v>
+      </c>
+      <c r="O58" s="18" t="n">
+        <v>124947.86</v>
+      </c>
+      <c r="P58" s="37" t="n">
+        <v>124947.86</v>
+      </c>
+      <c r="Q58" s="18" t="n">
+        <v>135970.66</v>
+      </c>
+      <c r="R58" s="18" t="n">
+        <v>48489.08</v>
+      </c>
+      <c r="S58" s="18" t="n">
+        <v>20699.87</v>
+      </c>
       <c r="T58" s="18" t="n">
-        <v>2028126.04</v>
+        <v>46003.53</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>2028126.04</v>
+        <v>46003.53</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>2148801.12</v>
+        <v>15219.09</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>1997395.72</v>
+        <v>9163.17</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>2121094.74</v>
+        <v>11472.76</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>2346290.4</v>
+        <v>10204.24</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>2346290.4</v>
+        <v>10204.24</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>2613874.15</v>
+        <v>14360.34</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>2650095.3</v>
+        <v>25464.24</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -18930,58 +19059,58 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
       <c r="M59" s="18" t="n">
-        <v>559130.37</v>
+        <v>713220.26</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>564329.98</v>
+        <v>576236.23</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>558952.9399999999</v>
+        <v>526449.92</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>558952.9399999999</v>
+        <v>526449.92</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>565218.41</v>
+        <v>1713714.68</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>570792.59</v>
+        <v>2519938.37</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>494015.74</v>
+        <v>3179562.51</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>627183.51</v>
+        <v>3237744.03</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>627183.51</v>
+        <v>3237744.03</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>631242.74</v>
+        <v>3371868.65</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>609228.28</v>
+        <v>3030820.19</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>595238.89</v>
+        <v>3051187.29</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>560101.42</v>
+        <v>3300054.55</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>560101.42</v>
+        <v>3300054.55</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>711687.51</v>
+        <v>3529081.73</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>739416.48</v>
+        <v>3387397.65</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -19003,55 +19132,41 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>비지배주주지분</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
-      <c r="N60" s="18" t="n">
-        <v>4002.94</v>
-      </c>
-      <c r="O60" s="18" t="n">
-        <v>4704.47</v>
-      </c>
-      <c r="P60" s="37" t="n">
-        <v>4704.47</v>
-      </c>
-      <c r="Q60" s="18" t="n">
-        <v>4593.27</v>
-      </c>
-      <c r="R60" s="18" t="n">
-        <v>4730.03</v>
-      </c>
-      <c r="S60" s="18" t="n">
-        <v>4768.43</v>
-      </c>
+      <c r="M60" s="18" t="n">
+        <v>1626788.68</v>
+      </c>
+      <c r="P60" s="9" t="n"/>
       <c r="T60" s="18" t="n">
-        <v>4673.82</v>
+        <v>2028126.04</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>4673.82</v>
+        <v>2028126.04</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>4706.11</v>
+        <v>2148801.12</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>4765.92</v>
+        <v>1997395.72</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>4800.95</v>
+        <v>2121094.74</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>4755.45</v>
+        <v>2346290.4</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>4755.45</v>
+        <v>2346290.4</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>4782.51</v>
+        <v>2613874.15</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>4800.08</v>
+        <v>2650095.3</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -19073,33 +19188,58 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
+      <c r="M61" s="18" t="n">
+        <v>559130.37</v>
+      </c>
+      <c r="N61" s="18" t="n">
+        <v>564329.98</v>
+      </c>
+      <c r="O61" s="18" t="n">
+        <v>558952.9399999999</v>
+      </c>
+      <c r="P61" s="37" t="n">
+        <v>558952.9399999999</v>
+      </c>
+      <c r="Q61" s="18" t="n">
+        <v>565218.41</v>
+      </c>
+      <c r="R61" s="18" t="n">
+        <v>570792.59</v>
+      </c>
+      <c r="S61" s="18" t="n">
+        <v>494015.74</v>
+      </c>
+      <c r="T61" s="18" t="n">
+        <v>627183.51</v>
+      </c>
+      <c r="U61" s="37" t="n">
+        <v>627183.51</v>
+      </c>
       <c r="V61" s="18" t="n">
-        <v>85122.85000000001</v>
+        <v>631242.74</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>86777.56</v>
+        <v>609228.28</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>88520.34</v>
+        <v>595238.89</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>119161.33</v>
+        <v>560101.42</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>119161.33</v>
+        <v>560101.42</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>121099.73</v>
+        <v>711687.51</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>185016.91</v>
+        <v>739416.48</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -19121,26 +19261,56 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>비유동파생상품자산</t>
+          <t>비지배주주지분</t>
         </is>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="K62" s="9" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="U62" s="9" t="n"/>
+      <c r="N62" s="18" t="n">
+        <v>4002.94</v>
+      </c>
+      <c r="O62" s="18" t="n">
+        <v>4704.47</v>
+      </c>
+      <c r="P62" s="37" t="n">
+        <v>4704.47</v>
+      </c>
+      <c r="Q62" s="18" t="n">
+        <v>4593.27</v>
+      </c>
+      <c r="R62" s="18" t="n">
+        <v>4730.03</v>
+      </c>
+      <c r="S62" s="18" t="n">
+        <v>4768.43</v>
+      </c>
+      <c r="T62" s="18" t="n">
+        <v>4673.82</v>
+      </c>
+      <c r="U62" s="37" t="n">
+        <v>4673.82</v>
+      </c>
+      <c r="V62" s="18" t="n">
+        <v>4706.11</v>
+      </c>
       <c r="W62" s="18" t="n">
-        <v>12.81</v>
+        <v>4765.92</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>1418.5</v>
+        <v>4800.95</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>4864.26</v>
+        <v>4755.45</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>4864.26</v>
-      </c>
-      <c r="AB62" s="5" t="n"/>
+        <v>4755.45</v>
+      </c>
+      <c r="AA62" s="18" t="n">
+        <v>4782.51</v>
+      </c>
+      <c r="AB62" s="19" t="n">
+        <v>4800.08</v>
+      </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
       <c r="AE62" s="11" t="n"/>
@@ -19161,30 +19331,33 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>단기파생상품부채</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="K63" s="9" t="n"/>
       <c r="P63" s="9" t="n"/>
       <c r="U63" s="9" t="n"/>
+      <c r="V63" s="18" t="n">
+        <v>85122.85000000001</v>
+      </c>
       <c r="W63" s="18" t="n">
-        <v>155113.83</v>
+        <v>86777.56</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>142423.97</v>
+        <v>88520.34</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>68957.10000000001</v>
+        <v>119161.33</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>68957.10000000001</v>
+        <v>119161.33</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>74104.37</v>
+        <v>121099.73</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>103732.82</v>
+        <v>185016.91</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -19206,20 +19379,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>유동파생상품자산</t>
+          <t>비유동파생상품자산</t>
         </is>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="K64" s="9" t="n"/>
       <c r="P64" s="9" t="n"/>
       <c r="U64" s="9" t="n"/>
-      <c r="Z64" s="9" t="n"/>
-      <c r="AA64" s="18" t="n">
-        <v>11835.59</v>
-      </c>
-      <c r="AB64" s="19" t="n">
-        <v>14682.83</v>
-      </c>
+      <c r="W64" s="18" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="X64" s="18" t="n">
+        <v>1418.5</v>
+      </c>
+      <c r="Y64" s="18" t="n">
+        <v>4864.26</v>
+      </c>
+      <c r="Z64" s="37" t="n">
+        <v>4864.26</v>
+      </c>
+      <c r="AB64" s="5" t="n"/>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
       <c r="AE64" s="11" t="n"/>
@@ -19240,16 +19419,30 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>유동확정계약자산</t>
+          <t>단기파생상품부채</t>
         </is>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="K65" s="9" t="n"/>
       <c r="P65" s="9" t="n"/>
       <c r="U65" s="9" t="n"/>
-      <c r="Z65" s="9" t="n"/>
+      <c r="W65" s="18" t="n">
+        <v>155113.83</v>
+      </c>
+      <c r="X65" s="18" t="n">
+        <v>142423.97</v>
+      </c>
+      <c r="Y65" s="18" t="n">
+        <v>68957.10000000001</v>
+      </c>
+      <c r="Z65" s="37" t="n">
+        <v>68957.10000000001</v>
+      </c>
+      <c r="AA65" s="18" t="n">
+        <v>74104.37</v>
+      </c>
       <c r="AB65" s="19" t="n">
-        <v>46143.95</v>
+        <v>103732.82</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -19271,7 +19464,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
+          <t>유동파생상품자산</t>
         </is>
       </c>
       <c r="F66" s="9" t="n"/>
@@ -19279,8 +19472,11 @@
       <c r="P66" s="9" t="n"/>
       <c r="U66" s="9" t="n"/>
       <c r="Z66" s="9" t="n"/>
+      <c r="AA66" s="18" t="n">
+        <v>11835.59</v>
+      </c>
       <c r="AB66" s="19" t="n">
-        <v>40801.81</v>
+        <v>14682.83</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -19302,7 +19498,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>리스부채</t>
+          <t>유동확정계약자산</t>
         </is>
       </c>
       <c r="F67" s="9" t="n"/>
@@ -19311,7 +19507,7 @@
       <c r="U67" s="9" t="n"/>
       <c r="Z67" s="9" t="n"/>
       <c r="AB67" s="19" t="n">
-        <v>149966.01</v>
+        <v>46143.95</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -19333,7 +19529,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>유동리스부채</t>
         </is>
       </c>
       <c r="F68" s="9" t="n"/>
@@ -19342,7 +19538,7 @@
       <c r="U68" s="9" t="n"/>
       <c r="Z68" s="9" t="n"/>
       <c r="AB68" s="19" t="n">
-        <v>109164.2</v>
+        <v>40801.81</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -23834,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24990,10 +25186,54 @@
       <c r="K15" s="37" t="n">
         <v>40246.06</v>
       </c>
-      <c r="P15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="Z15" s="9" t="n"/>
-      <c r="AB15" s="5" t="n"/>
+      <c r="M15" s="18" t="n">
+        <v>39272.25</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>40653.63</v>
+      </c>
+      <c r="O15" s="18" t="n">
+        <v>39438.84</v>
+      </c>
+      <c r="P15" s="37" t="n">
+        <v>39438.84</v>
+      </c>
+      <c r="Q15" s="18" t="n">
+        <v>40492.13</v>
+      </c>
+      <c r="R15" s="18" t="n">
+        <v>51092.14</v>
+      </c>
+      <c r="S15" s="18" t="n">
+        <v>51684.41</v>
+      </c>
+      <c r="T15" s="18" t="n">
+        <v>55154.82</v>
+      </c>
+      <c r="U15" s="37" t="n">
+        <v>55154.82</v>
+      </c>
+      <c r="V15" s="18" t="n">
+        <v>53416.43</v>
+      </c>
+      <c r="W15" s="18" t="n">
+        <v>53394.9</v>
+      </c>
+      <c r="X15" s="18" t="n">
+        <v>54493.26</v>
+      </c>
+      <c r="Y15" s="18" t="n">
+        <v>54797.44</v>
+      </c>
+      <c r="Z15" s="37" t="n">
+        <v>54797.44</v>
+      </c>
+      <c r="AA15" s="18" t="n">
+        <v>54997.5</v>
+      </c>
+      <c r="AB15" s="19" t="n">
+        <v>54808.07</v>
+      </c>
       <c r="AC15" s="10" t="n"/>
       <c r="AD15" s="10" t="n"/>
       <c r="AE15" s="11" t="n"/>
@@ -25042,49 +25282,52 @@
         <v>312078.78</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>237733.03</v>
+        <v>277005.28</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>202982.23</v>
+        <v>243635.86</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>87209.37</v>
+        <v>126648.21</v>
       </c>
       <c r="P16" s="37" t="n">
-        <v>87209.37</v>
+        <v>126648.21</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>143325.39</v>
+        <v>183817.52</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>161122.66</v>
+        <v>212214.8</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>56010.89</v>
+        <v>107695.3</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>37718.5</v>
+        <v>92873.32000000001</v>
       </c>
       <c r="U16" s="37" t="n">
-        <v>37718.5</v>
+        <v>92873.32000000001</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>53416.43</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>12.81</v>
+        <v>53407.71</v>
       </c>
       <c r="X16" s="18" t="n">
-        <v>1418.5</v>
+        <v>55911.76</v>
       </c>
       <c r="Y16" s="18" t="n">
-        <v>4864.26</v>
+        <v>59661.7</v>
       </c>
       <c r="Z16" s="37" t="n">
-        <v>4864.26</v>
+        <v>59661.7</v>
       </c>
       <c r="AA16" s="18" t="n">
-        <v>75547.42999999999</v>
+        <v>130544.93</v>
       </c>
       <c r="AB16" s="19" t="n">
-        <v>108869.93</v>
+        <v>163678</v>
       </c>
       <c r="AC16" s="10" t="n"/>
       <c r="AD16" s="10" t="n"/>
@@ -26891,46 +27134,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>장기파생상품부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>393.23</v>
+        <v>61499.05</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>284.35</v>
+        <v>56743.12</v>
+      </c>
+      <c r="I38" s="18" t="n">
+        <v>53365.03</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>151.85</v>
-      </c>
-      <c r="P38" s="9" t="n"/>
+        <v>44450.98</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>55851.5</v>
+      </c>
+      <c r="N38" s="18" t="n">
+        <v>52719</v>
+      </c>
+      <c r="O38" s="18" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="P38" s="37" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="Q38" s="18" t="n">
+        <v>45868.28</v>
+      </c>
+      <c r="R38" s="18" t="n">
+        <v>38284.48</v>
+      </c>
       <c r="S38" s="18" t="n">
-        <v>2285.84</v>
-      </c>
-      <c r="U38" s="9" t="n"/>
+        <v>33941.18</v>
+      </c>
+      <c r="T38" s="18" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="U38" s="37" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="V38" s="18" t="n">
+        <v>91238.03999999999</v>
+      </c>
+      <c r="W38" s="18" t="n">
+        <v>89698.49000000001</v>
+      </c>
+      <c r="X38" s="18" t="n">
+        <v>87190.03</v>
+      </c>
       <c r="Y38" s="18" t="n">
-        <v>4878.03</v>
+        <v>80584.42</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>4878.03</v>
+        <v>80584.42</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>73775.64999999999</v>
+        <v>75718.56</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>112763.85</v>
+        <v>95057.7</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -26952,46 +27229,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>1062.99</v>
+        <v>61166.93</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>393.23</v>
+        <v>61499.05</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>284.35</v>
+        <v>56743.12</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>53365.03</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="K39" s="37" t="n">
-        <v>69.29000000000001</v>
+        <v>48605.25</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>151.85</v>
-      </c>
-      <c r="P39" s="9" t="n"/>
+        <v>44450.98</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <v>55851.5</v>
+      </c>
+      <c r="N39" s="18" t="n">
+        <v>52719</v>
+      </c>
+      <c r="O39" s="18" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="P39" s="37" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="Q39" s="18" t="n">
+        <v>45868.28</v>
+      </c>
+      <c r="R39" s="18" t="n">
+        <v>38284.48</v>
+      </c>
       <c r="S39" s="18" t="n">
-        <v>2285.84</v>
-      </c>
-      <c r="U39" s="9" t="n"/>
+        <v>33941.18</v>
+      </c>
+      <c r="T39" s="18" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="U39" s="37" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="V39" s="18" t="n">
+        <v>91238.03999999999</v>
+      </c>
+      <c r="W39" s="18" t="n">
+        <v>89698.49000000001</v>
+      </c>
+      <c r="X39" s="18" t="n">
+        <v>87190.03</v>
+      </c>
       <c r="Y39" s="18" t="n">
-        <v>4878.03</v>
+        <v>110804.24</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>4878.03</v>
+        <v>110804.24</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>73775.64999999999</v>
+        <v>75718.56</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>207821.55</v>
+        <v>126350.75</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -27013,43 +27324,81 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>60437.62</v>
+        <v>62229.92</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>60437.62</v>
+        <v>62229.92</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>60437.62</v>
+        <v>61892.28</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>73172.12</v>
+        <v>57027.47</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>36901.12</v>
+        <v>53365.03</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>118380.57</v>
+        <v>48674.54</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>118380.57</v>
+        <v>48674.54</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>118364.76</v>
+        <v>44602.83</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>127453.62</v>
+        <v>55851.5</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>127720.83</v>
-      </c>
-      <c r="P40" s="9" t="n"/>
-      <c r="U40" s="9" t="n"/>
-      <c r="Z40" s="9" t="n"/>
-      <c r="AB40" s="5" t="n"/>
+        <v>52719</v>
+      </c>
+      <c r="O40" s="18" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="P40" s="37" t="n">
+        <v>49361.21</v>
+      </c>
+      <c r="Q40" s="18" t="n">
+        <v>45868.28</v>
+      </c>
+      <c r="R40" s="18" t="n">
+        <v>38284.48</v>
+      </c>
+      <c r="S40" s="18" t="n">
+        <v>36227.02</v>
+      </c>
+      <c r="T40" s="18" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="U40" s="37" t="n">
+        <v>95156.12</v>
+      </c>
+      <c r="V40" s="18" t="n">
+        <v>91238.03999999999</v>
+      </c>
+      <c r="W40" s="18" t="n">
+        <v>89698.49000000001</v>
+      </c>
+      <c r="X40" s="18" t="n">
+        <v>87190.03</v>
+      </c>
+      <c r="Y40" s="18" t="n">
+        <v>85462.45</v>
+      </c>
+      <c r="Z40" s="37" t="n">
+        <v>85462.45</v>
+      </c>
+      <c r="AA40" s="18" t="n">
+        <v>149494.21</v>
+      </c>
+      <c r="AB40" s="19" t="n">
+        <v>207821.55</v>
+      </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
@@ -27070,80 +27419,46 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>장기파생상품부채</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>8313147.25</v>
+        <v>1062.99</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>8313147.25</v>
+        <v>1062.99</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>8942455.539999999</v>
+        <v>393.23</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>10375971.54</v>
-      </c>
-      <c r="I41" s="18" t="n">
-        <v>11486431.4</v>
+        <v>284.35</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>11402970.67</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>11402970.67</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>11590802.07</v>
-      </c>
-      <c r="M41" s="18" t="n">
-        <v>11217394.67</v>
-      </c>
-      <c r="N41" s="18" t="n">
-        <v>10404833.09</v>
-      </c>
-      <c r="O41" s="18" t="n">
-        <v>9458216.800000001</v>
-      </c>
-      <c r="P41" s="37" t="n">
-        <v>9458216.800000001</v>
-      </c>
-      <c r="Q41" s="18" t="n">
-        <v>10349000.78</v>
-      </c>
-      <c r="R41" s="18" t="n">
-        <v>11809071.18</v>
-      </c>
+        <v>151.85</v>
+      </c>
+      <c r="P41" s="9" t="n"/>
       <c r="S41" s="18" t="n">
-        <v>12114587.37</v>
-      </c>
-      <c r="T41" s="18" t="n">
-        <v>12892016.67</v>
-      </c>
-      <c r="U41" s="37" t="n">
-        <v>12892016.67</v>
-      </c>
-      <c r="V41" s="18" t="n">
-        <v>13021358.3</v>
-      </c>
-      <c r="W41" s="18" t="n">
-        <v>12944363.79</v>
-      </c>
-      <c r="X41" s="18" t="n">
-        <v>12879531.07</v>
-      </c>
+        <v>2285.84</v>
+      </c>
+      <c r="U41" s="9" t="n"/>
       <c r="Y41" s="18" t="n">
-        <v>13730328.43</v>
+        <v>4878.03</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>13730328.43</v>
+        <v>4878.03</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>13725794.58</v>
+        <v>73775.64999999999</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>12370945.99</v>
+        <v>112763.85</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -27165,81 +27480,43 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>541453.34</v>
+        <v>60437.62</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>541453.34</v>
+        <v>60437.62</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>541453.34</v>
+        <v>60437.62</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>541453.34</v>
+        <v>73172.12</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>541453.34</v>
+        <v>36901.12</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>541453.34</v>
+        <v>118380.57</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>541453.34</v>
+        <v>118380.57</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>541453.34</v>
+        <v>118364.76</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>1089366.99</v>
+        <v>127453.62</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>1089366.99</v>
-      </c>
-      <c r="O42" s="18" t="n">
-        <v>1536794.49</v>
-      </c>
-      <c r="P42" s="37" t="n">
-        <v>1536794.49</v>
-      </c>
-      <c r="Q42" s="18" t="n">
-        <v>1536794.49</v>
-      </c>
-      <c r="R42" s="18" t="n">
-        <v>1536794.49</v>
-      </c>
-      <c r="S42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="T42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="U42" s="37" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="V42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="W42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="X42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="Y42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="Z42" s="37" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="AA42" s="18" t="n">
-        <v>1537066.97</v>
-      </c>
-      <c r="AB42" s="19" t="n">
-        <v>1537066.97</v>
-      </c>
+        <v>127720.83</v>
+      </c>
+      <c r="P42" s="9" t="n"/>
+      <c r="U42" s="9" t="n"/>
+      <c r="Z42" s="9" t="n"/>
+      <c r="AB42" s="5" t="n"/>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
       <c r="AE42" s="11" t="n"/>
@@ -27260,80 +27537,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-714.45</v>
+        <v>8313147.25</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>-714.45</v>
+        <v>8313147.25</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-714.45</v>
+        <v>8942455.539999999</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-714.45</v>
+        <v>10375971.54</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-714.45</v>
+        <v>11486431.4</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-714.45</v>
+        <v>11402970.67</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>-714.45</v>
+        <v>11402970.67</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-714.45</v>
+        <v>11590802.07</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>1594965.47</v>
+        <v>11217394.67</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>1594964.97</v>
+        <v>10404833.09</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>2628374.16</v>
+        <v>9458216.800000001</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>2628374.16</v>
+        <v>9458216.800000001</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>0</v>
+        <v>10349000.78</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0</v>
+        <v>11809071.18</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>5839.6</v>
+        <v>12114587.37</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>23477.33</v>
+        <v>12892016.67</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>23477.33</v>
+        <v>12892016.67</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>36431.91</v>
+        <v>13021358.3</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>54678.7</v>
+        <v>12944363.79</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>58222.95</v>
+        <v>12879531.07</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>86656.92999999999</v>
+        <v>13730328.43</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>86656.92999999999</v>
+        <v>13730328.43</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>111709.32</v>
+        <v>13725794.58</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>113743.9</v>
+        <v>12370945.99</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -27355,80 +27632,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>2649143.02</v>
+        <v>541453.34</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>2649143.02</v>
+        <v>541453.34</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2649129.53</v>
+        <v>541453.34</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>2650568.57</v>
+        <v>541453.34</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>2605756.89</v>
+        <v>541453.34</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>2887329.3</v>
+        <v>541453.34</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>2887329.3</v>
+        <v>541453.34</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>2886938.06</v>
+        <v>541453.34</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>2327785.08</v>
+        <v>1089366.99</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>2327785.08</v>
+        <v>1089366.99</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>2327785.08</v>
+        <v>1536794.49</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>2327785.08</v>
+        <v>1536794.49</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>2329460.92</v>
+        <v>1536794.49</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>2332291.43</v>
+        <v>1536794.49</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>2327441.31</v>
+        <v>1537066.97</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>2322532.67</v>
+        <v>1537066.97</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>2322328.81</v>
+        <v>1537066.97</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -27450,80 +27727,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>-1062232.18</v>
+        <v>-714.45</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>-1062232.18</v>
+        <v>-714.45</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>-1553880.9</v>
+        <v>-714.45</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>-1736810.44</v>
+        <v>-714.45</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>-2345249.84</v>
+        <v>-714.45</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>-2784208.46</v>
+        <v>-714.45</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>-2784208.46</v>
+        <v>-714.45</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>-2906552.12</v>
+        <v>-714.45</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>-3354914.56</v>
+        <v>1594965.47</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>-3138940.8</v>
+        <v>1594964.97</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>-3001572.42</v>
+        <v>2628374.16</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>-3001572.42</v>
+        <v>2628374.16</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>-334450.25</v>
+        <v>0</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>-384877.35</v>
+        <v>0</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>-479215.28</v>
+        <v>5839.6</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>73450.78999999999</v>
+        <v>23477.33</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>73450.78999999999</v>
+        <v>23477.33</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>280083.97</v>
+        <v>36431.91</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>455059.88</v>
+        <v>54678.7</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>731159.55</v>
+        <v>58222.95</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>1488301.84</v>
+        <v>86656.92999999999</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>1488301.84</v>
+        <v>86656.92999999999</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>1989235.35</v>
+        <v>111709.32</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>2666816.9</v>
+        <v>113743.9</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -27545,80 +27822,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>2127649.73</v>
+        <v>2649143.02</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>2127649.73</v>
+        <v>2649143.02</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>1635987.52</v>
+        <v>2649129.53</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>1454497.02</v>
+        <v>2650568.57</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>801245.9399999999</v>
+        <v>2605756.89</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>643859.73</v>
+        <v>2887329.3</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>643859.73</v>
+        <v>2887329.3</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>521124.82</v>
+        <v>2886938.06</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>2210544.28</v>
+        <v>2327785.08</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>2427893.63</v>
+        <v>2327785.08</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>4044940.34</v>
+        <v>2327785.08</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>4044940.34</v>
+        <v>2327785.08</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>4085449.25</v>
+        <v>2329460.92</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>4037600.33</v>
+        <v>2332291.43</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>3945116.15</v>
+        <v>2327441.31</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>4515193.28</v>
+        <v>2327441.31</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>4515193.28</v>
+        <v>2327441.31</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>4734670.41</v>
+        <v>2327441.31</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>4938122.38</v>
+        <v>2327441.31</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>5217711.92</v>
+        <v>2327441.31</v>
       </c>
       <c r="Y46" s="18" t="n">
-        <v>5994317.61</v>
+        <v>2327441.31</v>
       </c>
       <c r="Z46" s="37" t="n">
-        <v>5994317.61</v>
+        <v>2327441.31</v>
       </c>
       <c r="AA46" s="18" t="n">
-        <v>6514137.13</v>
+        <v>2322532.67</v>
       </c>
       <c r="AB46" s="19" t="n">
-        <v>7193208.51</v>
+        <v>2322328.81</v>
       </c>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
@@ -27640,80 +27917,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>10440796.98</v>
+        <v>-1062232.18</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>10440796.98</v>
+        <v>-1062232.18</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>10578443.06</v>
+        <v>-1553880.9</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>11830468.56</v>
+        <v>-1736810.44</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>12287677.34</v>
+        <v>-2345249.84</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>12046830.4</v>
+        <v>-2784208.46</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>12046830.4</v>
+        <v>-2784208.46</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>12111926.89</v>
+        <v>-2906552.12</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>13427938.96</v>
+        <v>-3354914.56</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>12832726.72</v>
+        <v>-3138940.8</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>13503157.15</v>
+        <v>-3001572.42</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>13503157.15</v>
+        <v>-3001572.42</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>14434450.02</v>
+        <v>-334450.25</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>15846671.5</v>
+        <v>-384877.35</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>16059703.52</v>
+        <v>-479215.28</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>17407209.94</v>
+        <v>73450.78999999999</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>17407209.94</v>
+        <v>73450.78999999999</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>17756028.72</v>
+        <v>280083.97</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>17882486.17</v>
+        <v>455059.88</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>18097243</v>
+        <v>731159.55</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>19724646.03</v>
+        <v>1488301.84</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>19724646.03</v>
+        <v>1488301.84</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>20239931.7</v>
+        <v>1989235.35</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>19564154.5</v>
+        <v>2666816.9</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -27735,7 +28012,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
@@ -27830,80 +28107,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>2637131.45</v>
+        <v>10440796.98</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>2637131.45</v>
+        <v>10440796.98</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>2815381</v>
+        <v>10578443.06</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>2911794.27</v>
+        <v>11830468.56</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>2962710.77</v>
+        <v>12287677.34</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>2622272.39</v>
+        <v>12046830.4</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>2622272.39</v>
+        <v>12046830.4</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>3010594.51</v>
+        <v>12111926.89</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>2274257.09</v>
+        <v>13427938.96</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>2206763.51</v>
+        <v>12832726.72</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>2084114.02</v>
+        <v>13503157.15</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>2084114.02</v>
+        <v>13503157.15</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>3322377.04</v>
+        <v>14434450.02</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>4165013.54</v>
+        <v>15846671.5</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>4786290.48</v>
+        <v>16059703.52</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>5163714.54</v>
+        <v>17407209.94</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>5163714.54</v>
+        <v>17407209.94</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>5420481.96</v>
+        <v>17756028.72</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>4922539.27</v>
+        <v>17882486.17</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>5039167.84</v>
+        <v>18097243</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>5506183.62</v>
+        <v>19724646.03</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>5506183.62</v>
+        <v>19724646.03</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>5999427.8</v>
+        <v>20239931.7</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>5870915.14</v>
+        <v>19564154.5</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -27925,80 +28202,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>597133.5</v>
+        <v>2127649.73</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>597133.5</v>
+        <v>2127649.73</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1416803.7</v>
+        <v>1635987.52</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>1672286</v>
+        <v>1454497.02</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>1854260.15</v>
+        <v>801245.9399999999</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>1509598.26</v>
+        <v>643859.73</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>1509598.26</v>
+        <v>643859.73</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>2773587.23</v>
+        <v>521124.82</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>739774.79</v>
+        <v>2210544.28</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>1251788.42</v>
+        <v>2427893.63</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>313617.03</v>
+        <v>4044940.34</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>313617.03</v>
+        <v>4044940.34</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>1733555.3</v>
+        <v>4085449.25</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>2439859.78</v>
+        <v>4037600.33</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>3898297.43</v>
+        <v>3945116.15</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>4749380.08</v>
+        <v>4515193.28</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>4749380.08</v>
+        <v>4515193.28</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>4657769.36</v>
+        <v>4734670.41</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>4103785.61</v>
+        <v>4938122.38</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>4820025.42</v>
+        <v>5217711.92</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>4904159.23</v>
+        <v>5994317.61</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>4904159.23</v>
+        <v>5994317.61</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>5102679.93</v>
+        <v>6514137.13</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>4624949.6</v>
+        <v>7193208.51</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -28020,80 +28297,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>2273162.65</v>
+        <v>2637131.45</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>2273162.65</v>
+        <v>2637131.45</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>1626919.5</v>
+        <v>2815381</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1317531.68</v>
+        <v>2911794.27</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1148673.61</v>
+        <v>2962710.77</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>1152920.19</v>
+        <v>2622272.39</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>1152920.19</v>
+        <v>2622272.39</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>237007.28</v>
+        <v>3010594.51</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>1534482.3</v>
+        <v>2274257.09</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>954975.09</v>
+        <v>2206763.51</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>1770496.99</v>
+        <v>2084114.02</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>1770496.99</v>
+        <v>2084114.02</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>1588821.74</v>
+        <v>3322377.04</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1725153.76</v>
+        <v>4165013.54</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>887993.05</v>
+        <v>4786290.48</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>414334.46</v>
+        <v>5163714.54</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>414334.46</v>
+        <v>5163714.54</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>762712.6</v>
+        <v>5420481.96</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>818753.66</v>
+        <v>4922539.27</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>219142.42</v>
+        <v>5039167.84</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>602024.39</v>
+        <v>5506183.62</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>602024.39</v>
+        <v>5506183.62</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>896747.87</v>
+        <v>5999427.8</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>1245965.54</v>
+        <v>5870915.14</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -28115,67 +28392,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>당기법인세자산(선급법인세)</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="n"/>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>597133.5</v>
+      </c>
+      <c r="F52" s="37" t="n">
+        <v>597133.5</v>
+      </c>
       <c r="G52" s="18" t="n">
-        <v>948.34</v>
+        <v>1416803.7</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>3795.75</v>
+        <v>1672286</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>4818.44</v>
+        <v>1854260.15</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>5751.49</v>
+        <v>1509598.26</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>5751.49</v>
+        <v>1509598.26</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>6576.28</v>
+        <v>2773587.23</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>2389.52</v>
+        <v>739774.79</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>3792.54</v>
+        <v>1251788.42</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>5328.55</v>
+        <v>313617.03</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>5328.55</v>
+        <v>313617.03</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>7961.76</v>
+        <v>1733555.3</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>5622.7</v>
+        <v>2439859.78</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>7125.81</v>
+        <v>3898297.43</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>8150.98</v>
+        <v>4749380.08</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>8150.98</v>
+        <v>4749380.08</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>8948.76</v>
+        <v>4657769.36</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>1897.41</v>
+        <v>4103785.61</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>2481.71</v>
-      </c>
-      <c r="Z52" s="9" t="n"/>
+        <v>4820025.42</v>
+      </c>
+      <c r="Y52" s="18" t="n">
+        <v>4904159.23</v>
+      </c>
+      <c r="Z52" s="37" t="n">
+        <v>4904159.23</v>
+      </c>
+      <c r="AA52" s="18" t="n">
+        <v>5102679.93</v>
+      </c>
       <c r="AB52" s="19" t="n">
-        <v>1835.03</v>
+        <v>4624949.6</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -28197,32 +28487,81 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>기타유동금융부채</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>2273162.65</v>
+      </c>
+      <c r="F53" s="37" t="n">
+        <v>2273162.65</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>1626919.5</v>
+      </c>
       <c r="H53" s="18" t="n">
-        <v>25751.28</v>
+        <v>1317531.68</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>50921.84</v>
+        <v>1148673.61</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>31440.48</v>
+        <v>1152920.19</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>31440.48</v>
+        <v>1152920.19</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>28739.37</v>
+        <v>237007.28</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>16702.79</v>
-      </c>
-      <c r="P53" s="9" t="n"/>
-      <c r="U53" s="9" t="n"/>
-      <c r="Z53" s="9" t="n"/>
-      <c r="AB53" s="5" t="n"/>
+        <v>1573754.55</v>
+      </c>
+      <c r="N53" s="18" t="n">
+        <v>995628.72</v>
+      </c>
+      <c r="O53" s="18" t="n">
+        <v>1809935.83</v>
+      </c>
+      <c r="P53" s="37" t="n">
+        <v>1809935.83</v>
+      </c>
+      <c r="Q53" s="18" t="n">
+        <v>1629313.87</v>
+      </c>
+      <c r="R53" s="18" t="n">
+        <v>1776245.9</v>
+      </c>
+      <c r="S53" s="18" t="n">
+        <v>939677.46</v>
+      </c>
+      <c r="T53" s="18" t="n">
+        <v>469489.28</v>
+      </c>
+      <c r="U53" s="37" t="n">
+        <v>469489.28</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>816129.03</v>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>872148.5600000001</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>273635.68</v>
+      </c>
+      <c r="Y53" s="18" t="n">
+        <v>656821.83</v>
+      </c>
+      <c r="Z53" s="37" t="n">
+        <v>656821.83</v>
+      </c>
+      <c r="AA53" s="18" t="n">
+        <v>951745.37</v>
+      </c>
+      <c r="AB53" s="19" t="n">
+        <v>1300773.61</v>
+      </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -28243,47 +28582,67 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
+          <t>당기법인세자산(선급법인세)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
+      <c r="G54" s="18" t="n">
+        <v>948.34</v>
+      </c>
       <c r="H54" s="18" t="n">
-        <v>25751.28</v>
+        <v>3795.75</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>50921.84</v>
+        <v>4818.44</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>31440.48</v>
+        <v>5751.49</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>31440.48</v>
+        <v>5751.49</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>28739.37</v>
+        <v>6576.28</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>16702.79</v>
-      </c>
-      <c r="P54" s="9" t="n"/>
-      <c r="U54" s="9" t="n"/>
+        <v>2389.52</v>
+      </c>
+      <c r="N54" s="18" t="n">
+        <v>3792.54</v>
+      </c>
+      <c r="O54" s="18" t="n">
+        <v>5328.55</v>
+      </c>
+      <c r="P54" s="37" t="n">
+        <v>5328.55</v>
+      </c>
+      <c r="Q54" s="18" t="n">
+        <v>7961.76</v>
+      </c>
+      <c r="R54" s="18" t="n">
+        <v>5622.7</v>
+      </c>
+      <c r="S54" s="18" t="n">
+        <v>7125.81</v>
+      </c>
+      <c r="T54" s="18" t="n">
+        <v>8150.98</v>
+      </c>
+      <c r="U54" s="37" t="n">
+        <v>8150.98</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>8948.76</v>
+      </c>
       <c r="W54" s="18" t="n">
-        <v>155113.83</v>
+        <v>1897.41</v>
       </c>
       <c r="X54" s="18" t="n">
-        <v>142423.97</v>
-      </c>
-      <c r="Y54" s="18" t="n">
-        <v>99176.92</v>
-      </c>
-      <c r="Z54" s="37" t="n">
-        <v>99176.92</v>
-      </c>
-      <c r="AA54" s="18" t="n">
-        <v>74104.37</v>
-      </c>
+        <v>2481.71</v>
+      </c>
+      <c r="Z54" s="9" t="n"/>
       <c r="AB54" s="19" t="n">
-        <v>135025.87</v>
+        <v>1835.03</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -28305,62 +28664,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>기타유동금융자산</t>
+          <t>기타유동금융부채</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
+      <c r="H55" s="18" t="n">
+        <v>25751.28</v>
+      </c>
+      <c r="I55" s="18" t="n">
+        <v>50921.84</v>
+      </c>
+      <c r="J55" s="18" t="n">
+        <v>31440.48</v>
+      </c>
+      <c r="K55" s="37" t="n">
+        <v>31440.48</v>
+      </c>
       <c r="L55" s="18" t="n">
-        <v>414700.74</v>
+        <v>28739.37</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>429609.86</v>
-      </c>
-      <c r="N55" s="18" t="n">
-        <v>91734.81</v>
-      </c>
-      <c r="O55" s="18" t="n">
-        <v>108239.3</v>
-      </c>
-      <c r="P55" s="37" t="n">
-        <v>108239.3</v>
-      </c>
-      <c r="Q55" s="18" t="n">
-        <v>109262.09</v>
-      </c>
-      <c r="R55" s="18" t="n">
-        <v>10780.51</v>
-      </c>
-      <c r="S55" s="18" t="n">
-        <v>10991.31</v>
-      </c>
-      <c r="T55" s="18" t="n">
-        <v>11454.87</v>
-      </c>
-      <c r="U55" s="37" t="n">
-        <v>11454.87</v>
-      </c>
-      <c r="V55" s="18" t="n">
-        <v>11462.79</v>
-      </c>
-      <c r="W55" s="18" t="n">
-        <v>4752.2</v>
-      </c>
-      <c r="X55" s="18" t="n">
-        <v>4834.52</v>
-      </c>
-      <c r="Y55" s="18" t="n">
-        <v>4404</v>
-      </c>
-      <c r="Z55" s="37" t="n">
-        <v>4404</v>
-      </c>
-      <c r="AA55" s="18" t="n">
-        <v>4485</v>
-      </c>
-      <c r="AB55" s="19" t="n">
-        <v>14512</v>
-      </c>
+        <v>16702.79</v>
+      </c>
+      <c r="P55" s="9" t="n"/>
+      <c r="U55" s="9" t="n"/>
+      <c r="Z55" s="9" t="n"/>
+      <c r="AB55" s="5" t="n"/>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
       <c r="AE55" s="11" t="n"/>
@@ -28381,36 +28710,47 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>단기금융부채</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
+      <c r="H56" s="18" t="n">
+        <v>25751.28</v>
+      </c>
+      <c r="I56" s="18" t="n">
+        <v>50921.84</v>
+      </c>
+      <c r="J56" s="18" t="n">
+        <v>31440.48</v>
+      </c>
+      <c r="K56" s="37" t="n">
+        <v>31440.48</v>
+      </c>
       <c r="L56" s="18" t="n">
-        <v>21558.39</v>
+        <v>28739.37</v>
+      </c>
+      <c r="M56" s="18" t="n">
+        <v>16702.79</v>
       </c>
       <c r="P56" s="9" t="n"/>
       <c r="U56" s="9" t="n"/>
-      <c r="V56" s="18" t="n">
-        <v>157130.47</v>
-      </c>
       <c r="W56" s="18" t="n">
-        <v>175991.71</v>
+        <v>155113.83</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>190644.95</v>
+        <v>142423.97</v>
       </c>
       <c r="Y56" s="18" t="n">
-        <v>129805.8</v>
+        <v>99176.92</v>
       </c>
       <c r="Z56" s="37" t="n">
-        <v>129805.8</v>
+        <v>99176.92</v>
       </c>
       <c r="AA56" s="18" t="n">
-        <v>41662.76</v>
+        <v>74104.37</v>
       </c>
       <c r="AB56" s="19" t="n">
-        <v>182381.4</v>
+        <v>135025.87</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -28432,58 +28772,61 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>기타유동금융자산</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
+      <c r="L57" s="18" t="n">
+        <v>414700.74</v>
+      </c>
       <c r="M57" s="18" t="n">
-        <v>647468.41</v>
+        <v>429609.86</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>544631.12</v>
+        <v>91734.81</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>494162.6</v>
+        <v>108239.3</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>494162.6</v>
+        <v>108239.3</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>1679649.27</v>
+        <v>109262.09</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>2485199.05</v>
+        <v>10780.51</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>3145042.2</v>
+        <v>10991.31</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>3201449.85</v>
+        <v>11454.87</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>3201449.85</v>
+        <v>11454.87</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>3335499.92</v>
+        <v>11462.79</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>2983414.4</v>
+        <v>4752.2</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>2978045.82</v>
+        <v>4834.52</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>3220177.27</v>
+        <v>4404</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>3220177.27</v>
+        <v>4404</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>3443704.22</v>
+        <v>4485</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>3292402.72</v>
+        <v>14512</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -28505,44 +28848,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
-      <c r="M58" s="18" t="n">
-        <v>1626788.68</v>
-      </c>
-      <c r="N58" s="18" t="n">
-        <v>1662132.39</v>
+      <c r="L58" s="18" t="n">
+        <v>21558.39</v>
       </c>
       <c r="P58" s="9" t="n"/>
-      <c r="T58" s="18" t="n">
-        <v>1962264.69</v>
-      </c>
-      <c r="U58" s="37" t="n">
-        <v>1962264.69</v>
-      </c>
+      <c r="U58" s="9" t="n"/>
       <c r="V58" s="18" t="n">
-        <v>2084982.04</v>
+        <v>157130.47</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>1939124.87</v>
+        <v>175991.71</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>2061122.02</v>
+        <v>190644.95</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>2286006.35</v>
+        <v>129805.8</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>2286006.35</v>
+        <v>129805.8</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>2555723.58</v>
+        <v>41662.76</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>2578512.42</v>
+        <v>182381.4</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -28564,58 +28899,58 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
       <c r="M59" s="18" t="n">
-        <v>553341.3100000001</v>
+        <v>647468.41</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>554717.39</v>
+        <v>544631.12</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>553559.04</v>
+        <v>494162.6</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>553559.04</v>
+        <v>494162.6</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>553644.09</v>
+        <v>1679649.27</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>553391.75</v>
+        <v>2485199.05</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>553983.5600000001</v>
+        <v>3145042.2</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>553756.89</v>
+        <v>3201449.85</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>553756.89</v>
+        <v>3201449.85</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>553646.26</v>
+        <v>3335499.92</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>563875.53</v>
+        <v>2983414.4</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>563821.14</v>
+        <v>2978045.82</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>554850.5600000001</v>
+        <v>3220177.27</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>554850.5600000001</v>
+        <v>3220177.27</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>553592.8199999999</v>
+        <v>3443704.22</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>553251.9300000001</v>
+        <v>3292402.72</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -28637,52 +28972,44 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>이연법인세자산</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
-      <c r="O60" s="18" t="n">
-        <v>163892.42</v>
-      </c>
-      <c r="P60" s="37" t="n">
-        <v>163892.42</v>
-      </c>
-      <c r="Q60" s="18" t="n">
-        <v>163892.42</v>
-      </c>
-      <c r="R60" s="18" t="n">
-        <v>154090.12</v>
-      </c>
-      <c r="S60" s="18" t="n">
-        <v>154090.12</v>
-      </c>
+      <c r="M60" s="18" t="n">
+        <v>1626788.68</v>
+      </c>
+      <c r="N60" s="18" t="n">
+        <v>1662132.39</v>
+      </c>
+      <c r="P60" s="9" t="n"/>
       <c r="T60" s="18" t="n">
-        <v>506573.93</v>
+        <v>1962264.69</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>506573.93</v>
+        <v>1962264.69</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>506573.93</v>
+        <v>2084982.04</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>498512.13</v>
+        <v>1939124.87</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>498484.85</v>
+        <v>2061122.02</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>950308.59</v>
+        <v>2286006.35</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>950308.59</v>
+        <v>2286006.35</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>950335.73</v>
+        <v>2555723.58</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>950335.73</v>
+        <v>2578512.42</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -28704,26 +29031,59 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>비유동파생상품자산</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
+      <c r="M61" s="18" t="n">
+        <v>553341.3100000001</v>
+      </c>
+      <c r="N61" s="18" t="n">
+        <v>554717.39</v>
+      </c>
+      <c r="O61" s="18" t="n">
+        <v>553559.04</v>
+      </c>
+      <c r="P61" s="37" t="n">
+        <v>553559.04</v>
+      </c>
+      <c r="Q61" s="18" t="n">
+        <v>553644.09</v>
+      </c>
+      <c r="R61" s="18" t="n">
+        <v>553391.75</v>
+      </c>
+      <c r="S61" s="18" t="n">
+        <v>553983.5600000001</v>
+      </c>
+      <c r="T61" s="18" t="n">
+        <v>553756.89</v>
+      </c>
+      <c r="U61" s="37" t="n">
+        <v>553756.89</v>
+      </c>
+      <c r="V61" s="18" t="n">
+        <v>553646.26</v>
+      </c>
       <c r="W61" s="18" t="n">
-        <v>12.81</v>
+        <v>563875.53</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>1418.5</v>
+        <v>563821.14</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>4864.26</v>
+        <v>554850.5600000001</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>4864.26</v>
-      </c>
-      <c r="AB61" s="5" t="n"/>
+        <v>554850.5600000001</v>
+      </c>
+      <c r="AA61" s="18" t="n">
+        <v>553592.8199999999</v>
+      </c>
+      <c r="AB61" s="19" t="n">
+        <v>553251.9300000001</v>
+      </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
       <c r="AE61" s="11" t="n"/>
@@ -28744,30 +29104,52 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>단기파생상품부채</t>
+          <t>이연법인세자산</t>
         </is>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="K62" s="9" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="U62" s="9" t="n"/>
+      <c r="O62" s="18" t="n">
+        <v>163892.42</v>
+      </c>
+      <c r="P62" s="37" t="n">
+        <v>163892.42</v>
+      </c>
+      <c r="Q62" s="18" t="n">
+        <v>163892.42</v>
+      </c>
+      <c r="R62" s="18" t="n">
+        <v>154090.12</v>
+      </c>
+      <c r="S62" s="18" t="n">
+        <v>154090.12</v>
+      </c>
+      <c r="T62" s="18" t="n">
+        <v>506573.93</v>
+      </c>
+      <c r="U62" s="37" t="n">
+        <v>506573.93</v>
+      </c>
+      <c r="V62" s="18" t="n">
+        <v>506573.93</v>
+      </c>
       <c r="W62" s="18" t="n">
-        <v>155113.83</v>
+        <v>498512.13</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>142423.97</v>
+        <v>498484.85</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>68957.10000000001</v>
+        <v>950308.59</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>68957.10000000001</v>
+        <v>950308.59</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>74104.37</v>
+        <v>950335.73</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>103732.82</v>
+        <v>950335.73</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -28789,22 +29171,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
+          <t>비유동파생상품자산</t>
         </is>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="K63" s="9" t="n"/>
       <c r="P63" s="9" t="n"/>
       <c r="U63" s="9" t="n"/>
+      <c r="W63" s="18" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="X63" s="18" t="n">
+        <v>1418.5</v>
+      </c>
       <c r="Y63" s="18" t="n">
-        <v>30219.82</v>
+        <v>4864.26</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>30219.82</v>
-      </c>
-      <c r="AB63" s="19" t="n">
-        <v>31293.05</v>
-      </c>
+        <v>4864.26</v>
+      </c>
+      <c r="AB63" s="5" t="n"/>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="11" t="n"/>
@@ -28825,21 +29211,30 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>리스부채</t>
+          <t>단기파생상품부채</t>
         </is>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="K64" s="9" t="n"/>
       <c r="P64" s="9" t="n"/>
       <c r="U64" s="9" t="n"/>
+      <c r="W64" s="18" t="n">
+        <v>155113.83</v>
+      </c>
+      <c r="X64" s="18" t="n">
+        <v>142423.97</v>
+      </c>
       <c r="Y64" s="18" t="n">
-        <v>30219.82</v>
+        <v>68957.10000000001</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>30219.82</v>
+        <v>68957.10000000001</v>
+      </c>
+      <c r="AA64" s="18" t="n">
+        <v>74104.37</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>126350.75</v>
+        <v>103732.82</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -28861,19 +29256,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>유동파생상품자산</t>
+          <t>유동리스부채</t>
         </is>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="K65" s="9" t="n"/>
       <c r="P65" s="9" t="n"/>
       <c r="U65" s="9" t="n"/>
-      <c r="Z65" s="9" t="n"/>
-      <c r="AA65" s="18" t="n">
-        <v>11835.59</v>
+      <c r="Y65" s="18" t="n">
+        <v>30219.82</v>
+      </c>
+      <c r="Z65" s="37" t="n">
+        <v>30219.82</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>14682.83</v>
+        <v>31293.05</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -28895,7 +29292,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>유동파생상품자산</t>
         </is>
       </c>
       <c r="F66" s="9" t="n"/>
@@ -28903,8 +29300,11 @@
       <c r="P66" s="9" t="n"/>
       <c r="U66" s="9" t="n"/>
       <c r="Z66" s="9" t="n"/>
+      <c r="AA66" s="18" t="n">
+        <v>11835.59</v>
+      </c>
       <c r="AB66" s="19" t="n">
-        <v>95057.7</v>
+        <v>14682.83</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -37957,7 +38357,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18" t="n"/>
@@ -52520,7 +52920,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님 · ※ 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모)</t>
+          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].covered_scope_new_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님 · ※ 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모)</t>
         </is>
       </c>
     </row>
@@ -53304,39 +53704,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>112.77</v>
+        <v>0</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
+        <v>112.77</v>
+      </c>
+      <c r="I18" s="34" t="n">
         <v>427.02</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="J18" s="34" t="n">
         <v>906.65</v>
       </c>
-      <c r="J18" s="34" t="n">
+      <c r="K18" s="34" t="n">
         <v>1515.57</v>
-      </c>
-      <c r="K18" s="34" t="n">
-        <v>2217.68</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
+        <v>2217.68</v>
+      </c>
+      <c r="N18" s="34" t="n">
         <v>2976.88</v>
       </c>
-      <c r="N18" s="34" t="n">
+      <c r="O18" s="34" t="n">
         <v>3757.09</v>
       </c>
-      <c r="O18" s="34" t="n">
+      <c r="P18" s="34" t="n">
         <v>4522.2</v>
-      </c>
-      <c r="P18" s="34" t="n">
-        <v>5236.12</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -53610,39 +54010,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>693.09</v>
+        <v>96</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>2624.48</v>
+        <v>960.62</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>5572.3</v>
+        <v>3032.79</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>9314.719999999999</v>
+        <v>6090.68</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>13629.89</v>
+        <v>9912.43</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>18295.95</v>
+        <v>14276.2</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>23091.06</v>
+        <v>18960.14</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>27793.38</v>
+        <v>23742.4</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>32181.05</v>
+        <v>28401.13</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -58691,7 +59091,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18">
@@ -61440,7 +61840,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(상선·해양및특수선·EP및특수선) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15454억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3044억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15450억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3043억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14303억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2964억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14344억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2973억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14025억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14114억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13867억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13133억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13171억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12537억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12574억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12338억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12374억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26116억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26115억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30347억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34671억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34680억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39190억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39204억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43925억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43943억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48896억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48919억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52668억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52695억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55459억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55490억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 26116억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 26115억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30347억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34671억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34680억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39190억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39204억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43925억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43943억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48896억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48919억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52668억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52695억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55459억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55490억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15454억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3044억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15450억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3043억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14303억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2964억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14344억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2973억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14025억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14114억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13979억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13827억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13867억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13133억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2997억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13171억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12537억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12574억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12338억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3030억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12374억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,342억 vs 0억 · 2027 12,023억 vs 13,801억 · 2028 12,055억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,341억 vs 0억 · 2027 12,057억 vs 13,801억 · 2028 12,090억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5553.2</v>
+        <v>5556.2</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.95</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="33">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2261</v>
+        <v>0.2263</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>71900</v>
+        <v>71800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>76180</v>
+        <v>76160</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006752221</v>
+        <v>0.006753015</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033408184</v>
+        <v>0.033409012</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060064586</v>
+        <v>0.060064646</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.086719712</v>
+        <v>0.08671960300000001</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.113376851</v>
+        <v>0.113377183</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.140031553</v>
+        <v>0.14003232</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166688023</v>
+        <v>0.166687632</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193344027</v>
+        <v>0.193345705</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.219999898</v>
+        <v>0.220000613</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.016425706</v>
+        <v>-0.014521284</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.000236324</v>
+        <v>0.001353525</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.001785977</v>
+        <v>-0.004426981</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-2.8442e-05</v>
+        <v>0.003579479</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.011250797</v>
+        <v>-0.010786195</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.001146071</v>
+        <v>-0.001359264</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.00272848</v>
+        <v>-0.010909062</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.005292611</v>
+        <v>-0.00085558</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.002267233</v>
+        <v>-0.008710074999999999</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.0055904</v>
+        <v>0.002062173</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010652692</v>
+        <v>-0.009643917</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.008852317</v>
+        <v>-0.008173438999999999</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.005879843</v>
+        <v>0.008587993</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.000577546</v>
+        <v>-0.006910699</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.00722992</v>
+        <v>-0.007901129999999999</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.002289838</v>
+        <v>-0.00597331</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.004323726</v>
+        <v>-0.003729064</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.005487749</v>
+        <v>-0.002007149</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.001393514</v>
+        <v>-0.005785149</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.000801439</v>
+        <v>-0.003935404</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.104625896</v>
+        <v>-0.104613503</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.114720877</v>
+        <v>-0.1148501</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.132685072</v>
+        <v>-0.132846097</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.159727465</v>
+        <v>-0.159942296</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.199177033</v>
+        <v>-0.199481541</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.261132455</v>
+        <v>-0.261612993</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.268153915</v>
+        <v>-0.268877148</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.271126921</v>
+        <v>-0.272205866</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.406236756</v>
+        <v>-0.408393162</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.197410223</v>
+        <v>0.197386839</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.161858113</v>
+        <v>0.162045839</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.14263996</v>
+        <v>0.142773916</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.13033653</v>
+        <v>0.130436538</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.12081983</v>
+        <v>0.120893119</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113177612</v>
+        <v>0.113230995</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.07714112100000001</v>
+        <v>0.07718957799999999</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.052993377</v>
+        <v>0.053039628</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054960976</v>
+        <v>0.054997796</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29205.238064</v>
+        <v>29204.385094</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29125.601358</v>
+        <v>29134.210468</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29158.443461</v>
+        <v>29167.142528</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29191.409897</v>
+        <v>29200.207645</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29191.404955</v>
+        <v>29200.195906</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29158.453973</v>
+        <v>29167.1502</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15333.25406</v>
+        <v>15341.95312</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3030.318631</v>
+        <v>3039.111429</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3030.400783</v>
+        <v>3039.192836</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007467</v>
+        <v>0.119007537</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230675</v>
+        <v>0.120230656</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882774</v>
+        <v>0.120882775</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881153</v>
+        <v>0.120881124</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893227</v>
+        <v>0.120893154</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120792928</v>
+        <v>0.120793003</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799659</v>
+        <v>0.12079982</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869848</v>
+        <v>0.12086994</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890176</v>
+        <v>0.12089024</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13135,11 +13135,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>71900</v>
+        <v>71800</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 77,200원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 74,100원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559124419752796</v>
+        <v>0.05559123495662265</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999654830113993</v>
+        <v>0.9999652673314794</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777805522130511</v>
+        <v>0.05777775705033357</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568173077088636</v>
+        <v>0.03568151653332233</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1367.81</v>
+        <v>1367.43</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1361.59</v>
+        <v>1365.54</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1629698</v>
+        <v>1629244</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1512325</v>
+        <v>1516713.4</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1437984.3</v>
+        <v>1442157</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1445591.6</v>
+        <v>1449786.4</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1432040.8</v>
+        <v>1436196.2</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1394178.8</v>
+        <v>1398224.3</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1313291.3</v>
+        <v>1317102.2</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1253738.6</v>
+        <v>1257376.6</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1233784.9</v>
+        <v>1237365</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1114188.2</v>
+        <v>1117421.3</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>956356.8</v>
+        <v>959131.9</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>419456.9</v>
+        <v>420674</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>210669.4</v>
+        <v>211280.7</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119761.2</v>
+        <v>120108.8</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60616.6</v>
+        <v>60792.5</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61282.7</v>
+        <v>61460.6</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>53929.5</v>
+        <v>54086</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33478.8</v>
+        <v>33576</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5751280.6</v>
+        <v>5750826.6</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5827941.7</v>
+        <v>5844853</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5194993.6</v>
+        <v>5210068.1</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2700671.3</v>
+        <v>2708507.9</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>295590</v>
+        <v>296447.9</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>135775.2</v>
+        <v>136169.2</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67701.60000000001</v>
+        <v>67898</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1545444.6</v>
+        <v>1545014.1</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1430278.1</v>
+        <v>1434428.4</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1402548.1</v>
+        <v>1406617.9</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1411403.8</v>
+        <v>1415499.4</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1397853</v>
+        <v>1401909.2</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1382659</v>
+        <v>1386671.1</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1313291.3</v>
+        <v>1317102.2</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1253738.6</v>
+        <v>1257376.6</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1233784.9</v>
+        <v>1237365</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1114188.2</v>
+        <v>1117421.3</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>956356.8</v>
+        <v>959131.9</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>419456.9</v>
+        <v>420674</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>210669.4</v>
+        <v>211280.7</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119761.2</v>
+        <v>120108.8</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60616.6</v>
+        <v>60792.5</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61282.7</v>
+        <v>61460.6</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>53929.5</v>
+        <v>54086</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33478.8</v>
+        <v>33576</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5399477.5</v>
+        <v>5399047</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5642083</v>
+        <v>5658454.9</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5183473.8</v>
+        <v>5198514.9</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2700671.3</v>
+        <v>2708507.9</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>295590</v>
+        <v>296447.9</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>135775.2</v>
+        <v>136169.2</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67701.60000000001</v>
+        <v>67898</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1241026</v>
+        <v>1240680.3</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1133831.5</v>
+        <v>1137121.7</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1102807.7</v>
+        <v>1106007.8</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1108369.6</v>
+        <v>1111585.8</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1094818.8</v>
+        <v>1097995.7</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1082918.6</v>
+        <v>1086060.9</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1013550.9</v>
+        <v>1016492</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>950704.3</v>
+        <v>953463.1</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>930750.6</v>
+        <v>933451.4</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>817741.6</v>
+        <v>820114.5</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>656616.4</v>
+        <v>658521.7</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>129932.7</v>
+        <v>130309.8</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104790.6</v>
+        <v>105094.7</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34713.3</v>
+        <v>34814.1</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>304418.7</v>
+        <v>304333.9</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>296446.5</v>
+        <v>297306.8</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>299740.4</v>
+        <v>300610.2</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>303034.2</v>
+        <v>303913.6</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>303034.2</v>
+        <v>303913.6</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>299740.4</v>
+        <v>300610.2</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>299740.4</v>
+        <v>300610.2</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>303034.2</v>
+        <v>303913.6</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>303034.2</v>
+        <v>303913.6</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>296446.5</v>
+        <v>297306.8</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>299740.4</v>
+        <v>300610.2</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>289524.1</v>
+        <v>290364.2</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>105878.8</v>
+        <v>106186.1</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85047.89999999999</v>
+        <v>85294.7</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60616.6</v>
+        <v>60792.5</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61282.7</v>
+        <v>61460.6</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>53929.5</v>
+        <v>54086</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33478.8</v>
+        <v>33576</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34222.8</v>
+        <v>34322.1</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33850.8</v>
+        <v>33949</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15450억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3043억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15445억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3042억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14344억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2973억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2970억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13867억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13171억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12574억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12559억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12374억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30347억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30345억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34680억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34676억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39204억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39197억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43943억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43935억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48919억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48909억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52695억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52683억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55490억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55476억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30347억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30345억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34680억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34676억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39204억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39197억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43943억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43935억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48919억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48909억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52695억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52683억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55490억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55476억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15450억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3043억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15445억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3042억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14344억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2973억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2970억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13867억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13171억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3006억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12574억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12559억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12374억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,341억 vs 0억 · 2027 12,057억 vs 13,801억 · 2028 12,090억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,340억 vs 0억 · 2027 12,043억 vs 13,801억 · 2028 12,076억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5556.2</v>
+        <v>5554.7</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="32">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2263</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006753015</v>
+        <v>0.006754059</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033409012</v>
+        <v>0.033408819</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060064646</v>
+        <v>0.060065587</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.08671960300000001</v>
+        <v>0.08672020499999999</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.113377183</v>
+        <v>0.11337725</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.14003232</v>
+        <v>0.14003202</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166687632</v>
+        <v>0.166688009</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193345705</v>
+        <v>0.193344191</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.220000613</v>
+        <v>0.219999489</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.014521284</v>
+        <v>-0.01662006</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.001353525</v>
+        <v>-0.010357283</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.004426981</v>
+        <v>0.004744529</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.003579479</v>
+        <v>-0.015303061</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.010786195</v>
+        <v>-0.008136676000000001</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.001359264</v>
+        <v>-0.006513659</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.010909062</v>
+        <v>-0.003354116</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.00085558</v>
+        <v>0.001469314</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.008710074999999999</v>
+        <v>3.5952e-05</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.002062173</v>
+        <v>-0.001256641</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.009643917</v>
+        <v>-0.009763957</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.008173438999999999</v>
+        <v>-0.0078098</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.008587993</v>
+        <v>-0.000155394</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.006910699</v>
+        <v>-0.013661483</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.007901129999999999</v>
+        <v>-0.003030048</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.00597331</v>
+        <v>0.001194955</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.003729064</v>
+        <v>-0.003740682</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.002007149</v>
+        <v>0.002175579</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.005785149</v>
+        <v>0.004347552</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.003935404</v>
+        <v>0.004252885</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.104613503</v>
+        <v>-0.104597465</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.1148501</v>
+        <v>-0.114793494</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.132846097</v>
+        <v>-0.132775746</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.159942296</v>
+        <v>-0.159848001</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.199481541</v>
+        <v>-0.19934754</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.261612993</v>
+        <v>-0.261401577</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.268877148</v>
+        <v>-0.268558853</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.272205866</v>
+        <v>-0.271734488</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.408393162</v>
+        <v>-0.407446936</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.197386839</v>
+        <v>0.197356579</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.162045839</v>
+        <v>0.161972966</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.142773916</v>
+        <v>0.142722546</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.130436538</v>
+        <v>0.13039822</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.120893119</v>
+        <v>0.120865328</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113230995</v>
+        <v>0.113211043</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.07718957799999999</v>
+        <v>0.077170791</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.053039628</v>
+        <v>0.053021488</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054997796</v>
+        <v>0.054983289</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29204.385094</v>
+        <v>29203.284263</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29134.210468</v>
+        <v>29130.658466</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29167.142528</v>
+        <v>29163.548846</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29200.207645</v>
+        <v>29196.570587</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29200.195906</v>
+        <v>29196.566456</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29167.1502</v>
+        <v>29163.558152</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15341.95312</v>
+        <v>15338.359776</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3039.111429</v>
+        <v>3035.474886</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3039.192836</v>
+        <v>3035.557062</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007537</v>
+        <v>0.11900748</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230656</v>
+        <v>0.120230674</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882775</v>
+        <v>0.120882587</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881124</v>
+        <v>0.120881243</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893154</v>
+        <v>0.120893259</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120793003</v>
+        <v>0.120793034</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.12079982</v>
+        <v>0.120799855</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.12086994</v>
+        <v>0.120869829</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.12089024</v>
+        <v>0.120890179</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559123495662265</v>
+        <v>0.05559126936026393</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999652673314794</v>
+        <v>0.9999657438466775</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777775705033357</v>
+        <v>0.05777813684516334</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568151653332233</v>
+        <v>0.03568176760762954</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1367.43</v>
+        <v>1366.93</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1365.54</v>
+        <v>1363.91</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1629244</v>
+        <v>1628651.9</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1516713.4</v>
+        <v>1514901</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1442157</v>
+        <v>1440433.7</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1449786.4</v>
+        <v>1448053.9</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1436196.2</v>
+        <v>1434480</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1398224.3</v>
+        <v>1396553.5</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1317102.2</v>
+        <v>1315528.3</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1257376.6</v>
+        <v>1255874.1</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1237365</v>
+        <v>1235886.4</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1117421.3</v>
+        <v>1116086</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>959131.9</v>
+        <v>957985.8</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>420674</v>
+        <v>420171.3</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>211280.7</v>
+        <v>211028.2</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>120108.8</v>
+        <v>119965.2</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60792.5</v>
+        <v>60719.9</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61460.6</v>
+        <v>61387.1</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>54086</v>
+        <v>54021.4</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33576</v>
+        <v>33535.9</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5750826.6</v>
+        <v>5750234.5</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5844853</v>
+        <v>5837868.6</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5210068.1</v>
+        <v>5203842.3</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2708507.9</v>
+        <v>2705271.3</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>296447.9</v>
+        <v>296093.6</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>136169.2</v>
+        <v>136006.6</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67898</v>
+        <v>67817</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1545014.1</v>
+        <v>1544452.6</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1434428.4</v>
+        <v>1432714.3</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1406617.9</v>
+        <v>1404937.1</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1415499.4</v>
+        <v>1413807.9</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1401909.2</v>
+        <v>1400234</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1386671.1</v>
+        <v>1385014.1</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1317102.2</v>
+        <v>1315528.3</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1257376.6</v>
+        <v>1255874.1</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1237365</v>
+        <v>1235886.4</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1117421.3</v>
+        <v>1116086</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>959131.9</v>
+        <v>957985.8</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>420674</v>
+        <v>420171.3</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>211280.7</v>
+        <v>211028.2</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>120108.8</v>
+        <v>119965.2</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60792.5</v>
+        <v>60719.9</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61460.6</v>
+        <v>61387.1</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>54086</v>
+        <v>54021.4</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33576</v>
+        <v>33535.9</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5399047</v>
+        <v>5398485.5</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5658454.9</v>
+        <v>5651693.3</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5198514.9</v>
+        <v>5192302.9</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2708507.9</v>
+        <v>2705271.3</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>296447.9</v>
+        <v>296093.6</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>136169.2</v>
+        <v>136006.6</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67898</v>
+        <v>67817</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1240680.3</v>
+        <v>1240229.3</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1137121.7</v>
+        <v>1135762.8</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1106007.8</v>
+        <v>1104686.1</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1111585.8</v>
+        <v>1110257.5</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1097995.7</v>
+        <v>1096683.6</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1086060.9</v>
+        <v>1084763.1</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1016492</v>
+        <v>1015277.3</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>953463.1</v>
+        <v>952323.7</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>933451.4</v>
+        <v>932336</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>820114.5</v>
+        <v>819134.5</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>658521.7</v>
+        <v>657734.8</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>130309.8</v>
+        <v>130154.1</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>105094.7</v>
+        <v>104969.1</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34814.1</v>
+        <v>34772.4</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>304333.9</v>
+        <v>304223.3</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>297306.8</v>
+        <v>296951.5</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>300610.2</v>
+        <v>300251</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>303913.6</v>
+        <v>303550.4</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>303913.6</v>
+        <v>303550.4</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>300610.2</v>
+        <v>300251</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>300610.2</v>
+        <v>300251</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>303913.6</v>
+        <v>303550.4</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>303913.6</v>
+        <v>303550.4</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>297306.8</v>
+        <v>296951.5</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>300610.2</v>
+        <v>300251</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>290364.2</v>
+        <v>290017.3</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>106186.1</v>
+        <v>106059.2</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85294.7</v>
+        <v>85192.8</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60792.5</v>
+        <v>60719.9</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61460.6</v>
+        <v>61387.1</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>54086</v>
+        <v>54021.4</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33576</v>
+        <v>33535.9</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34322.1</v>
+        <v>34281.1</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33949</v>
+        <v>33908.5</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.93</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="33">
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>71800</v>
+        <v>67100</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9576,7 +9576,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>71500</v>
+        <v>67000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>76160</v>
+        <v>74650</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>71800</v>
+        <v>67100</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -54493,7 +54493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15445억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3042억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15430억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2970억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14254억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2954억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13978억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13931억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13779억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13088억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12559억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12495억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12296억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26115억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26113억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30345억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30334억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34676억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34657억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39197억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39171억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43935억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43900억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48909억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48866억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52683억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55476억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55420억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 26115억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 26113억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30345억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30334억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34676억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34657억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39197억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39171억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43935억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43900억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48909억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48866억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52683억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55476억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55420억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15445억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3042억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15430억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2970억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14254억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2954억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13978억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13931억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13779억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3003억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13088억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12559억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12495억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3036억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12296억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,340억 vs 0억 · 2027 12,043억 vs 13,801억 · 2028 12,076억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,338억 vs 0억 · 2027 11,982억 vs 13,801억 · 2028 12,014억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5554.7</v>
+        <v>5548.6</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.08</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="33">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2262</v>
+        <v>0.2259</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>67100</v>
+        <v>66700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9576,7 +9576,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>67000</v>
+        <v>62700</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>74650</v>
+        <v>73457.10000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006754059</v>
+        <v>0.006752062</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033408819</v>
+        <v>0.033409811</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060065587</v>
+        <v>0.060065408</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.08672020499999999</v>
+        <v>0.08672012699999999</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.11337725</v>
+        <v>0.113375875</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.14003202</v>
+        <v>0.140032798</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166688009</v>
+        <v>0.166688788</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193344191</v>
+        <v>0.193342944</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.219999489</v>
+        <v>0.22000123</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.01662006</v>
+        <v>-0.014939685</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.010357283</v>
+        <v>0.001237696</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.004744529</v>
+        <v>0.002194635</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.015303061</v>
+        <v>-0.011361178</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.008136676000000001</v>
+        <v>-0.004051476</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.006513659</v>
+        <v>-0.000248346</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.003354116</v>
+        <v>-0.011762222</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.001469314</v>
+        <v>-0.010318135</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>3.5952e-05</v>
+        <v>0.012287203</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.001256641</v>
+        <v>-0.008084749</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.009763957</v>
+        <v>-0.010338799</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.0078098</v>
+        <v>0.001505154</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.000155394</v>
+        <v>-0.004705978</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.013661483</v>
+        <v>-0.011783698</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.003030048</v>
+        <v>-0.001114993</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.001194955</v>
+        <v>-0.004834551</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.003740682</v>
+        <v>-0.014579443</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.002175579</v>
+        <v>-0.001408662</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.004347552</v>
+        <v>0.005318997</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.004252885</v>
+        <v>-0.004002615</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.104597465</v>
+        <v>-0.104556884</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.114793494</v>
+        <v>-0.114557081</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.132775746</v>
+        <v>-0.132480511</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.159848001</v>
+        <v>-0.159453647</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.19934754</v>
+        <v>-0.19878817</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.261401577</v>
+        <v>-0.260518022</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.268558853</v>
+        <v>-0.267235796</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.271734488</v>
+        <v>-0.269764835</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.407446936</v>
+        <v>-0.403520425</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.197356579</v>
+        <v>0.197280009</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.161972966</v>
+        <v>0.161657052</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.142722546</v>
+        <v>0.142497533</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.13039822</v>
+        <v>0.130230822</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.120865328</v>
+        <v>0.120743672</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113211043</v>
+        <v>0.113123458</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.077170791</v>
+        <v>0.07708904</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.053021488</v>
+        <v>0.052941799</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054983289</v>
+        <v>0.054920654</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29203.284263</v>
+        <v>29200.492338</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29130.658466</v>
+        <v>29115.50714</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29163.548846</v>
+        <v>29148.232691</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29196.570587</v>
+        <v>29181.088516</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29196.566456</v>
+        <v>29181.081952</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29163.558152</v>
+        <v>29148.235613</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15338.359776</v>
+        <v>15323.042626</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3035.474886</v>
+        <v>3019.996122</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3035.557062</v>
+        <v>3020.078227</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.11900748</v>
+        <v>0.119007547</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230674</v>
+        <v>0.120230617</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882587</v>
+        <v>0.120882674</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881243</v>
+        <v>0.120881197</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893259</v>
+        <v>0.120893162</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120793034</v>
+        <v>0.120792939</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799855</v>
+        <v>0.120799775</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869829</v>
+        <v>0.120869927</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890179</v>
+        <v>0.120890207</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13135,11 +13135,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>67100</v>
+        <v>66700</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 74,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 72,000원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559126936026393</v>
+        <v>0.05559126596879789</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999657438466775</v>
+        <v>0.9999652007439197</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777813684516334</v>
+        <v>0.05777803610839154</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568176760762954</v>
+        <v>0.03568162605870501</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1366.93</v>
+        <v>1365.68</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1363.91</v>
+        <v>1356.95</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1628651.9</v>
+        <v>1627161.7</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1514901</v>
+        <v>1507173</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1440433.7</v>
+        <v>1433085.6</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1448053.9</v>
+        <v>1440667</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1434480</v>
+        <v>1427162.3</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1396553.5</v>
+        <v>1389429.2</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1315528.3</v>
+        <v>1308817.4</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1255874.1</v>
+        <v>1249467.5</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1235886.4</v>
+        <v>1229581.8</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1116086</v>
+        <v>1110392.5</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>957985.8</v>
+        <v>953098.8</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>420171.3</v>
+        <v>418027.9</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>211028.2</v>
+        <v>209951.7</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119965.2</v>
+        <v>119353.3</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60719.9</v>
+        <v>60410.1</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61387.1</v>
+        <v>61074</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>54021.4</v>
+        <v>53745.8</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33535.9</v>
+        <v>33364.8</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5750234.5</v>
+        <v>5748744.3</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5837868.6</v>
+        <v>5808087.9</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5203842.3</v>
+        <v>5177295.9</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2705271.3</v>
+        <v>2691470.9</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>296093.6</v>
+        <v>294583.2</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>136006.6</v>
+        <v>135312.7</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67817</v>
+        <v>67471</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1544452.6</v>
+        <v>1543039.5</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1432714.3</v>
+        <v>1425405.6</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1404937.1</v>
+        <v>1397770</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1413807.9</v>
+        <v>1406595.6</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1400234</v>
+        <v>1393091</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1385014.1</v>
+        <v>1377948.7</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1315528.3</v>
+        <v>1308817.4</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1255874.1</v>
+        <v>1249467.5</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1235886.4</v>
+        <v>1229581.8</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1116086</v>
+        <v>1110392.5</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>957985.8</v>
+        <v>953098.8</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>420171.3</v>
+        <v>418027.9</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>211028.2</v>
+        <v>209951.7</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119965.2</v>
+        <v>119353.3</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60719.9</v>
+        <v>60410.1</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61387.1</v>
+        <v>61074</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>54021.4</v>
+        <v>53745.8</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33535.9</v>
+        <v>33364.8</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5398485.5</v>
+        <v>5397072.4</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5651693.3</v>
+        <v>5622862.2</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5192302.9</v>
+        <v>5165815.4</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2705271.3</v>
+        <v>2691470.9</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>296093.6</v>
+        <v>294583.2</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>136006.6</v>
+        <v>135312.7</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67817</v>
+        <v>67471</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1240229.3</v>
+        <v>1239094.5</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1135762.8</v>
+        <v>1129969</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1104686.1</v>
+        <v>1099050.8</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1110257.5</v>
+        <v>1104593.7</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1096683.6</v>
+        <v>1091089.1</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1084763.1</v>
+        <v>1079229.4</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1015277.3</v>
+        <v>1010098.1</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>952323.7</v>
+        <v>947465.6</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>932336</v>
+        <v>927579.9</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>819134.5</v>
+        <v>814955.9</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>657734.8</v>
+        <v>654379.5</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>130154.1</v>
+        <v>129490.1</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104969.1</v>
+        <v>104433.6</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34772.4</v>
+        <v>34595.1</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>304223.3</v>
+        <v>303944.9</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>296951.5</v>
+        <v>295436.6</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>300251</v>
+        <v>298719.3</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>303550.4</v>
+        <v>302001.9</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>303550.4</v>
+        <v>302001.9</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>300251</v>
+        <v>298719.3</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>300251</v>
+        <v>298719.3</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>303550.4</v>
+        <v>302001.9</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>303550.4</v>
+        <v>302001.9</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>296951.5</v>
+        <v>295436.6</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>300251</v>
+        <v>298719.3</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>290017.3</v>
+        <v>288537.8</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>106059.2</v>
+        <v>105518.1</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85192.8</v>
+        <v>84758.2</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60719.9</v>
+        <v>60410.1</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61387.1</v>
+        <v>61074</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>54021.4</v>
+        <v>53745.8</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33535.9</v>
+        <v>33364.8</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34281.1</v>
+        <v>34106.2</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33908.5</v>
+        <v>33735.5</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -54493,7 +54493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15430억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15428억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14254억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2954억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2969억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13978억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13931억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13779억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13088억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12495억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12558억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12296억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30334억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34657억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34673억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39171억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39195억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43900억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43933억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48866억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48906억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52681억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55420억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55474억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30334억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34657억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34673억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39171억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39195억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43900억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43933억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48866억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48906억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52681억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55420억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55474억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15430억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15428억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14254억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2954억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2969억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13978억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14066억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13931억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13779억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13088억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2987억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12495억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12558억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12296억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3020억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,338억 vs 0억 · 2027 11,982억 vs 13,801억 · 2028 12,014억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,337억 vs 0억 · 2027 12,043억 vs 13,801억 · 2028 12,076억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5548.6</v>
+        <v>5554</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.02</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="33">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2259</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>66700</v>
+        <v>67400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>73457.10000000001</v>
+        <v>72762.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006752062</v>
+        <v>0.006752483</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033409811</v>
+        <v>0.033409354</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060065408</v>
+        <v>0.060064329</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.08672012699999999</v>
+        <v>0.08672160600000001</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.113375875</v>
+        <v>0.113376864</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.140032798</v>
+        <v>0.140031986</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166688788</v>
+        <v>0.166688377</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193342944</v>
+        <v>0.193345212</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.22000123</v>
+        <v>0.220000869</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.014939685</v>
+        <v>-0.015257357</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.001237696</v>
+        <v>0.0007010230000000001</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.002194635</v>
+        <v>-0.012264729</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.011361178</v>
+        <v>-0.003820168</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.004051476</v>
+        <v>-0.008752393000000001</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.000248346</v>
+        <v>-0.007439525</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.011762222</v>
+        <v>-0.005199772</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.010318135</v>
+        <v>-0.001439259</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.012287203</v>
+        <v>-0.003693537</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.008084749</v>
+        <v>-0.015680582</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010338799</v>
+        <v>-0.009425813</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.001505154</v>
+        <v>-0.007746965</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.004705978</v>
+        <v>-0.008205636000000001</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.011783698</v>
+        <v>-0.003245124</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.001114993</v>
+        <v>-0.004758947</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.004834551</v>
+        <v>-0.000897713</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.014579443</v>
+        <v>-0.006811413</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.001408662</v>
+        <v>-0.001662061</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.005318997</v>
+        <v>-0.010068933</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.004002615</v>
+        <v>-0.000921426</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.104556884</v>
+        <v>-0.104550323</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.114557081</v>
+        <v>-0.114785822</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.132480511</v>
+        <v>-0.13276546</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.159453647</v>
+        <v>-0.15983383</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.19878817</v>
+        <v>-0.199327487</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.260518022</v>
+        <v>-0.261367291</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.267235796</v>
+        <v>-0.268511925</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.269764835</v>
+        <v>-0.271667339</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.403520425</v>
+        <v>-0.407310768</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.197280009</v>
+        <v>0.19726763</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.161657052</v>
+        <v>0.161982702</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.142497533</v>
+        <v>0.142729647</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.130230822</v>
+        <v>0.130403986</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.120743672</v>
+        <v>0.120870651</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113123458</v>
+        <v>0.113215093</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.07708904</v>
+        <v>0.07717313100000001</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.052941799</v>
+        <v>0.053022684</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054920654</v>
+        <v>0.054984567</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29200.492338</v>
+        <v>29200.056006</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29115.50714</v>
+        <v>29130.584365</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29148.232691</v>
+        <v>29163.477198</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29181.088516</v>
+        <v>29196.500292</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29181.081952</v>
+        <v>29196.492863</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29148.235613</v>
+        <v>29163.481664</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15323.042626</v>
+        <v>15338.286409</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3019.996122</v>
+        <v>3035.406225</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3020.078227</v>
+        <v>3035.483543</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007547</v>
+        <v>0.119007464</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230617</v>
+        <v>0.120230481</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882674</v>
+        <v>0.120882613</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881197</v>
+        <v>0.120881268</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893162</v>
+        <v>0.120893283</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120792939</v>
+        <v>0.120793055</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799775</v>
+        <v>0.120799821</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869927</v>
+        <v>0.120869705</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890207</v>
+        <v>0.120890068</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13135,11 +13135,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>66700</v>
+        <v>67400</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 72,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 67,300원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559126596879789</v>
+        <v>0.0555912388589173</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999652007439197</v>
+        <v>0.9999654971168068</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777803610839154</v>
+        <v>0.05777785200888787</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568162605870501</v>
+        <v>0.03568159340442493</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1365.68</v>
+        <v>1365.48</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1356.95</v>
+        <v>1363.87</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1627161.7</v>
+        <v>1626924.8</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1507173</v>
+        <v>1514864.2</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1433085.6</v>
+        <v>1440398.7</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1440667</v>
+        <v>1448018.8</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1427162.3</v>
+        <v>1434445.2</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1389429.2</v>
+        <v>1396519.6</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1308817.4</v>
+        <v>1315496.3</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1249467.5</v>
+        <v>1255843.6</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1229581.8</v>
+        <v>1235856.4</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1110392.5</v>
+        <v>1116058.9</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>953098.8</v>
+        <v>957962.5</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>418027.9</v>
+        <v>420161.1</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>209951.7</v>
+        <v>211023.1</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119353.3</v>
+        <v>119962.3</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60410.1</v>
+        <v>60718.4</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61074</v>
+        <v>61385.6</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>53745.8</v>
+        <v>54020</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33364.8</v>
+        <v>33535</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5748744.3</v>
+        <v>5748507.4</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5808087.9</v>
+        <v>5837726.9</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5177295.9</v>
+        <v>5203715.9</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2691470.9</v>
+        <v>2705205.6</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>294583.2</v>
+        <v>296086.3</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>135312.7</v>
+        <v>136003.3</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67471</v>
+        <v>67815.39999999999</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1543039.5</v>
+        <v>1542814.8</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1425405.6</v>
+        <v>1432679.5</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1397770</v>
+        <v>1404903</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1406595.6</v>
+        <v>1413773.6</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1393091</v>
+        <v>1400200</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1377948.7</v>
+        <v>1384980.4</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1308817.4</v>
+        <v>1315496.3</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1249467.5</v>
+        <v>1255843.6</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1229581.8</v>
+        <v>1235856.4</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1110392.5</v>
+        <v>1116058.9</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>953098.8</v>
+        <v>957962.5</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>418027.9</v>
+        <v>420161.1</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>209951.7</v>
+        <v>211023.1</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119353.3</v>
+        <v>119962.3</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60410.1</v>
+        <v>60718.4</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61074</v>
+        <v>61385.6</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>53745.8</v>
+        <v>54020</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33364.8</v>
+        <v>33535</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5397072.4</v>
+        <v>5396847.7</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5622862.2</v>
+        <v>5651556.1</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5165815.4</v>
+        <v>5192176.7</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2691470.9</v>
+        <v>2705205.6</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>294583.2</v>
+        <v>296086.3</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>135312.7</v>
+        <v>136003.3</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67471</v>
+        <v>67815.39999999999</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1239094.5</v>
+        <v>1238914.2</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1129969</v>
+        <v>1135735.3</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1099050.8</v>
+        <v>1104659.3</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1104593.7</v>
+        <v>1110230.5</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1091089.1</v>
+        <v>1096657</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1079229.4</v>
+        <v>1084736.8</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1010098.1</v>
+        <v>1015252.7</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>947465.6</v>
+        <v>952300.6</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>927579.9</v>
+        <v>932313.4</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>814955.9</v>
+        <v>819114.6</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>654379.5</v>
+        <v>657718.9</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>129490.1</v>
+        <v>130150.9</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104433.6</v>
+        <v>104966.5</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34595.1</v>
+        <v>34771.6</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>303944.9</v>
+        <v>303900.7</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>295436.6</v>
+        <v>296944.3</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>298719.3</v>
+        <v>300243.7</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>302001.9</v>
+        <v>303543</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>302001.9</v>
+        <v>303543</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>298719.3</v>
+        <v>300243.7</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>298719.3</v>
+        <v>300243.7</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>302001.9</v>
+        <v>303543</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>302001.9</v>
+        <v>303543</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>295436.6</v>
+        <v>296944.3</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>298719.3</v>
+        <v>300243.7</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>288537.8</v>
+        <v>290010.2</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>105518.1</v>
+        <v>106056.6</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>84758.2</v>
+        <v>85190.7</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60410.1</v>
+        <v>60718.4</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61074</v>
+        <v>61385.6</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>53745.8</v>
+        <v>54020</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33364.8</v>
+        <v>33535</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34106.2</v>
+        <v>34280.3</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33735.5</v>
+        <v>33907.7</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -54493,7 +54493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15428억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15416억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3037억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2969억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14245억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2953억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13969억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14057억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13922억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13771억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13080억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12558억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12487억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12288억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26113억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26111억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30332억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34673억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34653억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39195억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39166억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43933억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43894억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48906억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48860억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52681억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52626억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55474억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55411억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 26113억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 26111억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30343억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30332억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34673억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34653억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39195억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39166억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43933억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43894억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48906억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48860억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52681억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52626억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55474억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55411억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15428억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3039억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15416억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3037억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14327억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2969억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14245억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2953억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14049억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13969억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14138억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14057억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14002억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13922억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13850억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13771억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13155억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3002억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13080억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12558억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12487억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12359억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3035억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12288억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,337억 vs 0억 · 2027 12,043억 vs 13,801억 · 2028 12,076억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,335억 vs 0억 · 2027 11,974억 vs 13,801억 · 2028 12,007억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5554</v>
+        <v>5547.4</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.14</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="33">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2262</v>
+        <v>0.2259</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>67400</v>
+        <v>64200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9576,7 +9576,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>62700</v>
+        <v>61100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>72762.5</v>
+        <v>70200</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006752483</v>
+        <v>0.006752403</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033409354</v>
+        <v>0.033408761</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060064329</v>
+        <v>0.060064031</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.08672160600000001</v>
+        <v>0.08672086699999999</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.113376864</v>
+        <v>0.113376334</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.140031986</v>
+        <v>0.140031522</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166688377</v>
+        <v>0.166687687</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193345212</v>
+        <v>0.193345032</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.220000869</v>
+        <v>0.219999795</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.015257357</v>
+        <v>-0.014757751</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.0007010230000000001</v>
+        <v>0.000859731</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.012264729</v>
+        <v>-0.002707082</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.003820168</v>
+        <v>-0.001699528</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.008752393000000001</v>
+        <v>-0.008867233</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.007439525</v>
+        <v>-0.009232621999999999</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.005199772</v>
+        <v>-0.007106914</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.001439259</v>
+        <v>0.00242562</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.003693537</v>
+        <v>-0.017203453</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.015680582</v>
+        <v>-0.001148181</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.009425813</v>
+        <v>-0.010189068</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.007746965</v>
+        <v>0.001152316</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.008205636000000001</v>
+        <v>-0.009604751999999999</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.003245124</v>
+        <v>-0.002121094</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.004758947</v>
+        <v>-0.00593112</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.000897713</v>
+        <v>-0.013821772</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.006811413</v>
+        <v>6.9568e-05</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.001662061</v>
+        <v>-0.008663580000000001</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.010068933</v>
+        <v>-0.004164046</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.000921426</v>
+        <v>-0.007062043</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.104550323</v>
+        <v>-0.10451606</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.114785822</v>
+        <v>-0.114524179</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.13276546</v>
+        <v>-0.132438903</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.15983383</v>
+        <v>-0.159397836</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.199327487</v>
+        <v>-0.19870865</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.261367291</v>
+        <v>-0.260391532</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.268511925</v>
+        <v>-0.267048524</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.271667339</v>
+        <v>-0.269491525</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.407310768</v>
+        <v>-0.402972009</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.19726763</v>
+        <v>0.197202982</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.161982702</v>
+        <v>0.16162839</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.142729647</v>
+        <v>0.142477249</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.130403986</v>
+        <v>0.130216158</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.120870651</v>
+        <v>0.120733619</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113215093</v>
+        <v>0.113116604</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.07717313100000001</v>
+        <v>0.077081632</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.053022684</v>
+        <v>0.052933722</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054984567</v>
+        <v>0.054914423</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29200.056006</v>
+        <v>29197.695567</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29130.584365</v>
+        <v>29113.725627</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29163.477198</v>
+        <v>29146.424394</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29196.500292</v>
+        <v>29179.2637</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29196.492863</v>
+        <v>29179.255528</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29163.481664</v>
+        <v>29146.437528</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15338.286409</v>
+        <v>15321.236784</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3035.406225</v>
+        <v>3018.171768</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3035.483543</v>
+        <v>3018.24365</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007464</v>
+        <v>0.119007602</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.120230481</v>
+        <v>0.1202305</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882613</v>
+        <v>0.120882708</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881268</v>
+        <v>0.120881141</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893283</v>
+        <v>0.120893118</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120793055</v>
+        <v>0.120793038</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799821</v>
+        <v>0.120799662</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869705</v>
+        <v>0.120869679</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.120890068</v>
+        <v>0.12089019</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13135,11 +13135,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>67400</v>
+        <v>64200</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 67,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 62,400원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.0555912388589173</v>
+        <v>0.05559125403937505</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999654971168068</v>
+        <v>0.9999651929901624</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777785200888787</v>
+        <v>0.05777755724495182</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568159340442493</v>
+        <v>0.03568147386890744</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1365.48</v>
+        <v>1364.42</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1363.87</v>
+        <v>1356.13</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1626924.8</v>
+        <v>1625661.6</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1514864.2</v>
+        <v>1506262.2</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1440398.7</v>
+        <v>1432219.5</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1448018.8</v>
+        <v>1439796.3</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1434445.2</v>
+        <v>1426299.8</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1396519.6</v>
+        <v>1388589.6</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1315496.3</v>
+        <v>1308026.4</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1255843.6</v>
+        <v>1248712.4</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1235856.4</v>
+        <v>1228838.7</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1116058.9</v>
+        <v>1109721.5</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>957962.5</v>
+        <v>952522.8</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>420161.1</v>
+        <v>417775.3</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>211023.1</v>
+        <v>209824.8</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119962.3</v>
+        <v>119281.1</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60718.4</v>
+        <v>60373.6</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61385.6</v>
+        <v>61037.1</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>54020</v>
+        <v>53713.3</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33535</v>
+        <v>33344.6</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5748507.4</v>
+        <v>5747244.2</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5837726.9</v>
+        <v>5804577.8</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5203715.9</v>
+        <v>5174167.1</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2705205.6</v>
+        <v>2689844.4</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>296086.3</v>
+        <v>294405.1</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>136003.3</v>
+        <v>135230.9</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67815.39999999999</v>
+        <v>67430.2</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1542814.8</v>
+        <v>1541616.9</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1432679.5</v>
+        <v>1424544.2</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1404903</v>
+        <v>1396925.4</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1413773.6</v>
+        <v>1405745.6</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1400200</v>
+        <v>1392249.1</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1384980.4</v>
+        <v>1377116</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1315496.3</v>
+        <v>1308026.4</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1255843.6</v>
+        <v>1248712.4</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1235856.4</v>
+        <v>1228838.7</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1116058.9</v>
+        <v>1109721.5</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>957962.5</v>
+        <v>952522.8</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>420161.1</v>
+        <v>417775.3</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>211023.1</v>
+        <v>209824.8</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119962.3</v>
+        <v>119281.1</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60718.4</v>
+        <v>60373.6</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61385.6</v>
+        <v>61037.1</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>54020</v>
+        <v>53713.3</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33535</v>
+        <v>33344.6</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5396847.7</v>
+        <v>5395649.8</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5651556.1</v>
+        <v>5619464.3</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5192176.7</v>
+        <v>5162693.5</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2705205.6</v>
+        <v>2689844.4</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>296086.3</v>
+        <v>294405.1</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>136003.3</v>
+        <v>135230.9</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67815.39999999999</v>
+        <v>67430.2</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1238914.2</v>
+        <v>1237952.2</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1135735.3</v>
+        <v>1129286.1</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1104659.3</v>
+        <v>1098386.6</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1110230.5</v>
+        <v>1103926.2</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1096657</v>
+        <v>1090429.7</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1084736.8</v>
+        <v>1078577.2</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1015252.7</v>
+        <v>1009487.7</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>952300.6</v>
+        <v>946893</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>932313.4</v>
+        <v>927019.3</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>819114.6</v>
+        <v>814463.4</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>657718.9</v>
+        <v>653984.1</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>130150.9</v>
+        <v>129411.9</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104966.5</v>
+        <v>104370.5</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34771.6</v>
+        <v>34574.2</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>303900.7</v>
+        <v>303664.7</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>296944.3</v>
+        <v>295258.1</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>300243.7</v>
+        <v>298538.8</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>303543</v>
+        <v>301819.4</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>303543</v>
+        <v>301819.4</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>300243.7</v>
+        <v>298538.8</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>300243.7</v>
+        <v>298538.8</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>303543</v>
+        <v>301819.4</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>303543</v>
+        <v>301819.4</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>296944.3</v>
+        <v>295258.1</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>300243.7</v>
+        <v>298538.8</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>290010.2</v>
+        <v>288363.4</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>106056.6</v>
+        <v>105454.4</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>85190.7</v>
+        <v>84707</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60718.4</v>
+        <v>60373.6</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61385.6</v>
+        <v>61037.1</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>54020</v>
+        <v>53713.3</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33535</v>
+        <v>33344.6</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34280.3</v>
+        <v>34085.6</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33907.7</v>
+        <v>33715.1</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.39)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1342.11)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
     </row>
@@ -54493,7 +54493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/042660_model.xlsx
+++ b/argus/kship/models/042660_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15416억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3037억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15373억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3028억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14245억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2953억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 14179억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2939억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13969억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13904억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14057억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13992억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13922억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13857억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13771억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13707억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 13080억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 13019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12487억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12429억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 26161.09; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12288억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 12231억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26111억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 26106억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30332억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 30319억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34653억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 34633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39166억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39138억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43894억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 43859억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48860억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48817억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52626억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52577억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55411억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +2.92억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 55356억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 26111억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 26106억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 30332억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 30319억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 34653억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 34633억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39166억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39138억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 43894억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 43859억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48860억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48817억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52626억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52577억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 55411억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 55356억 × 5.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 60375억 × 3.57%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4105,55 +4105,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15416억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3037억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15373억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 143141억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3028억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14245억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2953억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 14179억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 116980억) + 신규수주 매출 525억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2939억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13969억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13904억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 90819억) + 신규수주 매출 1990억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14057억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13992억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 64658억) + 신규수주 매출 4224억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13922억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13857억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 38497억) + 신규수주 매출 7061억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13771억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13707억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 26161억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 12336억) + 신규수주 매출 10333억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 13080억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2985억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 13019억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 12336억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 13870억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 2971억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12487억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12429억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 17505억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12288억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3018억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 12231억(sls.by_quarter.marine_hedged_krw_m(헤지 17% 적용; origin 2026Q2 이후 체결 6건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel), 패널 범위 밖 NAVAL 8,380억은 상계 안 함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 26161억/분기, 잔여 0억) + 신규수주 매출 21070억(forecast_panel.json.gz scenarios.base covered_scope_new_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; ※폴백 — 패널이 전범위 new_order_revenue 를 비워(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) 모델 대상 부문(상선·기타, 제외 EP및특수선)만 덮는 covered_scope_new_revenue 사용 · 저신뢰; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억)) · origin 이후 공시 수주 SLS 3004억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5216,7 +5216,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,335억 vs 0억 · 2027 11,974억 vs 13,801억 · 2028 12,007억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(12481억) &gt; 연결 매출(12455억) — 부문표/파서 문제(yards 레인 확인) / 2022Q2 조선 부문 매출(11969억) &gt; 연결 매출(11841억) — 부문표/파서 문제(yards 레인 확인) / 2022Q3 조선 부문 매출(10004억) &gt; 연결 매출(9815억) — 부문표/파서 문제(yards 레인 확인) / 2022Q4 조선 부문 매출(14764억) &gt; 연결 매출(14492억) — 부문표/파서 문제(yards 레인 확인) / 2023Q1 조선 부문 매출(14706억) &gt; 연결 매출(14398억) — 부문표/파서 문제(yards 레인 확인) / 2023Q2 조선 부문 매출(18569억) &gt; 연결 매출(18207억) — 부문표/파서 문제(yards 레인 확인) / 2023Q3 조선 부문 매출(20122억) &gt; 연결 매출(19168억) — 부문표/파서 문제(yards 레인 확인) / 2023Q4 조선 부문 매출(23388억) &gt; 연결 매출(22309억) — 부문표/파서 문제(yards 레인 확인) / 2024Q1 조선 부문 매출(23616억) &gt; 연결 매출(22836억) — 부문표/파서 문제(yards 레인 확인) / 2024Q2 조선 부문 매출(26384억) &gt; 연결 매출(25361억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(33310억) &gt; 연결 매출(32941억) — 부문표/파서 문제(yards 레인 확인) / 2026Q1 조선 부문 매출(33220억) &gt; 연결 매출(32099억) — 부문표/파서 문제(yards 레인 확인) / 2026Q2 조선 부문 매출(56347억) &gt; 연결 매출(54432억) — 부문표/파서 문제(yards 레인 확인) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base covered_scope_new_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 76,578억) — 보수/낙관은 scenarios 블록(합산 안 함) / 신규수주 폴백(저신뢰): 패널이 전범위 new_order_revenue 를 비웠다(book_value_only, scope_unverified, insufficient_segment_history, insufficient_burn_history, insufficient_order_history, negative_net_inflow) → 같은 엔진·같은 R1 인식·같은 시나리오 정의의 covered_scope_new_revenue 사용. 모델 대상 부문 상선·기타 (제외 EP및특수선)만 덮고 제외 부문(EP및특수선)의 신규분은 반영되지 않는다, 패널 신규수주는 공시 체결 속도 대비 84% 수준(분기 평균 31,967억 vs 공시 체결 38,167억 — 대체로 같은 규모) / origin 이후 공시 수주 6건 44,707억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 31,967억 − 공시 36,327억(범위 밖 8,380억 제외) = 0억) — 패널 base 신규 매출 −24,396억(2026 525억 · 2027 9,807억 · 2028 14,064억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 6건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 36,327억 vs 패널 base 신규수주 31,967억(114%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,326억 vs 0억 · 2027 11,918억 vs 13,801억 · 2028 11,951억 vs 62,778억 / 법인세율 이월결손 경로: 최근 양(+)세전 7분기 유효세율 중위 0.7% → 0.7% 를 2026Q4 까지 유지, 2027Q1~2028Q4 선형 램프로 법정세율 근사 22% 수렴 — 결손 잔액·만기는 주석 미파싱(추정) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 +30/+489/-282/-827(중위 -126억) → 추정 2026Q3 -281억(차 -154억, -122%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5547.4</v>
+        <v>5540.7</v>
       </c>
     </row>
     <row r="30">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.57</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -5862,7 +5862,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="33">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2259</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="34">
@@ -8426,35 +8426,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8545,35 +8545,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8664,35 +8664,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8783,35 +8783,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -8902,35 +8902,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9021,35 +9021,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9140,35 +9140,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9259,35 +9259,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9394,7 +9394,7 @@
         <v>78800</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>64200</v>
+        <v>52800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9576,7 +9576,7 @@
         <v>71300</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>61100</v>
+        <v>52700</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9667,7 +9667,7 @@
         <v>86733.89999999999</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>70200</v>
+        <v>65887.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10789,39 +10789,39 @@
         <v>0.006752619</v>
       </c>
       <c r="AD27" s="31" t="n">
-        <v>0.006752403</v>
+        <v>0.006753492</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE19/subQ!AE18,"")</f>
         <v/>
       </c>
       <c r="AF27" s="31" t="n">
-        <v>0.033408761</v>
+        <v>0.033408671</v>
       </c>
       <c r="AG27" s="31" t="n">
-        <v>0.060064031</v>
+        <v>0.06006519</v>
       </c>
       <c r="AH27" s="31" t="n">
-        <v>0.08672086699999999</v>
+        <v>0.086719768</v>
       </c>
       <c r="AI27" s="31" t="n">
-        <v>0.113376334</v>
+        <v>0.113375887</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ19/subQ!AJ18,"")</f>
         <v/>
       </c>
       <c r="AK27" s="31" t="n">
-        <v>0.140031522</v>
+        <v>0.140031429</v>
       </c>
       <c r="AL27" s="31" t="n">
-        <v>0.166687687</v>
+        <v>0.166688463</v>
       </c>
       <c r="AM27" s="31" t="n">
-        <v>0.193345032</v>
+        <v>0.193345136</v>
       </c>
       <c r="AN27" s="31" t="n">
-        <v>0.219999795</v>
+        <v>0.220000514</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO19/subQ!AO18,"")</f>
@@ -11216,36 +11216,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.014757751</v>
+        <v>-0.015836222</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.000859731</v>
+        <v>-0.009787850000000001</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.002707082</v>
+        <v>0.003122409</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.001699528</v>
+        <v>-0.008462747</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.008867233</v>
+        <v>-0.005064338</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.009232621999999999</v>
+        <v>-0.003944413</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.007106914</v>
+        <v>-0.005253218</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.00242562</v>
+        <v>-0.000851124</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.017203453</v>
+        <v>-0.015522044</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.001148181</v>
+        <v>0.000330402</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11344,36 +11344,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010189068</v>
+        <v>-0.009446843999999999</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.001152316</v>
+        <v>-0.007433415</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.009604751999999999</v>
+        <v>-0.001656576</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.002121094</v>
+        <v>-0.006728367</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.00593112</v>
+        <v>0.000108627</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.013821772</v>
+        <v>0.003791502</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>6.9568e-05</v>
+        <v>-0.005654698</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.008663580000000001</v>
+        <v>-0.010059989</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.004164046</v>
+        <v>-0.001046137</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.007062043</v>
+        <v>-0.00404173</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11603,33 +11603,33 @@
         <v>-0.091654624</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>-0.10451606</v>
+        <v>-0.104391887</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>-0.114524179</v>
+        <v>-0.114296397</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>-0.132438903</v>
+        <v>-0.132153975</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>-0.159397836</v>
+        <v>-0.159016991</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>-0.19870865</v>
+        <v>-0.198167206</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>-0.260391532</v>
+        <v>-0.25953685</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>-0.267048524</v>
+        <v>-0.265775026</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>-0.269491525</v>
+        <v>-0.267613459</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0.402972009</v>
+        <v>-0.399242493</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11731,33 +11731,33 @@
         <v>0.235155723</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.197202982</v>
+        <v>0.196968231</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.16162839</v>
+        <v>0.16136131</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.142477249</v>
+        <v>0.142287625</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.130216158</v>
+        <v>0.130076139</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.120733619</v>
+        <v>0.1206328</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.113116604</v>
+        <v>0.113045463</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.077081632</v>
+        <v>0.077012075</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.052933722</v>
+        <v>0.052864142</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.054914423</v>
+        <v>0.054860279</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12457,33 +12457,33 @@
         <v>27459.150974</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>29197.695567</v>
+        <v>29189.176169</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>29113.725627</v>
+        <v>29099.921205</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>29146.424394</v>
+        <v>29132.476645</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>29179.2637</v>
+        <v>29165.16467</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>29179.255528</v>
+        <v>29165.145891</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>29146.437528</v>
+        <v>29132.484144</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>15321.236784</v>
+        <v>15307.285272</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>3018.171768</v>
+        <v>3004.065394</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>3018.24365</v>
+        <v>3004.148282</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12758,39 +12758,39 @@
         <v>0.118831446</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.119007602</v>
+        <v>0.119007503</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.1202305</v>
+        <v>0.120230591</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.120882708</v>
+        <v>0.120882709</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.120881141</v>
+        <v>0.120881129</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.120893118</v>
+        <v>0.120893231</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.120793038</v>
+        <v>0.1207929</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.120799662</v>
+        <v>0.120799745</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.120869679</v>
+        <v>0.120869771</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.12089019</v>
+        <v>0.120890199</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13135,11 +13135,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>64200</v>
+        <v>52800</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 62,400원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 57,200원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.05559125403937505</v>
+        <v>0.05559123006923741</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.9999651929901624</v>
+        <v>0.9999656314533085</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.05777755724495182</v>
+        <v>0.05777791290175002</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03568147386890744</v>
+        <v>0.03568164982599446</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42673,73 +42673,73 @@
         <v>1418.75</v>
       </c>
       <c r="AI21" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AJ21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AK21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AP21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AQ21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AR21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AS21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AT21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AU21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AV21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AW21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AX21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AY21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AZ21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BA21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BB21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BC21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BD21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="BE21" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
     </row>
     <row r="22">
@@ -42844,73 +42844,73 @@
         <v>1427.9</v>
       </c>
       <c r="AI22" s="13" t="n">
-        <v>1364.42</v>
+        <v>1360.59</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AL22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AM22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AO22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AP22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AR22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AS22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AT22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AU22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AV22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AW22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AX22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AY22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="BA22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="BB22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="BC22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="BD22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
       <c r="BE22" s="13" t="n">
-        <v>1356.13</v>
+        <v>1349.79</v>
       </c>
     </row>
     <row r="23">
@@ -43015,73 +43015,73 @@
         <v>1560284.1</v>
       </c>
       <c r="AI23" s="18" t="n">
-        <v>1625661.6</v>
+        <v>1621102.2</v>
       </c>
       <c r="AJ23" s="18" t="n">
-        <v>1506262.2</v>
+        <v>1499224.2</v>
       </c>
       <c r="AK23" s="18" t="n">
-        <v>1432219.5</v>
+        <v>1425527.5</v>
       </c>
       <c r="AL23" s="18" t="n">
-        <v>1439796.3</v>
+        <v>1433068.9</v>
       </c>
       <c r="AM23" s="18" t="n">
-        <v>1426299.8</v>
+        <v>1419635.5</v>
       </c>
       <c r="AN23" s="18" t="n">
-        <v>1388589.6</v>
+        <v>1382101.4</v>
       </c>
       <c r="AO23" s="18" t="n">
-        <v>1308026.4</v>
+        <v>1301914.7</v>
       </c>
       <c r="AP23" s="18" t="n">
-        <v>1248712.4</v>
+        <v>1242877.9</v>
       </c>
       <c r="AQ23" s="18" t="n">
-        <v>1228838.7</v>
+        <v>1223097</v>
       </c>
       <c r="AR23" s="18" t="n">
-        <v>1109721.5</v>
+        <v>1104536.3</v>
       </c>
       <c r="AS23" s="18" t="n">
-        <v>952522.8</v>
+        <v>948072.2</v>
       </c>
       <c r="AT23" s="18" t="n">
-        <v>417775.3</v>
+        <v>415823.2</v>
       </c>
       <c r="AU23" s="18" t="n">
-        <v>209824.8</v>
+        <v>208844.4</v>
       </c>
       <c r="AV23" s="18" t="n">
-        <v>119281.1</v>
+        <v>118723.8</v>
       </c>
       <c r="AW23" s="18" t="n">
-        <v>60373.6</v>
+        <v>60091.5</v>
       </c>
       <c r="AX23" s="18" t="n">
-        <v>61037.1</v>
+        <v>60751.9</v>
       </c>
       <c r="AY23" s="18" t="n">
-        <v>53713.3</v>
+        <v>53462.3</v>
       </c>
       <c r="AZ23" s="18" t="n">
-        <v>33344.6</v>
+        <v>33188.8</v>
       </c>
       <c r="BA23" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BB23" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BC23" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BD23" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BE23" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BF23" s="18" t="n">
         <v>221934.2</v>
@@ -43105,25 +43105,25 @@
         <v>1743172</v>
       </c>
       <c r="BM23" s="18" t="n">
-        <v>5747244.2</v>
+        <v>5742684.8</v>
       </c>
       <c r="BN23" s="18" t="n">
-        <v>5804577.8</v>
+        <v>5777456.1</v>
       </c>
       <c r="BO23" s="18" t="n">
-        <v>5174167.1</v>
+        <v>5149991</v>
       </c>
       <c r="BP23" s="18" t="n">
-        <v>2689844.4</v>
+        <v>2677276.1</v>
       </c>
       <c r="BQ23" s="18" t="n">
-        <v>294405.1</v>
+        <v>293029.5</v>
       </c>
       <c r="BR23" s="18" t="n">
-        <v>135230.9</v>
+        <v>134599</v>
       </c>
       <c r="BS23" s="18" t="n">
-        <v>67430.2</v>
+        <v>67115.2</v>
       </c>
     </row>
     <row r="24">
@@ -43228,73 +43228,73 @@
         <v>1472329.2</v>
       </c>
       <c r="AI24" s="18" t="n">
-        <v>1541616.9</v>
+        <v>1537293.2</v>
       </c>
       <c r="AJ24" s="18" t="n">
-        <v>1424544.2</v>
+        <v>1417888</v>
       </c>
       <c r="AK24" s="18" t="n">
-        <v>1396925.4</v>
+        <v>1390398.2</v>
       </c>
       <c r="AL24" s="18" t="n">
-        <v>1405745.6</v>
+        <v>1399177.3</v>
       </c>
       <c r="AM24" s="18" t="n">
-        <v>1392249.1</v>
+        <v>1385743.9</v>
       </c>
       <c r="AN24" s="18" t="n">
-        <v>1377116</v>
+        <v>1370681.4</v>
       </c>
       <c r="AO24" s="18" t="n">
-        <v>1308026.4</v>
+        <v>1301914.7</v>
       </c>
       <c r="AP24" s="18" t="n">
-        <v>1248712.4</v>
+        <v>1242877.9</v>
       </c>
       <c r="AQ24" s="18" t="n">
-        <v>1228838.7</v>
+        <v>1223097</v>
       </c>
       <c r="AR24" s="18" t="n">
-        <v>1109721.5</v>
+        <v>1104536.3</v>
       </c>
       <c r="AS24" s="18" t="n">
-        <v>952522.8</v>
+        <v>948072.2</v>
       </c>
       <c r="AT24" s="18" t="n">
-        <v>417775.3</v>
+        <v>415823.2</v>
       </c>
       <c r="AU24" s="18" t="n">
-        <v>209824.8</v>
+        <v>208844.4</v>
       </c>
       <c r="AV24" s="18" t="n">
-        <v>119281.1</v>
+        <v>118723.8</v>
       </c>
       <c r="AW24" s="18" t="n">
-        <v>60373.6</v>
+        <v>60091.5</v>
       </c>
       <c r="AX24" s="18" t="n">
-        <v>61037.1</v>
+        <v>60751.9</v>
       </c>
       <c r="AY24" s="18" t="n">
-        <v>53713.3</v>
+        <v>53462.3</v>
       </c>
       <c r="AZ24" s="18" t="n">
-        <v>33344.6</v>
+        <v>33188.8</v>
       </c>
       <c r="BA24" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BB24" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BC24" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BD24" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BE24" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BF24" s="18" t="n">
         <v>221934.2</v>
@@ -43318,25 +43318,25 @@
         <v>1415487.8</v>
       </c>
       <c r="BM24" s="18" t="n">
-        <v>5395649.8</v>
+        <v>5391326.1</v>
       </c>
       <c r="BN24" s="18" t="n">
-        <v>5619464.3</v>
+        <v>5593207.4</v>
       </c>
       <c r="BO24" s="18" t="n">
-        <v>5162693.5</v>
+        <v>5138571</v>
       </c>
       <c r="BP24" s="18" t="n">
-        <v>2689844.4</v>
+        <v>2677276.1</v>
       </c>
       <c r="BQ24" s="18" t="n">
-        <v>294405.1</v>
+        <v>293029.5</v>
       </c>
       <c r="BR24" s="18" t="n">
-        <v>135230.9</v>
+        <v>134599</v>
       </c>
       <c r="BS24" s="18" t="n">
-        <v>67430.2</v>
+        <v>67115.2</v>
       </c>
     </row>
     <row r="25">
@@ -43441,46 +43441,46 @@
         <v>1342515.1</v>
       </c>
       <c r="AI25" s="18" t="n">
-        <v>1237952.2</v>
+        <v>1234480.2</v>
       </c>
       <c r="AJ25" s="18" t="n">
-        <v>1129286.1</v>
+        <v>1124009.5</v>
       </c>
       <c r="AK25" s="18" t="n">
-        <v>1098386.6</v>
+        <v>1093254.4</v>
       </c>
       <c r="AL25" s="18" t="n">
-        <v>1103926.2</v>
+        <v>1098768.1</v>
       </c>
       <c r="AM25" s="18" t="n">
-        <v>1090429.7</v>
+        <v>1085334.7</v>
       </c>
       <c r="AN25" s="18" t="n">
-        <v>1078577.2</v>
+        <v>1073537.6</v>
       </c>
       <c r="AO25" s="18" t="n">
-        <v>1009487.7</v>
+        <v>1004770.8</v>
       </c>
       <c r="AP25" s="18" t="n">
-        <v>946893</v>
+        <v>942468.7</v>
       </c>
       <c r="AQ25" s="18" t="n">
-        <v>927019.3</v>
+        <v>922687.8</v>
       </c>
       <c r="AR25" s="18" t="n">
-        <v>814463.4</v>
+        <v>810657.8</v>
       </c>
       <c r="AS25" s="18" t="n">
-        <v>653984.1</v>
+        <v>650928.3</v>
       </c>
       <c r="AT25" s="18" t="n">
-        <v>129411.9</v>
+        <v>128807.2</v>
       </c>
       <c r="AU25" s="18" t="n">
-        <v>104370.5</v>
+        <v>103882.8</v>
       </c>
       <c r="AV25" s="18" t="n">
-        <v>34574.2</v>
+        <v>34412.6</v>
       </c>
       <c r="AW25" s="18" t="n">
         <v>0</v>
@@ -43612,73 +43612,73 @@
         <v>129814.1</v>
       </c>
       <c r="AI26" s="18" t="n">
-        <v>303664.7</v>
+        <v>302813</v>
       </c>
       <c r="AJ26" s="18" t="n">
-        <v>295258.1</v>
+        <v>293878.5</v>
       </c>
       <c r="AK26" s="18" t="n">
-        <v>298538.8</v>
+        <v>297143.8</v>
       </c>
       <c r="AL26" s="18" t="n">
-        <v>301819.4</v>
+        <v>300409.2</v>
       </c>
       <c r="AM26" s="18" t="n">
-        <v>301819.4</v>
+        <v>300409.2</v>
       </c>
       <c r="AN26" s="18" t="n">
-        <v>298538.8</v>
+        <v>297143.8</v>
       </c>
       <c r="AO26" s="18" t="n">
-        <v>298538.8</v>
+        <v>297143.8</v>
       </c>
       <c r="AP26" s="18" t="n">
-        <v>301819.4</v>
+        <v>300409.2</v>
       </c>
       <c r="AQ26" s="18" t="n">
-        <v>301819.4</v>
+        <v>300409.2</v>
       </c>
       <c r="AR26" s="18" t="n">
-        <v>295258.1</v>
+        <v>293878.5</v>
       </c>
       <c r="AS26" s="18" t="n">
-        <v>298538.8</v>
+        <v>297143.8</v>
       </c>
       <c r="AT26" s="18" t="n">
-        <v>288363.4</v>
+        <v>287016.1</v>
       </c>
       <c r="AU26" s="18" t="n">
-        <v>105454.4</v>
+        <v>104961.6</v>
       </c>
       <c r="AV26" s="18" t="n">
-        <v>84707</v>
+        <v>84311.2</v>
       </c>
       <c r="AW26" s="18" t="n">
-        <v>60373.6</v>
+        <v>60091.5</v>
       </c>
       <c r="AX26" s="18" t="n">
-        <v>61037.1</v>
+        <v>60751.9</v>
       </c>
       <c r="AY26" s="18" t="n">
-        <v>53713.3</v>
+        <v>53462.3</v>
       </c>
       <c r="AZ26" s="18" t="n">
-        <v>33344.6</v>
+        <v>33188.8</v>
       </c>
       <c r="BA26" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BB26" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BC26" s="18" t="n">
-        <v>34085.6</v>
+        <v>33926.3</v>
       </c>
       <c r="BD26" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
       <c r="BE26" s="18" t="n">
-        <v>33715.1</v>
+        <v>33557.6</v>
       </c>
     </row>
     <row r="27">
@@ -44006,95 +44006,95 @@
         <v/>
       </c>
       <c r="AI32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1342.11)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1337.49)</f>
         <v/>
       </c>
       <c r="AJ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AK32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AL32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AM32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AN32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AN$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AO32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AO$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AP32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AP$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AQ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AQ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AR32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AR$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AS32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AS$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AT32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AT$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AU32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AU$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AV32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AV$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AW32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AW$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AX32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AX$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AY32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AY$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AZ32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AZ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BA32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BA$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BB32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BB$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BC32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BC$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BD32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BD$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="BE32" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(BE$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
     </row>
@@ -54493,7 +54493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -60266,7 +60266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
